--- a/tame_output/ON/bt/strategyON_20240718.xlsx
+++ b/tame_output/ON/bt/strategyON_20240718.xlsx
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.0%</t>
+          <t>-71.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-500.2%</t>
+          <t>-499.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.8%</t>
+          <t>28.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-145.4%</t>
+          <t>-145.2%</t>
         </is>
       </c>
     </row>
@@ -48195,16 +48195,16 @@
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.386558802253087</v>
+        <v>-3.381708015295649</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.308088564130503</v>
+        <v>2.310028878913478</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.8533313651453369</v>
+        <v>0.8531188840605008</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.175067328432688</v>
+        <v>4.174939839781786</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240718.xlsx
+++ b/tame_output/ON/bt/strategyON_20240718.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>59.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.6%</t>
+          <t>18.1%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.4%</t>
+          <t>-11.7%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>47.3%</t>
+          <t>51.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>79.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>54.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.9%</t>
+          <t>-72.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.3%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-49.4%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.9%</t>
+          <t>-67.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.0%</t>
+          <t>457.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-499.7%</t>
+          <t>-512.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>28.9%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.3%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.3%</t>
+          <t>-9.5%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>24.8%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.9%</t>
+          <t>78.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-145.2%</t>
+          <t>-150.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-9.3%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.9%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.4%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.6%</t>
+          <t>-135.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-138.7%</t>
+          <t>-139.9%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>81.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2025</v>
+        <v>2024</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>74.3%</t>
+          <t>73.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.7</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1506,7 +1506,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-28.5%</t>
+          <t>-29.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2028"/>
+  <dimension ref="A1:G2027"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -47798,16 +47798,16 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647103</v>
+        <v>3.780973053504658</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.175799915698862</v>
+        <v>-2.167435081772867</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.350165216598611</v>
+        <v>2.353511150169009</v>
       </c>
       <c r="F2011" t="n">
         <v>1.132981408433784</v>
@@ -47821,16 +47821,16 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.74989685176353</v>
+        <v>3.751680267083167</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.177361558513722</v>
+        <v>-2.168996724587727</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.349540559472667</v>
+        <v>2.352886493043065</v>
       </c>
       <c r="F2012" t="n">
         <v>1.132981408433784</v>
@@ -47844,16 +47844,16 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392113</v>
+        <v>3.717617470711749</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.205262345623195</v>
+        <v>-2.1968975116972</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.33690428575588</v>
+        <v>2.340250219326278</v>
       </c>
       <c r="F2013" t="n">
         <v>1.098384484290849</v>
@@ -47867,16 +47867,16 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172524</v>
+        <v>3.686693354492161</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.208295343135869</v>
+        <v>-2.199930509209874</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.332455530728009</v>
+        <v>2.335801464298407</v>
       </c>
       <c r="F2014" t="n">
         <v>1.095351486778175</v>
@@ -47890,16 +47890,16 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971077</v>
+        <v>3.621145657290713</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.228356664412376</v>
+        <v>-2.21999183048638</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.39113696180791</v>
+        <v>2.394482895378308</v>
       </c>
       <c r="F2015" t="n">
         <v>1.075290165501668</v>
@@ -47913,16 +47913,16 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199804</v>
+        <v>3.64254766351944</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.4850774824072</v>
+        <v>-2.476712648481204</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.428760353611827</v>
+        <v>2.432106287182226</v>
       </c>
       <c r="F2016" t="n">
         <v>0.9668755913578532</v>
@@ -47936,16 +47936,16 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622235</v>
+        <v>3.670086579941871</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.63906390018334</v>
+        <v>-2.630699066257345</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.436146055647011</v>
+        <v>2.439491989217409</v>
       </c>
       <c r="F2017" t="n">
         <v>0.9668755913578532</v>
@@ -47959,16 +47959,16 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808527</v>
+        <v>3.621720592128163</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.588541996355674</v>
+        <v>-2.580177162429679</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.442406019298199</v>
+        <v>2.445751952868596</v>
       </c>
       <c r="F2018" t="n">
         <v>0.9668755913578532</v>
@@ -47982,16 +47982,16 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994892</v>
+        <v>3.658130309314528</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.841017150363399</v>
+        <v>-2.832652316437404</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.353286446750523</v>
+        <v>2.356632380320921</v>
       </c>
       <c r="F2019" t="n">
         <v>0.9668755913578532</v>
@@ -48005,16 +48005,16 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358296</v>
+        <v>3.675826111677932</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.110489952285107</v>
+        <v>-3.102125118359112</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.246707860500783</v>
+        <v>2.250053794071181</v>
       </c>
       <c r="F2020" t="n">
         <v>0.9668755913578532</v>
@@ -48028,16 +48028,16 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637084</v>
+        <v>3.66530703295672</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.268034024014548</v>
+        <v>-3.259669190088553</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.187811974036328</v>
+        <v>2.191157907606726</v>
       </c>
       <c r="F2021" t="n">
         <v>0.8999737862175787</v>
@@ -48051,16 +48051,16 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301341</v>
+        <v>3.653946728620977</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.396884574716595</v>
+        <v>-3.3885197407906</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.131349606491699</v>
+        <v>2.134695540062097</v>
       </c>
       <c r="F2022" t="n">
         <v>0.8589803773668572</v>
@@ -48074,16 +48074,16 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215468</v>
+        <v>3.669759882535104</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.513852267355486</v>
+        <v>-3.505487433429491</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.246766586135187</v>
+        <v>2.250112519705584</v>
       </c>
       <c r="F2023" t="n">
         <v>0.8589803773668572</v>
@@ -48097,16 +48097,16 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.69655362845669</v>
+        <v>3.698337043776326</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.598570209576439</v>
+        <v>-3.590205375650444</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.207726047210619</v>
+        <v>2.211071980781017</v>
       </c>
       <c r="F2024" t="n">
         <v>0.7738643484388108</v>
@@ -48120,16 +48120,16 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253286</v>
+        <v>3.751841591572922</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.680505027845323</v>
+        <v>-3.672140193919328</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.185181537471557</v>
+        <v>2.188527471041955</v>
       </c>
       <c r="F2025" t="n">
         <v>0.7639296028517306</v>
@@ -48143,16 +48143,16 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.78364702771783</v>
+        <v>3.785430443037466</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.626766854445061</v>
+        <v>-3.618402020519066</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.215602445287564</v>
+        <v>2.218948378857962</v>
       </c>
       <c r="F2026" t="n">
         <v>0.8176677762519927</v>
@@ -48166,45 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616946</v>
+        <v>3.797596990737665</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.516760570967839</v>
+        <v>-3.508395737041844</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.251757845922628</v>
+        <v>2.255103779493026</v>
       </c>
       <c r="F2027" t="n">
         <v>0.8408723481692679</v>
       </c>
       <c r="G2027" t="n">
         <v>4.163341907525072</v>
-      </c>
-    </row>
-    <row r="2028">
-      <c r="A2028" s="2" t="n">
-        <v>45490</v>
-      </c>
-      <c r="B2028" t="n">
-        <v>3.753720747048117</v>
-      </c>
-      <c r="C2028" t="n">
-        <v>3.663068509345485</v>
-      </c>
-      <c r="D2028" t="n">
-        <v>-3.381708015295649</v>
-      </c>
-      <c r="E2028" t="n">
-        <v>2.310028878913478</v>
-      </c>
-      <c r="F2028" t="n">
-        <v>0.8531188840605008</v>
-      </c>
-      <c r="G2028" t="n">
-        <v>4.174939839781786</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240718.xlsx
+++ b/tame_output/ON/bt/strategyON_20240718.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.5%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.7%</t>
+          <t>50.5%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.7%</t>
+          <t>79.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.7%</t>
         </is>
       </c>
     </row>
@@ -921,7 +921,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.4%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.3%</t>
+          <t>96.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.6%</t>
+          <t>-67.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-512.4%</t>
+          <t>-511.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-9.5%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-34.0%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>23.7%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1190,7 +1190,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-12.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-150.7%</t>
+          <t>-149.8%</t>
         </is>
       </c>
     </row>
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.4%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-139.9%</t>
+          <t>-140.1%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.8%</t>
+          <t>81.9%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-16</t>
+          <t>2024-07-17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.1%</t>
+          <t>48.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-29.7%</t>
+          <t>-29.4%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2027"/>
+  <dimension ref="A1:G2028"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -48166,7 +48166,7 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.797596990737665</v>
+        <v>3.800094359936582</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
@@ -48182,6 +48182,29 @@
       </c>
       <c r="G2027" t="n">
         <v>4.163341907525072</v>
+      </c>
+    </row>
+    <row r="2028">
+      <c r="A2028" s="2" t="n">
+        <v>45490</v>
+      </c>
+      <c r="B2028" t="n">
+        <v>3.786005218201046</v>
+      </c>
+      <c r="C2028" t="n">
+        <v>3.663068509345485</v>
+      </c>
+      <c r="D2028" t="n">
+        <v>-3.496927623390207</v>
+      </c>
+      <c r="E2028" t="n">
+        <v>2.263941035675655</v>
+      </c>
+      <c r="F2028" t="n">
+        <v>0.8387299776243229</v>
+      </c>
+      <c r="G2028" t="n">
+        <v>4.166306495920079</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240718.xlsx
+++ b/tame_output/ON/bt/strategyON_20240718.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.6%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.7%</t>
+          <t>-11.8%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>50.5%</t>
+          <t>56.6%</t>
         </is>
       </c>
     </row>
@@ -763,21 +763,21 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.0%</t>
+          <t>38.3%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>58.7%</t>
         </is>
       </c>
       <c r="F3" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,22 +786,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.7%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.3%</t>
+          <t>63.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.8%</t>
+          <t>31.1%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.5%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.4%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.5%</t>
+          <t>-72.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>109.5%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,11 +931,11 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,17 +944,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.2%</t>
+          <t>122.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.2%</t>
+          <t>96.5%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>24.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.4%</t>
+          <t>-48.9%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>90.7%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.7%</t>
+          <t>457.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.8%</t>
+          <t>-8.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-511.3%</t>
+          <t>-512.9%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,16 +1084,16 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,17 +1102,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>50.8%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1140,7 +1140,7 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-7.2%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-33.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.7%</t>
+          <t>21.9%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>78.8%</t>
+          <t>64.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-12.0%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-149.8%</t>
+          <t>-158.4%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.3%</t>
+          <t>-9.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1247,11 +1247,11 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.9%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.5%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.5%</t>
+          <t>-135.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-140.1%</t>
+          <t>-139.1%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>81.9%</t>
+          <t>62.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>56.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-07-17</t>
+          <t>2024-07-18</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>61.5%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1447,7 +1447,7 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,42 +1456,42 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-3.9%</t>
+          <t>-8.3%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.1%</t>
+          <t>-1.6%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>11.6%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>73.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>47.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-29.4%</t>
+          <t>-79.7%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2028"/>
+  <dimension ref="A1:G2029"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502790399141701</v>
+        <v>3.5027903991417</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440634</v>
+        <v>3.499971739440633</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.4900592416086</v>
+        <v>3.490059241608599</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485878594410271</v>
+        <v>3.48587859441027</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390585</v>
+        <v>3.493716014390584</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297398</v>
+        <v>3.492101641297397</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322542</v>
+        <v>3.573674025322541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.60003826515892</v>
+        <v>3.600038265158919</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940717</v>
+        <v>3.691571733940716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812102</v>
+        <v>3.684843823812101</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646216</v>
+        <v>3.710935533646214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611567</v>
+        <v>3.768951674611565</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955326</v>
+        <v>3.728577929955324</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.74770266023241</v>
+        <v>3.747702660232409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436226</v>
+        <v>3.766317079436225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311946</v>
+        <v>3.784684521311944</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
@@ -45199,7 +45199,7 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097241</v>
+        <v>3.800829354097239</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017769</v>
+        <v>3.789311112017767</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839722</v>
+        <v>3.833252747839721</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388725</v>
+        <v>3.839374447388724</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856161751626471</v>
+        <v>3.85616175162647</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787330429291812</v>
+        <v>3.78733042929181</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785787</v>
+        <v>3.801637122785785</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.155859013848905</v>
+        <v>3.076705710446317</v>
       </c>
       <c r="D1904" t="n">
         <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.3813071458480124</v>
       </c>
       <c r="F1904" t="n">
         <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.606150014052655</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390428</v>
+        <v>3.763182248390425</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.072073197193344</v>
       </c>
       <c r="D1905" t="n">
         <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.4295848220473939</v>
       </c>
       <c r="F1905" t="n">
         <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.680882784978214</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105951</v>
+        <v>3.784718794105949</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.074888257880981</v>
       </c>
       <c r="D1906" t="n">
         <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.4946952157589273</v>
       </c>
       <c r="F1906" t="n">
         <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.777140845201696</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960986</v>
+        <v>3.753882571960983</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.08779459910464</v>
       </c>
       <c r="D1907" t="n">
         <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.6072014764560185</v>
       </c>
       <c r="F1907" t="n">
         <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.790047186425355</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607644</v>
+        <v>3.692931855607641</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>2.959818669505421</v>
       </c>
       <c r="D1908" t="n">
         <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.4369895509475579</v>
       </c>
       <c r="F1908" t="n">
         <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.598717262962274</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987903</v>
+        <v>3.7704225839879</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.008363011382508</v>
       </c>
       <c r="D1909" t="n">
         <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.4780399319772055</v>
       </c>
       <c r="F1909" t="n">
         <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.643903999043281</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710813</v>
+        <v>3.760333686710809</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.88848408869434</v>
       </c>
       <c r="D1910" t="n">
         <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.4173370258520777</v>
       </c>
       <c r="F1910" t="n">
         <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.536217625900248</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409205</v>
+        <v>3.723566229409202</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.879770102440862</v>
       </c>
       <c r="D1911" t="n">
         <v>-6.124007074067299</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5089641519027821</v>
+        <v>0.4298108485001948</v>
       </c>
       <c r="F1911" t="n">
         <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.638438656401751</v>
+        <v>2.559285352999163</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.72996971609811</v>
+        <v>3.729969716098107</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.872809490345769</v>
       </c>
       <c r="D1912" t="n">
         <v>-6.080458667296608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5194229025159651</v>
+        <v>0.4402695991133778</v>
       </c>
       <c r="F1912" t="n">
         <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.631478044306657</v>
+        <v>2.55232474090407</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493421</v>
+        <v>3.782922533493418</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.887271844726912</v>
       </c>
       <c r="D1913" t="n">
         <v>-5.83831027384275</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.6307446142786515</v>
+        <v>0.5515913108760642</v>
       </c>
       <c r="F1913" t="n">
         <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.645940398687801</v>
+        <v>2.566787095285213</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722818</v>
+        <v>3.828551486722814</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.881803965186107</v>
       </c>
       <c r="D1914" t="n">
         <v>-5.730051136720228</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6685803895868552</v>
+        <v>0.5894270861842679</v>
       </c>
       <c r="F1914" t="n">
         <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.640472519146996</v>
+        <v>2.561319215744408</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792046</v>
+        <v>3.828052928792043</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.879302059196684</v>
       </c>
       <c r="D1915" t="n">
         <v>-5.606760001903098</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.7153949375242847</v>
+        <v>0.6362416341216974</v>
       </c>
       <c r="F1915" t="n">
         <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.711945294047851</v>
+        <v>2.632791990645264</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919907</v>
+        <v>3.812453678919904</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.887003037434009</v>
       </c>
       <c r="D1916" t="n">
         <v>-5.585610802999654</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.7315555953229871</v>
+        <v>0.6524022919203998</v>
       </c>
       <c r="F1916" t="n">
         <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.732335791627242</v>
+        <v>2.653182488224655</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318093</v>
+        <v>3.748328408318089</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.882783745781059</v>
       </c>
       <c r="D1917" t="n">
         <v>-5.34184536101621</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.8248424804634156</v>
+        <v>0.7456891770608283</v>
       </c>
       <c r="F1917" t="n">
         <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.728116499974293</v>
+        <v>2.648963196571705</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057525</v>
+        <v>3.824311233057522</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.884908059701075</v>
       </c>
       <c r="D1918" t="n">
         <v>-5.240082540738915</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8676719224943494</v>
+        <v>0.7885186190917621</v>
       </c>
       <c r="F1918" t="n">
         <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.738172254929766</v>
+        <v>2.659018951527178</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279185</v>
+        <v>3.826354974279181</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.877650134684778</v>
       </c>
       <c r="D1919" t="n">
         <v>-4.990232146789841</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9603541550576815</v>
+        <v>0.8812008516550942</v>
       </c>
       <c r="F1919" t="n">
         <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.730914329913468</v>
+        <v>2.651761026510881</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011498</v>
+        <v>3.835957987011494</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.881249258205426</v>
       </c>
       <c r="D1920" t="n">
         <v>-4.814340054322408</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.034310115565303</v>
+        <v>0.9551568121627161</v>
       </c>
       <c r="F1920" t="n">
         <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.734513453434117</v>
+        <v>2.655360150031529</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392987</v>
+        <v>3.780933911392983</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.89457676425998</v>
       </c>
       <c r="D1921" t="n">
         <v>-4.642893591299944</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.116216206828842</v>
+        <v>1.037062903426255</v>
       </c>
       <c r="F1921" t="n">
         <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.850708837302149</v>
+        <v>2.771555533899561</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632781</v>
+        <v>3.773765222632777</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.893597241876277</v>
       </c>
       <c r="D1922" t="n">
         <v>-4.568604025561605</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.144952510740475</v>
+        <v>1.065799207337888</v>
       </c>
       <c r="F1922" t="n">
         <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.894303054361449</v>
+        <v>2.815149750958862</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883073</v>
+        <v>3.764617879883069</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.898292042930594</v>
       </c>
       <c r="D1923" t="n">
         <v>-4.504968283327671</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.175101608688366</v>
+        <v>1.095948305285779</v>
       </c>
       <c r="F1923" t="n">
         <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.937179300756127</v>
+        <v>2.85802599735354</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074781</v>
+        <v>3.798814771074777</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.87948630171439</v>
       </c>
       <c r="D1924" t="n">
         <v>-4.39354152400175</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.20086657120253</v>
+        <v>1.121713267799942</v>
       </c>
       <c r="F1924" t="n">
         <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.918373559539923</v>
+        <v>2.839220256137335</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242292</v>
+        <v>3.797694884242288</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.881229378339267</v>
       </c>
       <c r="D1925" t="n">
         <v>-4.15311102719689</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.298781846549351</v>
+        <v>1.219628543146764</v>
       </c>
       <c r="F1925" t="n">
         <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.064374934247716</v>
+        <v>2.985221630845129</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367682</v>
+        <v>3.821593509367679</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.885158692174087</v>
       </c>
       <c r="D1926" t="n">
         <v>-4.080868459025695</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.331608187652649</v>
+        <v>1.252454884250062</v>
       </c>
       <c r="F1926" t="n">
         <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.068304248082536</v>
+        <v>2.989150944679949</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879964</v>
+        <v>3.82232699787996</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.885837276091427</v>
       </c>
       <c r="D1927" t="n">
         <v>-4.027870136744307</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.353486100482544</v>
+        <v>1.274332797079957</v>
       </c>
       <c r="F1927" t="n">
         <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.10218458740104</v>
+        <v>3.023031283998452</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502336</v>
+        <v>3.848616626502332</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.882835347311421</v>
       </c>
       <c r="D1928" t="n">
         <v>-3.919065251264581</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.394006125894429</v>
+        <v>1.314852822491841</v>
       </c>
       <c r="F1928" t="n">
         <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.099182658621033</v>
+        <v>3.020029355218446</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675936</v>
+        <v>3.818668951675932</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.884414384322035</v>
       </c>
       <c r="D1929" t="n">
         <v>-3.69904445322757</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.483593482119847</v>
+        <v>1.40444017871726</v>
       </c>
       <c r="F1929" t="n">
         <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.185493602672435</v>
+        <v>3.106340299269848</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539948</v>
+        <v>3.843274527539944</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.900308567123858</v>
       </c>
       <c r="D1930" t="n">
         <v>-3.566176764164292</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.552634740546982</v>
+        <v>1.473481437144395</v>
       </c>
       <c r="F1930" t="n">
         <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.201387785474259</v>
+        <v>3.122234482071671</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.84504738649626</v>
+        <v>3.845047386496256</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.90145441156416</v>
       </c>
       <c r="D1931" t="n">
         <v>-3.446003680799793</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.601849818333083</v>
+        <v>1.522696514930496</v>
       </c>
       <c r="F1931" t="n">
         <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.27463747993326</v>
+        <v>3.195484176530673</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576997</v>
+        <v>3.791273551576993</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.9115425141256</v>
       </c>
       <c r="D1932" t="n">
         <v>-3.301331535700055</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.669806778934418</v>
+        <v>1.590653475531831</v>
       </c>
       <c r="F1932" t="n">
         <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.371528869554542</v>
+        <v>3.292375566151955</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942102</v>
+        <v>3.735839222942098</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.897580005527026</v>
       </c>
       <c r="D1933" t="n">
         <v>-3.361206363057748</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.631894339392767</v>
+        <v>1.55274103599018</v>
       </c>
       <c r="F1933" t="n">
         <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.321641464541353</v>
+        <v>3.242488161138766</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674514</v>
+        <v>3.76264747767451</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>2.912869174761235</v>
       </c>
       <c r="D1934" t="n">
         <v>-3.24138613214691</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.695111600991311</v>
+        <v>1.615958297588723</v>
       </c>
       <c r="F1934" t="n">
         <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.336930633775562</v>
+        <v>3.257777330372974</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430692</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>2.820513374083676</v>
       </c>
       <c r="D1935" t="n">
         <v>-3.243855838608716</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.60176791772903</v>
+        <v>1.522614614326442</v>
       </c>
       <c r="F1935" t="n">
         <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.243093009220919</v>
+        <v>3.163939705818332</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003602</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>2.739775235568978</v>
       </c>
       <c r="D1936" t="n">
         <v>-3.312226024932726</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.493681704684727</v>
+        <v>1.41452840128214</v>
       </c>
       <c r="F1936" t="n">
         <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.16792029012795</v>
+        <v>3.088766986725362</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508369</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>2.730211944200869</v>
       </c>
       <c r="D1937" t="n">
         <v>-3.326014077779773</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.4786031921778</v>
+        <v>1.399449888775212</v>
       </c>
       <c r="F1937" t="n">
         <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.158356998759841</v>
+        <v>3.079203695357254</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417703</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.634074812643843</v>
+        <v>2.554921509241256</v>
       </c>
       <c r="D1938" t="n">
         <v>-3.357007237108478</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.290915493486704</v>
+        <v>1.211762190084117</v>
       </c>
       <c r="F1938" t="n">
         <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.983066563800228</v>
+        <v>2.903913260397641</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205898</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.638642044635631</v>
+        <v>2.559488741233043</v>
       </c>
       <c r="D1939" t="n">
         <v>-3.181532977316009</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.36567242939548</v>
+        <v>1.286519125992893</v>
       </c>
       <c r="F1939" t="n">
         <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.987633795792016</v>
+        <v>2.908480492389428</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225442</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.614384073396838</v>
+        <v>2.53523076999425</v>
       </c>
       <c r="D1940" t="n">
         <v>-3.292469229957257</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.297039957100188</v>
+        <v>1.2178866536976</v>
       </c>
       <c r="F1940" t="n">
         <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.963375824553223</v>
+        <v>2.884222521150635</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.542922386798288</v>
+        <v>2.4637690833957</v>
       </c>
       <c r="D1941" t="n">
         <v>-3.258805684484976</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.23904368869055</v>
+        <v>1.159890385287963</v>
       </c>
       <c r="F1941" t="n">
         <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.912112265238041</v>
+        <v>2.832958961835454</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264164</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.55309477323042</v>
+        <v>2.473941469827833</v>
       </c>
       <c r="D1942" t="n">
         <v>-3.198953065281252</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.273157122804172</v>
+        <v>1.194003819401584</v>
       </c>
       <c r="F1942" t="n">
         <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.922284651670174</v>
+        <v>2.843131348267586</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.7869499577423</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.54804104380428</v>
+        <v>2.468887740401693</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.112709602254875</v>
+        <v>-3.252414789086573</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.302600778588583</v>
+        <v>1.167565400453316</v>
       </c>
       <c r="F1943" t="n">
         <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.917230922244034</v>
+        <v>2.838077618841447</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316047</v>
+        <v>3.752027499316044</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.539816819248806</v>
+        <v>2.460663515846218</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.158016421653855</v>
+        <v>-3.297721608485554</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.276253826273517</v>
+        <v>1.14121844813825</v>
       </c>
       <c r="F1944" t="n">
         <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.884520599883021</v>
+        <v>2.805367296480434</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803192</v>
+        <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.540368692281907</v>
+        <v>2.46121538887932</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.187049526356156</v>
+        <v>-3.326754713187855</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.265192457425697</v>
+        <v>1.130157079290431</v>
       </c>
       <c r="F1945" t="n">
         <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.885072472916123</v>
+        <v>2.805919169513535</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.7333906008095</v>
+        <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.469641384173273</v>
+        <v>2.390488080770686</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.094239044905297</v>
+        <v>-3.233944231736996</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.231589341897407</v>
+        <v>1.09655396376214</v>
       </c>
       <c r="F1946" t="n">
         <v>0.6673167825078846</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.870031453678004</v>
+        <v>2.790878150275417</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560426</v>
+        <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.471514860097874</v>
+        <v>2.392361556695286</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.138628514234725</v>
+        <v>-3.278333701066424</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.215707030090237</v>
+        <v>1.08067165195497</v>
       </c>
       <c r="F1947" t="n">
         <v>0.622927313178457</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.845271248004948</v>
+        <v>2.766117944602361</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472739</v>
+        <v>3.721077195472735</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.466590568609597</v>
+        <v>2.387437265207009</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.025957295998475</v>
+        <v>-3.165662482830173</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.25585122589646</v>
+        <v>1.120815847761193</v>
       </c>
       <c r="F1948" t="n">
         <v>0.7355985314147071</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.907949687458421</v>
+        <v>2.828796384055834</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798537</v>
+        <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.472081864440264</v>
+        <v>2.392928561037677</v>
       </c>
       <c r="D1949" t="n">
-        <v>-2.913580294815802</v>
+        <v>-3.053285481647501</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.306293322200196</v>
+        <v>1.171257944064929</v>
       </c>
       <c r="F1949" t="n">
         <v>0.7355985314147071</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.913440983289088</v>
+        <v>2.834287679886501</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498865</v>
+        <v>3.689597840498861</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.483579066208803</v>
+        <v>2.404425762806216</v>
       </c>
       <c r="D1950" t="n">
-        <v>-2.941360692717155</v>
+        <v>-3.081065879548854</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.306678364808194</v>
+        <v>1.171642986672927</v>
       </c>
       <c r="F1950" t="n">
         <v>0.707818133513354</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.908269946316816</v>
+        <v>2.829116642914228</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705326</v>
+        <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.321934786209456</v>
+        <v>2.242781482806869</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.024361973742434</v>
+        <v>-3.164067160574133</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.111833572398735</v>
+        <v>0.9767981942634687</v>
       </c>
       <c r="F1951" t="n">
         <v>0.6892472489861803</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.735483135601165</v>
+        <v>2.656329832198578</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729271</v>
+        <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.442084446928662</v>
+        <v>2.362931143526075</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.132976052185765</v>
+        <v>-3.272681239017464</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.188537601740609</v>
+        <v>1.053502223605342</v>
       </c>
       <c r="F1952" t="n">
         <v>0.6892472489861803</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.85563279632037</v>
+        <v>2.776479492917783</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190769</v>
+        <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.456597473030985</v>
+        <v>2.377444169628398</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.097567013937622</v>
+        <v>-3.237272200769321</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.217214243142189</v>
+        <v>1.082178865006922</v>
       </c>
       <c r="F1953" t="n">
         <v>0.6892472489861803</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.870145822422693</v>
+        <v>2.790992519020106</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913426</v>
+        <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.454016914373354</v>
+        <v>2.374863610970766</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.059183351379471</v>
+        <v>-3.19888853821117</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.229987149507818</v>
+        <v>1.094951771372551</v>
       </c>
       <c r="F1954" t="n">
         <v>0.7276309115443315</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.890595461299953</v>
+        <v>2.811442157897365</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532486</v>
+        <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.450745943218656</v>
+        <v>2.371592639816068</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.882067021344305</v>
+        <v>-3.021772208176004</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.297562710367186</v>
+        <v>1.162527332231919</v>
       </c>
       <c r="F1955" t="n">
         <v>0.7276309115443315</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.887324490145255</v>
+        <v>2.808171186742667</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793903</v>
+        <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.451429334980569</v>
+        <v>2.372276031577981</v>
       </c>
       <c r="D1956" t="n">
-        <v>-2.927159266177851</v>
+        <v>-3.06686445300955</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.280209204195681</v>
+        <v>1.145173826060414</v>
       </c>
       <c r="F1956" t="n">
         <v>0.6657348683749417</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.850870256005534</v>
+        <v>2.771716952602947</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011234</v>
+        <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.445216310286983</v>
+        <v>2.366063006884396</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.747783844939083</v>
+        <v>-2.887489031770782</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.345746347997603</v>
+        <v>1.210710969862336</v>
       </c>
       <c r="F1957" t="n">
         <v>0.8225116265456603</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.93872328621438</v>
+        <v>2.859569982811792</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982229</v>
+        <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.426023765618573</v>
+        <v>2.346870462215985</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.792798058459689</v>
+        <v>-2.932503245291388</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.30854811792095</v>
+        <v>1.173512739785683</v>
       </c>
       <c r="F1958" t="n">
         <v>0.7921627312310557</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.901321404357207</v>
+        <v>2.822168100954619</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509536</v>
+        <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.431715327957519</v>
+        <v>2.352562024554931</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.059802568732125</v>
+        <v>-3.199507755563824</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.207437876150921</v>
+        <v>1.072402498015655</v>
       </c>
       <c r="F1959" t="n">
         <v>0.5977996931881071</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.790395143870383</v>
+        <v>2.711241840467796</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760812</v>
+        <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.43091924985402</v>
+        <v>2.351765946451433</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.161000350169298</v>
+        <v>-3.300705537000996</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.166162685472554</v>
+        <v>1.031127307337287</v>
       </c>
       <c r="F1960" t="n">
         <v>0.529390879642788</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.748553777639693</v>
+        <v>2.669400474237106</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815457</v>
+        <v>3.705571661815452</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.428519211408337</v>
+        <v>2.349365908005749</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.154489383554985</v>
+        <v>-3.294194570386684</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.166367033672596</v>
+        <v>1.031331655537329</v>
       </c>
       <c r="F1961" t="n">
         <v>0.529390879642788</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.74615373919401</v>
+        <v>2.667000435791422</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378101</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.425043930616582</v>
+        <v>2.345890627213994</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.135451255847688</v>
+        <v>-3.275156442679386</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.170507003963759</v>
+        <v>1.035471625828492</v>
       </c>
       <c r="F1962" t="n">
         <v>0.4712072683115934</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.707768291603538</v>
+        <v>2.628614988200951</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131251</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.602625799555262</v>
+        <v>2.523472496152675</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.166577886998306</v>
+        <v>-3.306283073830004</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.335638220442193</v>
+        <v>1.200602842306926</v>
       </c>
       <c r="F1963" t="n">
         <v>0.4712072683115934</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.885350160542218</v>
+        <v>2.806196857139631</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067866</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.603459128541396</v>
+        <v>2.524305825138808</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.180444648332223</v>
+        <v>-3.320149835163922</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.330924844894759</v>
+        <v>1.195889466759492</v>
       </c>
       <c r="F1964" t="n">
         <v>0.4333493515777705</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.863468739488058</v>
+        <v>2.784315436085471</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789123</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.609467658938322</v>
+        <v>2.530314355535734</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.135640476792293</v>
+        <v>-3.275345663623992</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.354855043907657</v>
+        <v>1.21981966577239</v>
       </c>
       <c r="F1965" t="n">
         <v>0.4333493515777705</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.869477269884984</v>
+        <v>2.790323966482397</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519909</v>
+        <v>3.781501250519904</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.507417880215521</v>
+        <v>2.428264576812934</v>
       </c>
       <c r="D1966" t="n">
-        <v>-2.987897506557291</v>
+        <v>-3.12760269338899</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.311902453278857</v>
+        <v>1.176867075143591</v>
       </c>
       <c r="F1966" t="n">
         <v>0.6011567088126537</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.868111905503114</v>
+        <v>2.788958602100526</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.80224592918117</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.510211501747002</v>
+        <v>2.431058198344415</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.089912189088512</v>
+        <v>-3.229617375920211</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.27389020179785</v>
+        <v>1.138854823662583</v>
       </c>
       <c r="F1967" t="n">
         <v>0.6011567088126537</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.870905527034595</v>
+        <v>2.791752223632007</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.80560898539473</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.51087385013866</v>
+        <v>2.431720546736073</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.083759483035728</v>
+        <v>-3.223464669867426</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.277013632610622</v>
+        <v>1.141978254475355</v>
       </c>
       <c r="F1968" t="n">
         <v>0.607309414865438</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.875259499057924</v>
+        <v>2.796106195655336</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890611</v>
+        <v>3.798239794890605</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.509954326878771</v>
+        <v>2.430801023476183</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.100568781186229</v>
+        <v>-3.240273968017928</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.269370390090532</v>
+        <v>1.134335011955265</v>
       </c>
       <c r="F1969" t="n">
         <v>0.5905001167149364</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.864254396907733</v>
+        <v>2.785101093505145</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798427</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.576289880675592</v>
+        <v>2.497136577273004</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.038270782410107</v>
+        <v>-3.177975969241806</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.360625143397801</v>
+        <v>1.225589765262535</v>
       </c>
       <c r="F1970" t="n">
         <v>0.5905001167149364</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.930589950704554</v>
+        <v>2.851436647301966</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992192</v>
+        <v>3.848729139992186</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.378581882389719</v>
+        <v>2.299428578987131</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.836480584744949</v>
+        <v>-2.976185771576648</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.243633224177992</v>
+        <v>1.108597846042725</v>
       </c>
       <c r="F1971" t="n">
         <v>0.7885183088840908</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.851692867720173</v>
+        <v>2.772539564317586</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852425</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.448872114711894</v>
+        <v>2.369718811309307</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.671667581666102</v>
+        <v>-2.811372768497801</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.379848657731706</v>
+        <v>1.244813279596439</v>
       </c>
       <c r="F1972" t="n">
         <v>0.9533313119629377</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.020870901889657</v>
+        <v>2.941717598487069</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319545</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.463499850827938</v>
+        <v>2.38434654742535</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.769408126291077</v>
+        <v>-2.909113313122775</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.35538017599776</v>
+        <v>1.220344797862493</v>
       </c>
       <c r="F1973" t="n">
         <v>0.9374420338299576</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.025965071125913</v>
+        <v>2.946811767723325</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489385</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.462035831652609</v>
+        <v>2.382882528250022</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.945745886414006</v>
+        <v>-3.085451073245705</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.28338105277326</v>
+        <v>1.148345674637993</v>
       </c>
       <c r="F1974" t="n">
         <v>0.7611042737070282</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.918698395876826</v>
+        <v>2.839545092474239</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397794</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.460527449692538</v>
+        <v>2.38137414628995</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.869323839982079</v>
+        <v>-3.009029026813778</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.312441489385959</v>
+        <v>1.177406111250692</v>
       </c>
       <c r="F1975" t="n">
         <v>0.7611042737070282</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.917190013916755</v>
+        <v>2.838036710514168</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316249</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.460390317127974</v>
+        <v>2.381237013725387</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.82495070834351</v>
+        <v>-2.964655895175209</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.330053609476822</v>
+        <v>1.195018231341556</v>
       </c>
       <c r="F1976" t="n">
         <v>0.8054774053455968</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.943676760335332</v>
+        <v>2.864523456932745</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105966</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.454784111266564</v>
+        <v>2.375630807863977</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.702116487456343</v>
+        <v>-2.841821674288042</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.37358109197028</v>
+        <v>1.238545713835013</v>
       </c>
       <c r="F1977" t="n">
         <v>0.8054774053455968</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.938070554473923</v>
+        <v>2.858917251071336</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190319</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.461165868294369</v>
+        <v>2.382012564891782</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.654460756895287</v>
+        <v>-2.794165943726986</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.399025141222507</v>
+        <v>1.26398976308724</v>
       </c>
       <c r="F1978" t="n">
         <v>0.8531331359066524</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.973045749838361</v>
+        <v>2.893892446435773</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569617</v>
+        <v>3.822678210569611</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.466058241669094</v>
+        <v>2.386904938266507</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.553942598396532</v>
+        <v>-2.693647785228231</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.444124777996734</v>
+        <v>1.309089399861467</v>
       </c>
       <c r="F1979" t="n">
         <v>0.953651294405407</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.038249018312338</v>
+        <v>2.959095714909751</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557292</v>
+        <v>3.828808877557287</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.452812914144966</v>
+        <v>2.373659610742379</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.614609188798922</v>
+        <v>-2.75431437563062</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.40661281431165</v>
+        <v>1.271577436176383</v>
       </c>
       <c r="F1980" t="n">
         <v>0.8719529776868733</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.975984700757091</v>
+        <v>2.896831397354503</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932767</v>
+        <v>3.816837033932762</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.456910616755595</v>
+        <v>2.377757313353007</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.569770787190524</v>
+        <v>-2.709475974022222</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.428645877565638</v>
+        <v>1.293610499430371</v>
       </c>
       <c r="F1981" t="n">
         <v>0.8764964106317428</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.982808463134641</v>
+        <v>2.903655159732053</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.81793235491705</v>
+        <v>3.817932354917045</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.461071556386673</v>
+        <v>2.381918252984085</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.670529422947522</v>
+        <v>-2.810234609779221</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.392503362893917</v>
+        <v>1.25746798475865</v>
       </c>
       <c r="F1982" t="n">
         <v>0.7876708419047374</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.933674061529516</v>
+        <v>2.854520758126928</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405958</v>
+        <v>3.826684745405953</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.46695115891451</v>
+        <v>2.387797855511923</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.626326585861622</v>
+        <v>-2.76603177269332</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.416064100256114</v>
+        <v>1.281028722120847</v>
       </c>
       <c r="F1983" t="n">
         <v>0.8318736789906378</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.966075366308893</v>
+        <v>2.886922062906305</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265644</v>
+        <v>3.838199629265639</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.465361159383757</v>
+        <v>2.38620785598117</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.663305613525065</v>
+        <v>-2.803010800356764</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.399682489659984</v>
+        <v>1.264647111524718</v>
       </c>
       <c r="F1984" t="n">
         <v>0.8688475807819683</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.986669707852939</v>
+        <v>2.907516404450352</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284879</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.516608924566797</v>
+        <v>2.43745562116421</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.505014195985793</v>
+        <v>-2.644719382817491</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.514246821858733</v>
+        <v>1.379211443723466</v>
       </c>
       <c r="F1985" t="n">
         <v>0.8688475807819683</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.037917473035979</v>
+        <v>2.958764169633391</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.86533868132102</v>
+        <v>3.865338681321015</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.51504962916105</v>
+        <v>2.435896325758463</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.297372192351316</v>
+        <v>-2.437077379183015</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.595744327906776</v>
+        <v>1.46070894977151</v>
       </c>
       <c r="F1986" t="n">
         <v>1.076489584416445</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.160943379810917</v>
+        <v>3.08179007640833</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475137</v>
+        <v>3.864489842475131</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.50999785739932</v>
+        <v>2.430844553996733</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.246340099628788</v>
+        <v>-2.386045286460487</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.611105393234058</v>
+        <v>1.476070015098791</v>
       </c>
       <c r="F1987" t="n">
         <v>1.127521677138973</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.186510863682704</v>
+        <v>3.107357560280117</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404851</v>
+        <v>3.842547360404846</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.527185261492025</v>
+        <v>2.448031958089438</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.181115918501582</v>
+        <v>-2.320821105333281</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.654382469777645</v>
+        <v>1.519347091642378</v>
       </c>
       <c r="F1988" t="n">
         <v>1.192745858266178</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.242832776451732</v>
+        <v>3.163679473049145</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882556</v>
+        <v>3.840061186882551</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.523146233791306</v>
+        <v>2.443992930388718</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.143688898430449</v>
+        <v>-2.283394085262147</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.665314250105379</v>
+        <v>1.530278871970112</v>
       </c>
       <c r="F1989" t="n">
         <v>1.19799739629536</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.241944671568522</v>
+        <v>3.162791368165935</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992659</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.524403026122546</v>
+        <v>2.445249722719959</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.163800554465157</v>
+        <v>-2.303505741296856</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.658526380022736</v>
+        <v>1.523491001887469</v>
       </c>
       <c r="F1990" t="n">
         <v>1.209024741292779</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.249817870898214</v>
+        <v>3.170664567495626</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636286</v>
+        <v>3.82866144563628</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.684960797143757</v>
+        <v>2.605807493741169</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.110055740037952</v>
+        <v>-2.249760926869651</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.840582076814828</v>
+        <v>1.705546698679562</v>
       </c>
       <c r="F1991" t="n">
         <v>1.219088050733241</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.416413627583702</v>
+        <v>3.337260324181115</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957623</v>
+        <v>3.813222820957618</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.805073706361574</v>
+        <v>2.725920402958987</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.03527347901294</v>
+        <v>-2.174978665844638</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.990607890442651</v>
+        <v>1.855572512307384</v>
       </c>
       <c r="F1992" t="n">
         <v>1.293870311758254</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.581395893416526</v>
+        <v>3.502242590013939</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998753</v>
+        <v>3.814230727998748</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.796781682375433</v>
+        <v>2.717628378972845</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.009189394749132</v>
+        <v>-2.14889458158083</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.992749500162033</v>
+        <v>1.857714122026766</v>
       </c>
       <c r="F1993" t="n">
         <v>1.293870311758254</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.573103869430385</v>
+        <v>3.493950566027798</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896927</v>
+        <v>3.803397818896921</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.794974877959212</v>
+        <v>2.715821574556625</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.931058213900185</v>
+        <v>-2.070763400731884</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.022195168085391</v>
+        <v>1.887159789950124</v>
       </c>
       <c r="F1994" t="n">
         <v>1.368047122641939</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.615803151544376</v>
+        <v>3.536649848141789</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959855</v>
+        <v>3.79626414395985</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.812529283686004</v>
+        <v>2.733375980283416</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.922165752506902</v>
+        <v>-2.061870939338601</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.043306558369496</v>
+        <v>1.908271180234229</v>
       </c>
       <c r="F1995" t="n">
         <v>1.368047122641939</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.633357557271167</v>
+        <v>3.55420425386858</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945366</v>
+        <v>3.79442494194536</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.804384331090588</v>
+        <v>2.725231027688</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.09064186947678</v>
+        <v>-2.230347056308478</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.967771158986129</v>
+        <v>1.832735780850862</v>
       </c>
       <c r="F1996" t="n">
         <v>1.340099286925358</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.608443903245802</v>
+        <v>3.529290599843215</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782707</v>
+        <v>3.795574066782701</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.785654028278449</v>
+        <v>2.706500724875862</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.392842340615196</v>
+        <v>-1.532547527446895</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.228160667718623</v>
+        <v>2.093125289583357</v>
       </c>
       <c r="F1997" t="n">
         <v>1.269751227554947</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.547504764811418</v>
+        <v>3.46835146140883</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.784671345632635</v>
+        <v>3.78467134563263</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.776318050775354</v>
+        <v>2.697164747372767</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.370121236932044</v>
+        <v>-1.509826423763743</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.227913131688789</v>
+        <v>2.092877753553522</v>
       </c>
       <c r="F1998" t="n">
         <v>1.269751227554947</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.538168787308322</v>
+        <v>3.459015483905735</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777672</v>
+        <v>3.783205696777666</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.935224176626523</v>
+        <v>2.856070873223936</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.368396193642</v>
+        <v>-1.508101380473699</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.387509274855976</v>
+        <v>2.252473896720709</v>
       </c>
       <c r="F1999" t="n">
         <v>1.271476270844991</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.698109939133518</v>
+        <v>3.61895663573093</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644411</v>
+        <v>3.779933725644406</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.97230199912017</v>
+        <v>2.893148695717582</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.523177200420256</v>
+        <v>-1.662882387251954</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.36267469463832</v>
+        <v>2.227639316503053</v>
       </c>
       <c r="F2000" t="n">
         <v>1.238108596790515</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.715167157194479</v>
+        <v>3.636013853791892</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799962</v>
+        <v>3.769443619799957</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.968977355109715</v>
+        <v>2.889824051707127</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.516122510205082</v>
+        <v>-1.65582769703678</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.362171926713935</v>
+        <v>2.227136548578668</v>
       </c>
       <c r="F2001" t="n">
         <v>1.245163287005689</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.716075327313128</v>
+        <v>3.636922023910541</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331116</v>
+        <v>3.76667349633111</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.978983508754456</v>
+        <v>2.899830205351869</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.489171285878594</v>
+        <v>-1.628876472710292</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.382958570089272</v>
+        <v>2.247923191954005</v>
       </c>
       <c r="F2002" t="n">
         <v>1.260043633033408</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.735009688574501</v>
+        <v>3.655856385171914</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784106</v>
+        <v>3.768052067784101</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.163086640899416</v>
+        <v>3.083933337496829</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.62512429393491</v>
+        <v>-1.764829480766609</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.512680499011705</v>
+        <v>2.377645120876438</v>
       </c>
       <c r="F2003" t="n">
         <v>1.260043633033408</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.919112820719461</v>
+        <v>3.839959517316874</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714424</v>
+        <v>3.743925505714419</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.155203335802409</v>
+        <v>3.076050032399822</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.647532411739782</v>
+        <v>-1.787237598571481</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.495833946792749</v>
+        <v>2.360798568657482</v>
       </c>
       <c r="F2004" t="n">
         <v>1.260043633033408</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.911229515622454</v>
+        <v>3.832076212219867</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155031</v>
+        <v>3.719118627155026</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.157257335352047</v>
+        <v>3.078104031949459</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.795538179219181</v>
+        <v>-1.93524336605088</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.438685639350627</v>
+        <v>2.30365026121536</v>
       </c>
       <c r="F2005" t="n">
         <v>1.173316624169866</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.861247309853967</v>
+        <v>3.782094006451379</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161976</v>
+        <v>3.729452285161971</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.213511053073894</v>
+        <v>3.134357749671306</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.804979105107711</v>
+        <v>-1.94468429193941</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.491162986717062</v>
+        <v>2.356127608581795</v>
       </c>
       <c r="F2006" t="n">
         <v>1.295743741713258</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.990957298101849</v>
+        <v>3.911803994699262</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321633</v>
+        <v>3.714941193321628</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.216402147619195</v>
+        <v>3.137248844216607</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.857252712443352</v>
+        <v>-1.996957899275051</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.473144638328106</v>
+        <v>2.33810926019284</v>
       </c>
       <c r="F2007" t="n">
         <v>1.243470134377616</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.962484228245764</v>
+        <v>3.883330924843178</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347701</v>
+        <v>3.727898186347696</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.21451396051297</v>
+        <v>3.135360657110382</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.933582690044258</v>
+        <v>-2.073287876875957</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.440724460181519</v>
+        <v>2.305689082046253</v>
       </c>
       <c r="F2008" t="n">
         <v>1.243470134377616</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.96059604113954</v>
+        <v>3.881442737736953</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887745</v>
+        <v>3.71065410488774</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.209334190115832</v>
+        <v>3.130180886713245</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.04533964265956</v>
+        <v>-2.185044829491258</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.390841908738261</v>
+        <v>2.255806530602994</v>
       </c>
       <c r="F2009" t="n">
         <v>1.131713181762315</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.888362099173222</v>
+        <v>3.809208795770634</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343063</v>
+        <v>3.712897612343058</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.207768200325984</v>
+        <v>3.128614896923397</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.043498623601308</v>
+        <v>-2.183203810433007</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.390012326571714</v>
+        <v>2.254976948436447</v>
       </c>
       <c r="F2010" t="n">
         <v>1.132981408433784</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.887557045386255</v>
+        <v>3.808403741983668</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.780973053504658</v>
+        <v>3.754911907647098</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.220841607191903</v>
+        <v>3.141688303789316</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.167435081772867</v>
+        <v>-2.31550510253056</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.353511150169009</v>
+        <v>2.215129838463345</v>
       </c>
       <c r="F2011" t="n">
         <v>1.132981408433784</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.900630452252174</v>
+        <v>3.821477148849586</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.751680267083167</v>
+        <v>3.749896851763524</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.220841607191903</v>
+        <v>3.141688303789316</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.168996724587727</v>
+        <v>-2.31706674534542</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.352886493043065</v>
+        <v>2.214505181337401</v>
       </c>
       <c r="F2012" t="n">
         <v>1.132981408433784</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.900630452252174</v>
+        <v>3.821477148849586</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.717617470711749</v>
+        <v>3.715834055392108</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.219365648318905</v>
+        <v>3.140212344916318</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.1968975116972</v>
+        <v>-2.344967532454893</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.340250219326278</v>
+        <v>2.201868907620613</v>
       </c>
       <c r="F2013" t="n">
         <v>1.098384484290849</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.878396338893415</v>
+        <v>3.799243035490827</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.686693354492161</v>
+        <v>3.684909939172519</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.216130092296104</v>
+        <v>3.136976788893516</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.199930509209874</v>
+        <v>-2.348000529967567</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.335801464298407</v>
+        <v>2.197420152592743</v>
       </c>
       <c r="F2014" t="n">
         <v>1.095351486778175</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.873340984363009</v>
+        <v>3.794187680960422</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.621145657290713</v>
+        <v>3.619362241971072</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.282836051886608</v>
+        <v>3.20368274848402</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.21999183048638</v>
+        <v>-2.368061851244073</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.394482895378308</v>
+        <v>2.256101583672644</v>
       </c>
       <c r="F2015" t="n">
         <v>1.075290165501668</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.928010151187609</v>
+        <v>3.848856847785021</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.64254766351944</v>
+        <v>3.640764248199798</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.423147770888455</v>
+        <v>3.343994467485867</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.476712648481204</v>
+        <v>-2.624782669238897</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.432106287182226</v>
+        <v>2.293724975476561</v>
       </c>
       <c r="F2016" t="n">
         <v>0.9668755913578532</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.003273125703167</v>
+        <v>3.92411982230058</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.670086579941871</v>
+        <v>3.668303164622229</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.492128040034094</v>
+        <v>3.412974736631507</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.630699066257345</v>
+        <v>-2.778769087015038</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.439491989217409</v>
+        <v>2.301110677511745</v>
       </c>
       <c r="F2017" t="n">
         <v>0.9668755913578532</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.072253394848807</v>
+        <v>3.99310009144622</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.621720592128163</v>
+        <v>3.619937176808522</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.478179242154215</v>
+        <v>3.399025938751628</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.580177162429679</v>
+        <v>-2.728247183187372</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.445751952868596</v>
+        <v>2.307370641162932</v>
       </c>
       <c r="F2018" t="n">
         <v>0.9668755913578532</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.058304596968927</v>
+        <v>3.97915129356634</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.658130309314528</v>
+        <v>3.656346893994887</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.490049731209629</v>
+        <v>3.410896427807042</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.832652316437404</v>
+        <v>-2.980722337195097</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.356632380320921</v>
+        <v>2.218251068615256</v>
       </c>
       <c r="F2019" t="n">
         <v>0.9668755913578532</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.070175086024341</v>
+        <v>3.991021782621754</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.675826111677932</v>
+        <v>3.67404269635829</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.491260265728573</v>
+        <v>3.412106962325986</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.102125118359112</v>
+        <v>-3.250195139116805</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.250053794071181</v>
+        <v>2.111672482365516</v>
       </c>
       <c r="F2020" t="n">
         <v>0.9668755913578532</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.071385620543285</v>
+        <v>3.992232317140698</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.66530703295672</v>
+        <v>3.663523617637079</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.495382007955894</v>
+        <v>3.416228704553307</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.259669190088553</v>
+        <v>-3.407739210846246</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.191157907606726</v>
+        <v>2.052776595901062</v>
       </c>
       <c r="F2021" t="n">
         <v>0.8999737862175787</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.035366279686442</v>
+        <v>3.956212976283854</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.653946728620977</v>
+        <v>3.652163313301336</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.490459860692084</v>
+        <v>3.411306557289496</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.3885197407906</v>
+        <v>-3.536589761548293</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.134695540062097</v>
+        <v>1.996314228356432</v>
       </c>
       <c r="F2022" t="n">
         <v>0.8589803773668572</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.005848087112199</v>
+        <v>3.926694783709611</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.669759882535104</v>
+        <v>3.667976467215462</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.652663917391128</v>
+        <v>3.573510613988541</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.505487433429491</v>
+        <v>-3.653557454187184</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.250112519705584</v>
+        <v>2.11173120799992</v>
       </c>
       <c r="F2023" t="n">
         <v>0.8589803773668572</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.168052143811242</v>
+        <v>4.088898840408655</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.698337043776326</v>
+        <v>3.696553628456685</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.647510555354942</v>
+        <v>3.568357251952355</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.590205375650444</v>
+        <v>-3.738275396408137</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.211071980781017</v>
+        <v>2.072690669075353</v>
       </c>
       <c r="F2024" t="n">
         <v>0.7738643484388108</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.111829164418229</v>
+        <v>4.032675861015641</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.751841591572922</v>
+        <v>3.750058176253281</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.657739972923433</v>
+        <v>3.578586669520846</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.672140193919328</v>
+        <v>-3.820210214677021</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.188527471041955</v>
+        <v>2.05014615933629</v>
       </c>
       <c r="F2025" t="n">
         <v>0.7639296028517306</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.116097734634472</v>
+        <v>4.036944431231884</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.785430443037466</v>
+        <v>3.783647027717825</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.666665611379336</v>
+        <v>3.587512307976748</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.618402020519066</v>
+        <v>-3.766472041276759</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.218948378857962</v>
+        <v>2.080567067152297</v>
       </c>
       <c r="F2026" t="n">
         <v>0.8176677762519927</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.157266277130532</v>
+        <v>4.078112973727944</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.800094359936582</v>
+        <v>3.798310944616941</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.658818498623511</v>
+        <v>3.579665195220924</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.508395737041844</v>
+        <v>-3.656465757799537</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.255103779493026</v>
+        <v>2.116722467787362</v>
       </c>
       <c r="F2027" t="n">
         <v>0.8408723481692679</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.163341907525072</v>
+        <v>4.084188604122485</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,45 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.786005218201046</v>
+        <v>3.723705980297934</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.663068509345485</v>
+        <v>3.583915205942898</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.496927623390207</v>
+        <v>-3.513406182058611</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.263941035675655</v>
+        <v>2.178196308805706</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.8387299776243229</v>
+        <v>0.8488857747592472</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.166306495920079</v>
+        <v>4.093246670798447</v>
+      </c>
+    </row>
+    <row r="2029">
+      <c r="A2029" s="2" t="n">
+        <v>45491</v>
+      </c>
+      <c r="B2029" t="n">
+        <v>3.847209947979509</v>
+      </c>
+      <c r="C2029" t="n">
+        <v>3.670335080891064</v>
+      </c>
+      <c r="D2029" t="n">
+        <v>-3.513406182058611</v>
+      </c>
+      <c r="E2029" t="n">
+        <v>2.178196308805706</v>
+      </c>
+      <c r="F2029" t="n">
+        <v>0.8488857747592472</v>
+      </c>
+      <c r="G2029" t="n">
+        <v>3.663398877877432</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240718.xlsx
+++ b/tame_output/ON/bt/strategyON_20240718.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.6%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.8%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.6%</t>
+          <t>51.5%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.8%</t>
+          <t>81.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>38.3%</t>
+          <t>38.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.7%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.7%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>31.1%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.4%</t>
+          <t>-7.6%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>60.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.6%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.5%</t>
+          <t>109.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.1%</t>
+          <t>121.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.5%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.2%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.9%</t>
+          <t>-48.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.5%</t>
+          <t>-66.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.7%</t>
+          <t>90.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>457.6%</t>
+          <t>458.1%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.2%</t>
+          <t>-8.0%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-512.9%</t>
+          <t>-492.7%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.8%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.1%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.6%</t>
+          <t>-33.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>21.9%</t>
+          <t>25.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>64.1%</t>
+          <t>162.9%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-10.7%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-158.4%</t>
+          <t>-142.4%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-9.1%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.14</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.0%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.4%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>0.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.3%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>27.9%</t>
+          <t>28.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.3%</t>
+          <t>-135.1%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-139.1%</t>
+          <t>-129.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>62.2%</t>
+          <t>61.6%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>70.1%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>93.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.6%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>47.4%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-17.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-74.3%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085799</v>
+        <v>3.301413393085798</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045692</v>
+        <v>3.317575502045691</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355689</v>
+        <v>3.311888301355688</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279813</v>
+        <v>3.385382209279812</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511403</v>
+        <v>3.367379938511402</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998559</v>
+        <v>3.367370539998558</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082123</v>
+        <v>3.299560092082122</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.293490533757921</v>
+        <v>3.29349053375792</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760739</v>
+        <v>3.293766719760738</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201486</v>
+        <v>3.295507330201485</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153005</v>
+        <v>3.258791981153004</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537425</v>
+        <v>3.271168579537424</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.27276013138219</v>
+        <v>3.272760131382189</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074621</v>
+        <v>3.25147557607462</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.233800325911638</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213495</v>
+        <v>3.223539378213494</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416044</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.235981977382328</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347053</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130015</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178242</v>
+        <v>3.315884374178241</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.30531679820781</v>
+        <v>3.305316798207809</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310979</v>
+        <v>3.284619513310978</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.30584953900653</v>
+        <v>3.305849539006529</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309421</v>
+        <v>3.31108639130942</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970901</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330519</v>
+        <v>3.300815818330518</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191733</v>
+        <v>3.302618194191732</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108635</v>
+        <v>3.305023265108634</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097817</v>
+        <v>3.341378723097816</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094112</v>
+        <v>3.374439043094111</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969589</v>
+        <v>3.424633354969588</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923082</v>
+        <v>3.419979433923081</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317612</v>
+        <v>3.447750501317611</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737166</v>
+        <v>3.503515506737165</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341309</v>
+        <v>3.503170282341308</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.50105255853946</v>
+        <v>3.501052558539459</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937498</v>
+        <v>3.492448711937497</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.680018109329392</v>
+        <v>-8.617334066908747</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3320435757902573</v>
+        <v>-0.3069699588219992</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.492449906936466</v>
+        <v>-1.483678187732079</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.244850148093368</v>
+        <v>2.250113179616</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.713670947837866</v>
+        <v>-8.65098690541722</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3410221567092107</v>
+        <v>-0.3159485397409525</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.592863274853503</v>
+        <v>-1.584091555649117</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.189084681827581</v>
+        <v>2.194347713350213</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.577517073749771</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.29626252254881</v>
+        <v>-0.2711889055805514</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.510621723981668</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.253801313844103</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-8.752641491136314</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3517570687559104</v>
+        <v>-0.3266834517876522</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.685746141368212</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.163281884159694</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-8.987093585150804</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4527570712633024</v>
+        <v>-0.4276834542950438</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.685746141368212</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.156062719258098</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.09146831617725</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.4761055374795986</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.790120872394658</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>2.086765689868254</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.144254471777577</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.4961042098811732</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-1.885796358977055</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>2.030476187757372</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.270291265145866</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.5438251985993743</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.860544736167313</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>2.048320890072333</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.213219493249936</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.5170061541546009</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.860544736167313</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>2.052311225758733</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.354891334974056</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.5751501177429907</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-1.860544736167313</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>2.050835998859991</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.305300490549222</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.5402603698081849</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-1.810953891742479</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>2.095643915679764</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.156382156077365</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.4937441696661251</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.779704301007306</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>2.101342536474185</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-8.930537003357955</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.3938270355421527</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.737777625420142</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.136077614862692</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-8.805958347020363</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.3428564284510567</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.737777625420142</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.137216759418751</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-8.85885363506465</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.3613807695066638</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.732822279331696</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.142823741233926</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-8.786720459776769</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.326793795152875</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.732822279331696</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.148557445472562</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-8.715354067167121</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.3079845005028812</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.661455886722048</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.181640018644486</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.621895033181897</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.2804843682216989</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.661455886722048</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.171756537331579</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.354653232313499</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.1754222083737136</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.661455886722048</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.169921976832205</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.256746193637008</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.1365597078765783</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.593470136861492</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.210413111775078</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.23279265266105</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.1263097853407014</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.569516595885534</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.225453742506146</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-7.968732714338254</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.03394612617333514</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.305456657562738</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.370629389338072</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.261653090833416</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.2460986895682993</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.305456657562738</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.367842355677771</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.221468792467226</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.2625160328026168</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.265272359196547</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.392296558585326</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.058068921527863</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.3272428023991187</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.101872488257185</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.489703302369701</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-6.824587699298265</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.4285597201288107</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-0.8683912660275861</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.637716464545313</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785785</v>
+        <v>3.801637122785786</v>
       </c>
       <c r="C1904" t="n">
-        <v>3.076705710446317</v>
+        <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.67492130829075</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3813071458480124</v>
+        <v>0.4855340662188574</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.7754877747850502</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.606150014052655</v>
+        <v>2.690566348977875</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390425</v>
+        <v>3.763182248390426</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.072073197193344</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.542645834659863</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4295848220473939</v>
+        <v>0.5338117424182389</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.6432123011541635</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.680882784978214</v>
+        <v>2.765299119903434</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784718794105949</v>
+        <v>3.78471879410595</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.074888257880981</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.386907502100121</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4946952157589273</v>
+        <v>0.5989221361297723</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4874739685944219</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.777140845201696</v>
+        <v>2.861557180126916</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960983</v>
+        <v>3.753882571960984</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.08779459910464</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.13790770341654</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6072014764560185</v>
+        <v>0.7114283968268635</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.4874739685944219</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.790047186425355</v>
+        <v>2.874463521350574</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607641</v>
+        <v>3.692931855607642</v>
       </c>
       <c r="C1908" t="n">
-        <v>2.959818669505421</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.243497693189645</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4369895509475579</v>
+        <v>0.5412164713184033</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.5930639583675263</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.598717262962274</v>
+        <v>2.683133597887493</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.7704225839879</v>
+        <v>3.770422583987902</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.008363011382508</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.262232595308242</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.4780399319772055</v>
+        <v>0.5822668523480505</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.5986599680276576</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.643903999043281</v>
+        <v>2.7283203339685</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710809</v>
+        <v>3.760333686710812</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.88848408869434</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.114292553900643</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.4173370258520777</v>
+        <v>0.5215639462229227</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.5783390521191001</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.536217625900248</v>
+        <v>2.620633960825467</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409202</v>
+        <v>3.723566229409204</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.879770102440862</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.124007074067299</v>
+        <v>-6.061323031646654</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4298108485001948</v>
+        <v>0.5340377688710403</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5253695298651112</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.559285352999163</v>
+        <v>2.643701687924382</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098107</v>
+        <v>3.729969716098109</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.872809490345769</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.080458667296608</v>
+        <v>-6.017774624875964</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4402695991133778</v>
+        <v>0.5444965194842233</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5253695298651112</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.55232474090407</v>
+        <v>2.636741075829289</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493418</v>
+        <v>3.78292253349342</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.887271844726912</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.83831027384275</v>
+        <v>-5.775626231422105</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5515913108760642</v>
+        <v>0.6558182312469096</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5253695298651112</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.566787095285213</v>
+        <v>2.651203430210432</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722814</v>
+        <v>3.828551486722817</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.881803965186107</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.730051136720228</v>
+        <v>-5.667367094299584</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5894270861842679</v>
+        <v>0.6936540065551133</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5341412490694978</v>
+        <v>-0.5253695298651112</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.561319215744408</v>
+        <v>2.645735550669627</v>
       </c>
     </row>
     <row r="1915">
@@ -45590,22 +45590,22 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.828052928792043</v>
+        <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.879302059196684</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.606760001903098</v>
+        <v>-5.544075959482453</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6362416341216974</v>
+        <v>0.7404685544925425</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4108501142523673</v>
+        <v>-0.4020783950479807</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.632791990645264</v>
+        <v>2.717208325570483</v>
       </c>
     </row>
     <row r="1916">
@@ -45613,22 +45613,22 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812453678919904</v>
+        <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.887003037434009</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.585610802999654</v>
+        <v>-5.52292676057901</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6524022919203998</v>
+        <v>0.7566292122912448</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.3809291961445374</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.653182488224655</v>
+        <v>2.737598823149874</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318089</v>
+        <v>3.748328408318091</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.882783745781059</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.34184536101621</v>
+        <v>-5.279161318595565</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7456891770608283</v>
+        <v>0.8499160974316733</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3897009153489239</v>
+        <v>-0.3809291961445374</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.648963196571705</v>
+        <v>2.733379531496924</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057522</v>
+        <v>3.824311233057523</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.884908059701075</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.240082540738915</v>
+        <v>-5.17739849831827</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7885186190917621</v>
+        <v>0.8927455394626072</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3677101277521087</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.659018951527178</v>
+        <v>2.743435286452398</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279181</v>
+        <v>3.826354974279183</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.877650134684778</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.990232146789841</v>
+        <v>-4.927548104369196</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8812008516550942</v>
+        <v>0.9854277720259392</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3677101277521087</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.651761026510881</v>
+        <v>2.7361773614361</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011494</v>
+        <v>3.835957987011496</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.881249258205426</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.814340054322408</v>
+        <v>-4.751656011901764</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9551568121627161</v>
+        <v>1.059383732533561</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3764818469564952</v>
+        <v>-0.3677101277521087</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.655360150031529</v>
+        <v>2.739776484956749</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392983</v>
+        <v>3.780933911392985</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.89457676425998</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.642893591299944</v>
+        <v>-4.5802095488793</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.037062903426255</v>
+        <v>1.1412898237971</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2050353839340321</v>
+        <v>-0.1962636647296455</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.771555533899561</v>
+        <v>2.85597186882478</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632777</v>
+        <v>3.773765222632779</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.893597241876277</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.568604025561605</v>
+        <v>-4.505919983140961</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.065799207337888</v>
+        <v>1.170026127708732</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1307458181956928</v>
+        <v>-0.1219740989913062</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.815149750958862</v>
+        <v>2.899566085884081</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883069</v>
+        <v>3.764617879883071</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.898292042930594</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.504968283327671</v>
+        <v>-4.442284240907027</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.095948305285779</v>
+        <v>1.200175225656624</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.0583383567573717</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.85802599735354</v>
+        <v>2.942442332278759</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074777</v>
+        <v>3.798814771074779</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.87948630171439</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.39354152400175</v>
+        <v>-4.330857481581107</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.121713267799942</v>
+        <v>1.225940188170787</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.06711007596175828</v>
+        <v>-0.0583383567573717</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.839220256137335</v>
+        <v>2.923636591062555</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797694884242288</v>
+        <v>3.79769488424229</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.881229378339267</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.15311102719689</v>
+        <v>-4.090426984776246</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.219628543146764</v>
+        <v>1.323855463517609</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1820921400474886</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.985221630845129</v>
+        <v>3.069637965770348</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821593509367679</v>
+        <v>3.82159350936768</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.885158692174087</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.080868459025695</v>
+        <v>-4.018184416605052</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.252454884250062</v>
+        <v>1.356681804620907</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.173320420843102</v>
+        <v>0.1820921400474886</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.989150944679949</v>
+        <v>3.073567279605168</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232699787996</v>
+        <v>3.822326997879962</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.885837276091427</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.027870136744307</v>
+        <v>-3.965186094323663</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.274332797079957</v>
+        <v>1.378559717450802</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.2374283990494274</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.023031283998452</v>
+        <v>3.107447618923671</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502332</v>
+        <v>3.848616626502334</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.882835347311421</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.919065251264581</v>
+        <v>-3.856381208843937</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.314852822491841</v>
+        <v>1.419079742862686</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2286566798450408</v>
+        <v>0.2374283990494274</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.020029355218446</v>
+        <v>3.104445690143665</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675932</v>
+        <v>3.818668951675934</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.884414384322035</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.69904445322757</v>
+        <v>-3.636360410806926</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.40444017871726</v>
+        <v>1.508667099088105</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.3786482441174077</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.106340299269848</v>
+        <v>3.190756634195067</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539944</v>
+        <v>3.843274527539946</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.900308567123858</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.566176764164292</v>
+        <v>-3.503492721743648</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.473481437144395</v>
+        <v>1.57770835751524</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3698765249130211</v>
+        <v>0.3786482441174077</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.122234482071671</v>
+        <v>3.20665081699689</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496256</v>
+        <v>3.845047386496258</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.90145441156416</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.446003680799793</v>
+        <v>-3.383319638379149</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.522696514930496</v>
+        <v>1.626923435301341</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4900496082775201</v>
+        <v>0.4988213274819067</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.195484176530673</v>
+        <v>3.279900511455892</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576993</v>
+        <v>3.791273551576995</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.9115425141256</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.301331535700055</v>
+        <v>-3.238647493279411</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.590653475531831</v>
+        <v>1.694880395902676</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6347217533772576</v>
+        <v>0.6434934725816441</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.292375566151955</v>
+        <v>3.376791901077174</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942098</v>
+        <v>3.7358392229421</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.897580005527026</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.361206363057748</v>
+        <v>-3.298522320637104</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.55274103599018</v>
+        <v>1.656967956361024</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.583618645223952</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.242488161138766</v>
+        <v>3.326904496063985</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264747767451</v>
+        <v>3.762647477674512</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.912869174761235</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.24138613214691</v>
+        <v>-3.178702089726266</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.615958297588723</v>
+        <v>1.720185217959568</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.5748469260195654</v>
+        <v>0.583618645223952</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.257777330372974</v>
+        <v>3.342193665298193</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.72914639843069</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.820513374083676</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.243855838608716</v>
+        <v>-3.181171796188072</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.522614614326442</v>
+        <v>1.626841534697287</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5723772195577592</v>
+        <v>0.5811489387621458</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.163939705818332</v>
+        <v>3.248356040743551</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.7432201960036</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.739775235568978</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.312226024932726</v>
+        <v>-3.249541982512082</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.41452840128214</v>
+        <v>1.518755321652985</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5904246377983607</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.088766986725362</v>
+        <v>3.173183321650582</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508367</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.730211944200869</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.326014077779773</v>
+        <v>-3.263330035359129</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.399449888775212</v>
+        <v>1.503676809146057</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5904246377983607</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.079203695357254</v>
+        <v>3.163620030282473</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417701</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.554921509241256</v>
+        <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.357007237108478</v>
+        <v>-3.294323194687834</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.211762190084117</v>
+        <v>1.315989110454962</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5904246377983607</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.903913260397641</v>
+        <v>2.98832959532286</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205896</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.559488741233043</v>
+        <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.181532977316009</v>
+        <v>-3.118848934895365</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.286519125992893</v>
+        <v>1.390746046363737</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5904246377983607</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.908480492389428</v>
+        <v>2.992896827314647</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225441</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.53523076999425</v>
+        <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.292469229957257</v>
+        <v>-3.229785187536613</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.2178866536976</v>
+        <v>1.322113574068445</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5816529185939742</v>
+        <v>0.5904246377983607</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.884222521150635</v>
+        <v>2.968638856075855</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.4637690833957</v>
+        <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.258805684484976</v>
+        <v>-3.196121642064332</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.159890385287963</v>
+        <v>1.264117305658808</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6240881832706426</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.832958961835454</v>
+        <v>2.917375296760673</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264162</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.473941469827833</v>
+        <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.198953065281252</v>
+        <v>-3.136269022860608</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.194003819401584</v>
+        <v>1.298230739772429</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6240881832706426</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.843131348267586</v>
+        <v>2.927547683192806</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.786949957742299</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.468887740401693</v>
+        <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.252414789086573</v>
+        <v>-3.050025559834231</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.167565400453316</v>
+        <v>1.32767439555684</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6153164640662561</v>
+        <v>0.6240881832706426</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.838077618841447</v>
+        <v>2.922493953766666</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316044</v>
+        <v>3.752027499316045</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.460663515846218</v>
+        <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.297721608485554</v>
+        <v>-3.095332379233211</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.14121844813825</v>
+        <v>1.301327443241774</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5832780202614118</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.805367296480434</v>
+        <v>2.889783631405653</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803189</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.46121538887932</v>
+        <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.326754713187855</v>
+        <v>-3.124365483935513</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.130157079290431</v>
+        <v>1.290266074393955</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5745063010570253</v>
+        <v>0.5832780202614118</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.805919169513535</v>
+        <v>2.890335504438755</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.733390600809496</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.390488080770686</v>
+        <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.233944231736996</v>
+        <v>-3.031555002484653</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.09655396376214</v>
+        <v>1.256662958865664</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6673167825078846</v>
+        <v>0.6760885017122712</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.790878150275417</v>
+        <v>2.875294485200636</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560423</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.392361556695286</v>
+        <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.278333701066424</v>
+        <v>-3.075944471814081</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.08067165195497</v>
+        <v>1.240780647058494</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.622927313178457</v>
+        <v>0.6316990323828435</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.766117944602361</v>
+        <v>2.85053427952758</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472735</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.387437265207009</v>
+        <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.165662482830173</v>
+        <v>-2.963273253577831</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.120815847761193</v>
+        <v>1.280924842864717</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.7443702506190937</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.828796384055834</v>
+        <v>2.913212718981053</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798534</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.392928561037677</v>
+        <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.053285481647501</v>
+        <v>-2.850896252395158</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.171257944064929</v>
+        <v>1.331366939168454</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7355985314147071</v>
+        <v>0.7443702506190937</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.834287679886501</v>
+        <v>2.918704014811721</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498861</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.404425762806216</v>
+        <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.081065879548854</v>
+        <v>-2.878676650296511</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.171642986672927</v>
+        <v>1.331751981776451</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.707818133513354</v>
+        <v>0.7165898527177406</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.829116642914228</v>
+        <v>2.913532977839448</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705322</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.242781482806869</v>
+        <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.164067160574133</v>
+        <v>-2.96167793132179</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9767981942634687</v>
+        <v>1.136907189366993</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.6980189681905669</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.656329832198578</v>
+        <v>2.740746167123797</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729267</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.362931143526075</v>
+        <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.272681239017464</v>
+        <v>-3.070292009765121</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.053502223605342</v>
+        <v>1.213611218708866</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.6980189681905669</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.776479492917783</v>
+        <v>2.860895827843002</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190765</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.377444169628398</v>
+        <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.237272200769321</v>
+        <v>-3.034882971516979</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.082178865006922</v>
+        <v>1.242287860110446</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6892472489861803</v>
+        <v>0.6980189681905669</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.790992519020106</v>
+        <v>2.875408853945325</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913423</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.374863610970766</v>
+        <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.19888853821117</v>
+        <v>-2.996499308958827</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.094951771372551</v>
+        <v>1.255060766476076</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.7276309115443315</v>
+        <v>0.736402630748718</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.811442157897365</v>
+        <v>2.895858492822585</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532482</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.371592639816068</v>
+        <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.021772208176004</v>
+        <v>-2.819382978923661</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.162527332231919</v>
+        <v>1.322636327335444</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.7276309115443315</v>
+        <v>0.736402630748718</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.808171186742667</v>
+        <v>2.892587521667886</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793899</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.372276031577981</v>
+        <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.06686445300955</v>
+        <v>-2.864475223757207</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.145173826060414</v>
+        <v>1.305282821163939</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6657348683749417</v>
+        <v>0.6745065875793282</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.771716952602947</v>
+        <v>2.856133287528166</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011231</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.366063006884396</v>
+        <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.887489031770782</v>
+        <v>-2.685099802518439</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.210710969862336</v>
+        <v>1.37081996496586</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8225116265456603</v>
+        <v>0.8312833457500469</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.859569982811792</v>
+        <v>2.943986317737012</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982225</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.346870462215985</v>
+        <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.932503245291388</v>
+        <v>-2.730114016039046</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.173512739785683</v>
+        <v>1.333621734889207</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7921627312310557</v>
+        <v>0.8009344504354423</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.822168100954619</v>
+        <v>2.906584435879839</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509533</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.352562024554931</v>
+        <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.199507755563824</v>
+        <v>-2.997118526311481</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.072402498015655</v>
+        <v>1.232511493119179</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5977996931881071</v>
+        <v>0.6065714123924937</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.711241840467796</v>
+        <v>2.795658175393015</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760808</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.351765946451433</v>
+        <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.300705537000996</v>
+        <v>-3.098316307748654</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.031127307337287</v>
+        <v>1.191236302440811</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.529390879642788</v>
+        <v>0.5381625988471745</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.669400474237106</v>
+        <v>2.753816809162325</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815452</v>
+        <v>3.705571661815453</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.349365908005749</v>
+        <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.294194570386684</v>
+        <v>-3.091805341134341</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.031331655537329</v>
+        <v>1.191440650640853</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.529390879642788</v>
+        <v>0.5381625988471745</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.667000435791422</v>
+        <v>2.751416770716641</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378098</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.345890627213994</v>
+        <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.275156442679386</v>
+        <v>-3.072767213427044</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.035471625828492</v>
+        <v>1.195580620932017</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.4712072683115934</v>
+        <v>0.47997898751598</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.628614988200951</v>
+        <v>2.71303132312617</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131247</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.523472496152675</v>
+        <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.306283073830004</v>
+        <v>-3.103893844577662</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.200602842306926</v>
+        <v>1.36071183741045</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.4712072683115934</v>
+        <v>0.47997898751598</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.806196857139631</v>
+        <v>2.89061319206485</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067863</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.524305825138808</v>
+        <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.320149835163922</v>
+        <v>-3.117760605911579</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.195889466759492</v>
+        <v>1.355998461863017</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4333493515777705</v>
+        <v>0.4421210707821571</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.784315436085471</v>
+        <v>2.86873177101069</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.78742558078912</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.530314355535734</v>
+        <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.275345663623992</v>
+        <v>-3.072956434371649</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.21981966577239</v>
+        <v>1.379928660875915</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4333493515777705</v>
+        <v>0.4421210707821571</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.790323966482397</v>
+        <v>2.874740301407616</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519904</v>
+        <v>3.781501250519906</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.428264576812934</v>
+        <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.12760269338899</v>
+        <v>-2.925213464136647</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.176867075143591</v>
+        <v>1.336976070247115</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6011567088126537</v>
+        <v>0.6099284280170403</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.788958602100526</v>
+        <v>2.873374937025746</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.802245929181167</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.431058198344415</v>
+        <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.229617375920211</v>
+        <v>-3.027228146667868</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.138854823662583</v>
+        <v>1.298963818766108</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6011567088126537</v>
+        <v>0.6099284280170403</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.791752223632007</v>
+        <v>2.876168558557227</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.805608985394726</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.431720546736073</v>
+        <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.223464669867426</v>
+        <v>-3.021075440615084</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.141978254475355</v>
+        <v>1.30208724957888</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.607309414865438</v>
+        <v>0.6160811340698246</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.796106195655336</v>
+        <v>2.880522530580556</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890605</v>
+        <v>3.798239794890607</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.430801023476183</v>
+        <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.240273968017928</v>
+        <v>-3.037884738765585</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.134335011955265</v>
+        <v>1.294444007058789</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5905001167149364</v>
+        <v>0.599271835919323</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.785101093505145</v>
+        <v>2.869517428430365</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798424</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.497136577273004</v>
+        <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.177975969241806</v>
+        <v>-2.975586739989463</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.225589765262535</v>
+        <v>1.385698760366059</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5905001167149364</v>
+        <v>0.599271835919323</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.851436647301966</v>
+        <v>2.935852982227185</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992186</v>
+        <v>3.848729139992188</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.299428578987131</v>
+        <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.976185771576648</v>
+        <v>-2.773796542324305</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.108597846042725</v>
+        <v>1.268706841146249</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7885183088840908</v>
+        <v>0.7972900280884774</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.772539564317586</v>
+        <v>2.856955899242805</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852421</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.369718811309307</v>
+        <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.811372768497801</v>
+        <v>-2.608983539245458</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.244813279596439</v>
+        <v>1.404922274699963</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9533313119629377</v>
+        <v>0.9621030311673243</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.941717598487069</v>
+        <v>3.026133933412289</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319542</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.38434654742535</v>
+        <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.909113313122775</v>
+        <v>-2.706724083870433</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.220344797862493</v>
+        <v>1.380453792966017</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9374420338299576</v>
+        <v>0.9462137530343442</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.946811767723325</v>
+        <v>3.031228102648544</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489381</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.382882528250022</v>
+        <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.085451073245705</v>
+        <v>-2.883061843993362</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.148345674637993</v>
+        <v>1.308454669741517</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7611042737070282</v>
+        <v>0.7698759929114147</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.839545092474239</v>
+        <v>2.923961427399458</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397791</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.38137414628995</v>
+        <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.009029026813778</v>
+        <v>-2.806639797561435</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.177406111250692</v>
+        <v>1.337515106354217</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7611042737070282</v>
+        <v>0.7698759929114147</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.838036710514168</v>
+        <v>2.922453045439387</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316246</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.381237013725387</v>
+        <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.964655895175209</v>
+        <v>-2.762266665922867</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.195018231341556</v>
+        <v>1.35512722644508</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8054774053455968</v>
+        <v>0.8142491245499833</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.864523456932745</v>
+        <v>2.948939791857964</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105963</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.375630807863977</v>
+        <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.841821674288042</v>
+        <v>-2.639432445035699</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.238545713835013</v>
+        <v>1.398654708938537</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8054774053455968</v>
+        <v>0.8142491245499833</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.858917251071336</v>
+        <v>2.943333585996555</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190319</v>
+        <v>3.833011148190321</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.382012564891782</v>
+        <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.794165943726986</v>
+        <v>-2.591776714474643</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.26398976308724</v>
+        <v>1.424098758190764</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.8531331359066524</v>
+        <v>0.861904855111039</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.893892446435773</v>
+        <v>2.978308781360993</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569611</v>
+        <v>3.822678210569613</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.386904938266507</v>
+        <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.693647785228231</v>
+        <v>-2.491258555975889</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.309089399861467</v>
+        <v>1.469198394964991</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.953651294405407</v>
+        <v>0.9624230136097935</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.959095714909751</v>
+        <v>3.04351204983497</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557287</v>
+        <v>3.828808877557289</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.373659610742379</v>
+        <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.75431437563062</v>
+        <v>-2.551925146378278</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.271577436176383</v>
+        <v>1.431686431279908</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8719529776868733</v>
+        <v>0.8807246968912599</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.896831397354503</v>
+        <v>2.981247732279722</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932762</v>
+        <v>3.816837033932764</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.377757313353007</v>
+        <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.709475974022222</v>
+        <v>-2.50708674476988</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.293610499430371</v>
+        <v>1.453719494533896</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8764964106317428</v>
+        <v>0.8852681298361293</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.903655159732053</v>
+        <v>2.988071494657273</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917045</v>
+        <v>3.817932354917047</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.381918252984085</v>
+        <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.810234609779221</v>
+        <v>-2.607845380526878</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.25746798475865</v>
+        <v>1.417576979862174</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7876708419047374</v>
+        <v>0.7964425611091239</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.854520758126928</v>
+        <v>2.938937093052147</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405953</v>
+        <v>3.826684745405955</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.387797855511923</v>
+        <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.76603177269332</v>
+        <v>-2.563642543440978</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.281028722120847</v>
+        <v>1.441137717224372</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8318736789906378</v>
+        <v>0.8406453981950244</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.886922062906305</v>
+        <v>2.971338397831525</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265639</v>
+        <v>3.838199629265641</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.38620785598117</v>
+        <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.803010800356764</v>
+        <v>-2.600621571104421</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.264647111524718</v>
+        <v>1.424756106628242</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8688475807819683</v>
+        <v>0.8776192999863549</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.907516404450352</v>
+        <v>2.991932739375571</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284875</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.43745562116421</v>
+        <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.644719382817491</v>
+        <v>-2.442330153565149</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.379211443723466</v>
+        <v>1.53932043882699</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8688475807819683</v>
+        <v>0.8776192999863549</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.958764169633391</v>
+        <v>3.04318050455861</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321015</v>
+        <v>3.865338681321017</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.435896325758463</v>
+        <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.437077379183015</v>
+        <v>-2.234688149930673</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.46070894977151</v>
+        <v>1.620817944875034</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.076489584416445</v>
+        <v>1.085261303620831</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.08179007640833</v>
+        <v>3.166206411333549</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475131</v>
+        <v>3.864489842475133</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.430844553996733</v>
+        <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.386045286460487</v>
+        <v>-2.183656057208144</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.476070015098791</v>
+        <v>1.636179010202315</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.127521677138973</v>
+        <v>1.136293396343359</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.107357560280117</v>
+        <v>3.191773895205336</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404846</v>
+        <v>3.842547360404848</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.448031958089438</v>
+        <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.320821105333281</v>
+        <v>-2.118431876080939</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.519347091642378</v>
+        <v>1.679456086745903</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.192745858266178</v>
+        <v>1.201517577470565</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.163679473049145</v>
+        <v>3.248095807974364</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882551</v>
+        <v>3.840061186882552</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.443992930388718</v>
+        <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.283394085262147</v>
+        <v>-2.081004856009805</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.530278871970112</v>
+        <v>1.690387867073636</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.19799739629536</v>
+        <v>1.206769115499747</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.162791368165935</v>
+        <v>3.247207703091154</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992655</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.445249722719959</v>
+        <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.303505741296856</v>
+        <v>-2.101116512044513</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.523491001887469</v>
+        <v>1.683599996990993</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.209024741292779</v>
+        <v>1.217796460497166</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.170664567495626</v>
+        <v>3.255080902420846</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563628</v>
+        <v>3.828661445636282</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.605807493741169</v>
+        <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.249760926869651</v>
+        <v>-2.047371697617308</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.705546698679562</v>
+        <v>1.865655693783086</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.219088050733241</v>
+        <v>1.227859769937628</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.337260324181115</v>
+        <v>3.421676659106334</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957618</v>
+        <v>3.81322282095762</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.725920402958987</v>
+        <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.174978665844638</v>
+        <v>-1.972589436592296</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.855572512307384</v>
+        <v>2.015681507410908</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.293870311758254</v>
+        <v>1.302642030962641</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.502242590013939</v>
+        <v>3.586658924939158</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998748</v>
+        <v>3.81423072799875</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.717628378972845</v>
+        <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.14889458158083</v>
+        <v>-1.946505352328488</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.857714122026766</v>
+        <v>2.01782311713029</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.293870311758254</v>
+        <v>1.302642030962641</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.493950566027798</v>
+        <v>3.578366900953017</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896921</v>
+        <v>3.803397818896922</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.715821574556625</v>
+        <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.070763400731884</v>
+        <v>-1.868374171479541</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.887159789950124</v>
+        <v>2.047268785053649</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.368047122641939</v>
+        <v>1.376818841846325</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.536649848141789</v>
+        <v>3.621066183067008</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79626414395985</v>
+        <v>3.796264143959851</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.733375980283416</v>
+        <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.061870939338601</v>
+        <v>-1.859481710086258</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.908271180234229</v>
+        <v>2.068380175337753</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.368047122641939</v>
+        <v>1.376818841846325</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.55420425386858</v>
+        <v>3.638620588793799</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.79442494194536</v>
+        <v>3.794424941945361</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.725231027688</v>
+        <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.230347056308478</v>
+        <v>-2.027957827056136</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.832735780850862</v>
+        <v>1.992844775954386</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.340099286925358</v>
+        <v>1.348871006129744</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.529290599843215</v>
+        <v>3.613706934768435</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782701</v>
+        <v>3.795574066782702</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.706500724875862</v>
+        <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.532547527446895</v>
+        <v>-1.330158298194553</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.093125289583357</v>
+        <v>2.253234284686881</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.269751227554947</v>
+        <v>1.278522946759334</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.46835146140883</v>
+        <v>3.55276779633405</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.78467134563263</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.697164747372767</v>
+        <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.509826423763743</v>
+        <v>-1.3074371945114</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.092877753553522</v>
+        <v>2.252986748657047</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.269751227554947</v>
+        <v>1.278522946759334</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.459015483905735</v>
+        <v>3.543431818830955</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777666</v>
+        <v>3.783205696777667</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.856070873223936</v>
+        <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.508101380473699</v>
+        <v>-1.305712151221356</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.252473896720709</v>
+        <v>2.412582891824233</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.271476270844991</v>
+        <v>1.280247990049378</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.61895663573093</v>
+        <v>3.70337297065615</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644406</v>
+        <v>3.779933725644407</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.893148695717582</v>
+        <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.662882387251954</v>
+        <v>-1.460493157999612</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.227639316503053</v>
+        <v>2.387748311606578</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.238108596790515</v>
+        <v>1.246880315994901</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.636013853791892</v>
+        <v>3.720430188717111</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799957</v>
+        <v>3.769443619799958</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.889824051707127</v>
+        <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.65582769703678</v>
+        <v>-1.453438467784438</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.227136548578668</v>
+        <v>2.387245543682192</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.245163287005689</v>
+        <v>1.253935006210075</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.636922023910541</v>
+        <v>3.72133835883576</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633111</v>
+        <v>3.766673496331111</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.899830205351869</v>
+        <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.628876472710292</v>
+        <v>-1.42648724345795</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.247923191954005</v>
+        <v>2.408032187057529</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.260043633033408</v>
+        <v>1.268815352237794</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.655856385171914</v>
+        <v>3.740272720097133</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784101</v>
+        <v>3.768052067784102</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.083933337496829</v>
+        <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.764829480766609</v>
+        <v>-1.562440251514266</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.377645120876438</v>
+        <v>2.537754115979963</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.260043633033408</v>
+        <v>1.268815352237794</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.839959517316874</v>
+        <v>3.924375852242093</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714419</v>
+        <v>3.74392550571442</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.076050032399822</v>
+        <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.787237598571481</v>
+        <v>-1.584848369319138</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.360798568657482</v>
+        <v>2.520907563761007</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.260043633033408</v>
+        <v>1.268815352237794</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.832076212219867</v>
+        <v>3.916492547145086</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155026</v>
+        <v>3.719118627155027</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.078104031949459</v>
+        <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.93524336605088</v>
+        <v>-1.732854136798537</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.30365026121536</v>
+        <v>2.463759256318884</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.173316624169866</v>
+        <v>1.268815352237794</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.782094006451379</v>
+        <v>3.918546546694723</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161972</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.134357749671306</v>
+        <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.94468429193941</v>
+        <v>-1.742295062687067</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.356127608581795</v>
+        <v>2.51623660368532</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.295743741713258</v>
+        <v>1.391242469781186</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.911803994699262</v>
+        <v>4.048256534942605</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.714941193321629</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.137248844216607</v>
+        <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.996957899275051</v>
+        <v>-1.794568670022708</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.33810926019284</v>
+        <v>2.498218255296364</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.243470134377616</v>
+        <v>1.338968862445544</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.883330924843178</v>
+        <v>4.019783465086522</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347696</v>
+        <v>3.727898186347698</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.135360657110382</v>
+        <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.073287876875957</v>
+        <v>-1.870898647623614</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.305689082046253</v>
+        <v>2.465798077149777</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.243470134377616</v>
+        <v>1.338968862445544</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.881442737736953</v>
+        <v>4.017895277980297</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488774</v>
+        <v>3.710654104887742</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.130180886713245</v>
+        <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.185044829491258</v>
+        <v>-1.982655600238916</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.255806530602994</v>
+        <v>2.415915525706519</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.131713181762315</v>
+        <v>1.227211909830243</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.809208795770634</v>
+        <v>3.945661336013979</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343058</v>
+        <v>3.71289761234306</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.128614896923397</v>
+        <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.183203810433007</v>
+        <v>-1.980814581180664</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.254976948436447</v>
+        <v>2.415085943539971</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.132981408433784</v>
+        <v>1.228480136501712</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.808403741983668</v>
+        <v>3.944856282227011</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647098</v>
+        <v>3.7549119076471</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.141688303789316</v>
+        <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.31550510253056</v>
+        <v>-2.113115873278217</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.215129838463345</v>
+        <v>2.375238833566869</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.132981408433784</v>
+        <v>1.228480136501712</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.821477148849586</v>
+        <v>3.95792968909293</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763524</v>
+        <v>3.749896851763527</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.141688303789316</v>
+        <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.31706674534542</v>
+        <v>-2.114677516093077</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.214505181337401</v>
+        <v>2.374614176440925</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.132981408433784</v>
+        <v>1.228480136501712</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.821477148849586</v>
+        <v>3.95792968909293</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392108</v>
+        <v>3.71583405539211</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.140212344916318</v>
+        <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.344967532454893</v>
+        <v>-2.14257830320255</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.201868907620613</v>
+        <v>2.361977902724138</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.098384484290849</v>
+        <v>1.193883212358777</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.799243035490827</v>
+        <v>3.935695575734171</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172519</v>
+        <v>3.684909939172521</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.136976788893516</v>
+        <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.348000529967567</v>
+        <v>-2.145611300715224</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.197420152592743</v>
+        <v>2.357529147696267</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.095351486778175</v>
+        <v>1.190850214846103</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.794187680960422</v>
+        <v>3.930640221203766</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971072</v>
+        <v>3.619362241971074</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.20368274848402</v>
+        <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.368061851244073</v>
+        <v>-2.165672621991731</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.256101583672644</v>
+        <v>2.416210578776168</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.075290165501668</v>
+        <v>1.170788893569596</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.848856847785021</v>
+        <v>3.985309388028365</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199798</v>
+        <v>3.6407642481998</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.343994467485867</v>
+        <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.624782669238897</v>
+        <v>-2.422393439986555</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.293724975476561</v>
+        <v>2.453833970580086</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.9668755913578532</v>
+        <v>1.062374319425781</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.92411982230058</v>
+        <v>4.060572362543923</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622229</v>
+        <v>3.668303164622231</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.412974736631507</v>
+        <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.778769087015038</v>
+        <v>-2.576379857762695</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.301110677511745</v>
+        <v>2.461219672615269</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.9668755913578532</v>
+        <v>1.062374319425781</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.99310009144622</v>
+        <v>4.129552631689563</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808522</v>
+        <v>3.619937176808524</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.399025938751628</v>
+        <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.728247183187372</v>
+        <v>-2.525857953935029</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.307370641162932</v>
+        <v>2.467479636266456</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.9668755913578532</v>
+        <v>1.062374319425781</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.97915129356634</v>
+        <v>4.115603833809685</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994887</v>
+        <v>3.656346893994888</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.410896427807042</v>
+        <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.980722337195097</v>
+        <v>-2.778333107942754</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.218251068615256</v>
+        <v>2.37836006371878</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.9668755913578532</v>
+        <v>1.062374319425781</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.991021782621754</v>
+        <v>4.127474322865099</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67404269635829</v>
+        <v>3.674042696358292</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.412106962325986</v>
+        <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.250195139116805</v>
+        <v>-3.047805909864462</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.111672482365516</v>
+        <v>2.271781477469041</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.9668755913578532</v>
+        <v>1.062374319425781</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.992232317140698</v>
+        <v>4.128684857384042</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637079</v>
+        <v>3.663523617637081</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.416228704553307</v>
+        <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.407739210846246</v>
+        <v>-3.205349981593903</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.052776595901062</v>
+        <v>2.212885591004586</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.8999737862175787</v>
+        <v>0.9954725142855065</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.956212976283854</v>
+        <v>4.092665516527198</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301336</v>
+        <v>3.652163313301338</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.411306557289496</v>
+        <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.536589761548293</v>
+        <v>-3.33420053229595</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.996314228356432</v>
+        <v>2.156423223459957</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.8589803773668572</v>
+        <v>0.954479105434785</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.926694783709611</v>
+        <v>4.063147323952955</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215462</v>
+        <v>3.667976467215464</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.573510613988541</v>
+        <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.653557454187184</v>
+        <v>-3.451168224934841</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.11173120799992</v>
+        <v>2.271840203103444</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.8589803773668572</v>
+        <v>0.954479105434785</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.088898840408655</v>
+        <v>4.225351380652</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456685</v>
+        <v>3.696553628456686</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.568357251952355</v>
+        <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.738275396408137</v>
+        <v>-3.535886167155795</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.072690669075353</v>
+        <v>2.232799664178877</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.7738643484388108</v>
+        <v>0.8693630765067386</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.032675861015641</v>
+        <v>4.169128401258986</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253281</v>
+        <v>3.750058176253282</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.578586669520846</v>
+        <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.820210214677021</v>
+        <v>-3.617820985424678</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.05014615933629</v>
+        <v>2.210255154439815</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.7639296028517306</v>
+        <v>0.8594283309196584</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.036944431231884</v>
+        <v>4.173396971475229</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717825</v>
+        <v>3.783647027717826</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.587512307976748</v>
+        <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.766472041276759</v>
+        <v>-3.564082812024416</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.080567067152297</v>
+        <v>2.240676062255822</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.8176677762519927</v>
+        <v>0.9131665043199205</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.078112973727944</v>
+        <v>4.214565513971288</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616941</v>
+        <v>3.798310944616943</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.579665195220924</v>
+        <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.656465757799537</v>
+        <v>-3.454076528547194</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.116722467787362</v>
+        <v>2.276831462890886</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.8408723481692679</v>
+        <v>0.9363710762371957</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.084188604122485</v>
+        <v>4.220641144365828</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.723705980297934</v>
+        <v>3.785578085203658</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.583915205942898</v>
+        <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.513406182058611</v>
+        <v>-3.311016952806269</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.178196308805706</v>
+        <v>2.338305303909231</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.8488857747592472</v>
+        <v>0.944384502827175</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.093246670798447</v>
+        <v>4.22969921104179</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.847209947979509</v>
+        <v>3.795385980328755</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.670335080891064</v>
+        <v>3.723832922524505</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.513406182058611</v>
+        <v>-3.311016952806269</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.178196308805706</v>
+        <v>2.338305303909231</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.8488857747592472</v>
+        <v>0.944384502827175</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.663398877877432</v>
+        <v>3.716896719510872</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240718.xlsx
+++ b/tame_output/ON/bt/strategyON_20240718.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>61.2%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -638,7 +638,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>51.5%</t>
+          <t>57.8%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.7%</t>
+          <t>81.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.5%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.8%</t>
+          <t>59.3%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-71.5%</t>
+          <t>-72.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.3%</t>
+          <t>111.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.3%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>121.8%</t>
+          <t>122.4%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>100.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-48.7%</t>
+          <t>-47.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-66.4%</t>
+          <t>-67.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.6%</t>
+          <t>92.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>458.1%</t>
+          <t>456.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-8.0%</t>
+          <t>-9.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-492.7%</t>
+          <t>-508.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.4%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.8%</t>
+          <t>51.9%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.1%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1140,22 +1140,22 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>-7.2%</t>
+          <t>-7.1%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-2.9%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>13.2%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-33.4%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>25.3%</t>
+          <t>23.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>162.9%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-10.7%</t>
+          <t>-11.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-142.4%</t>
+          <t>-148.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-11.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,12 +1242,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-0.17</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>54.8%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>63.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>11.2%</t>
+          <t>10.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-27.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>0.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>28.7%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-135.1%</t>
+          <t>-134.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-129.6%</t>
+          <t>-152.7%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>61.6%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>1.14</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.0%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>70.1%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.4%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.9%</t>
+          <t>11.7%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-23.5%</t>
+          <t>-22.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>46.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.8%</t>
+          <t>-17.6%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>33.6%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-74.3%</t>
+          <t>-75.8%</t>
         </is>
       </c>
     </row>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355688</v>
+        <v>3.311888301355687</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279812</v>
+        <v>3.385382209279811</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386092</v>
+        <v>3.376932391386091</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43888,7 +43888,7 @@
         <v>45303</v>
       </c>
       <c r="B1841" t="n">
-        <v>3.299560092082122</v>
+        <v>3.299560092082123</v>
       </c>
       <c r="C1841" t="n">
         <v>3.13483507841956</v>
@@ -43911,7 +43911,7 @@
         <v>45304</v>
       </c>
       <c r="B1842" t="n">
-        <v>3.29349053375792</v>
+        <v>3.293490533757921</v>
       </c>
       <c r="C1842" t="n">
         <v>3.13585268755003</v>
@@ -43934,7 +43934,7 @@
         <v>45305</v>
       </c>
       <c r="B1843" t="n">
-        <v>3.293766719760738</v>
+        <v>3.293766719760739</v>
       </c>
       <c r="C1843" t="n">
         <v>3.126480719537785</v>
@@ -44003,7 +44003,7 @@
         <v>45308</v>
       </c>
       <c r="B1846" t="n">
-        <v>3.295507330201485</v>
+        <v>3.295507330201486</v>
       </c>
       <c r="C1846" t="n">
         <v>3.119153558445966</v>
@@ -44026,7 +44026,7 @@
         <v>45309</v>
       </c>
       <c r="B1847" t="n">
-        <v>3.258791981153004</v>
+        <v>3.258791981153005</v>
       </c>
       <c r="C1847" t="n">
         <v>3.117080449951029</v>
@@ -44049,7 +44049,7 @@
         <v>45310</v>
       </c>
       <c r="B1848" t="n">
-        <v>3.271168579537424</v>
+        <v>3.271168579537425</v>
       </c>
       <c r="C1848" t="n">
         <v>3.116946666549951</v>
@@ -44072,7 +44072,7 @@
         <v>45311</v>
       </c>
       <c r="B1849" t="n">
-        <v>3.272760131382189</v>
+        <v>3.27276013138219</v>
       </c>
       <c r="C1849" t="n">
         <v>3.121838811103876</v>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.25147557607462</v>
+        <v>3.251475576074621</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911638</v>
+        <v>3.233800325911639</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213494</v>
+        <v>3.223539378213495</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416044</v>
+        <v>3.231167537416045</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382328</v>
+        <v>3.235981977382329</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347053</v>
+        <v>3.299136146347054</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130015</v>
+        <v>3.287377576130016</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178241</v>
+        <v>3.315884374178242</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207809</v>
+        <v>3.30531679820781</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.284619513310978</v>
+        <v>3.284619513310979</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006529</v>
+        <v>3.30584953900653</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.31108639130942</v>
+        <v>3.311086391309421</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970901</v>
+        <v>3.304715716970902</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330518</v>
+        <v>3.300815818330519</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191732</v>
+        <v>3.302618194191733</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108634</v>
+        <v>3.305023265108635</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097816</v>
+        <v>3.341378723097817</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094111</v>
+        <v>3.374439043094112</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969588</v>
+        <v>3.424633354969589</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923081</v>
+        <v>3.419979433923082</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317611</v>
+        <v>3.447750501317612</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737165</v>
+        <v>3.503515506737166</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341308</v>
+        <v>3.503170282341309</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.501052558539459</v>
+        <v>3.50105255853946</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492448711937497</v>
+        <v>3.492448711937498</v>
       </c>
       <c r="C1877" t="n">
         <v>3.134806895136605</v>
@@ -44745,16 +44745,16 @@
         <v>3.140320092255247</v>
       </c>
       <c r="D1878" t="n">
-        <v>-8.617334066908747</v>
+        <v>-8.680018109329392</v>
       </c>
       <c r="E1878" t="n">
-        <v>-0.3069699588219992</v>
+        <v>-0.3320435757902573</v>
       </c>
       <c r="F1878" t="n">
-        <v>-1.483678187732079</v>
+        <v>-1.492449906936466</v>
       </c>
       <c r="G1878" t="n">
-        <v>2.250113179616</v>
+        <v>2.244850148093368</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.144802646739683</v>
       </c>
       <c r="D1879" t="n">
-        <v>-8.65098690541722</v>
+        <v>-8.713670947837866</v>
       </c>
       <c r="E1879" t="n">
-        <v>-0.3159485397409525</v>
+        <v>-0.3410221567092107</v>
       </c>
       <c r="F1879" t="n">
-        <v>-1.584091555649117</v>
+        <v>-1.592863274853503</v>
       </c>
       <c r="G1879" t="n">
-        <v>2.194347713350213</v>
+        <v>2.189084681827581</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.577517073749771</v>
+        <v>-8.640201116170417</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.2711889055805514</v>
+        <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.510621723981668</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.253801313844103</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608599</v>
+        <v>3.490059241608598</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.752641491136314</v>
+        <v>-8.81532553355696</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3266834517876522</v>
+        <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.685746141368212</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.163281884159694</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-8.987093585150804</v>
+        <v>-9.04977762757145</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4276834542950438</v>
+        <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.685746141368212</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.156062719258098</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.09146831617725</v>
+        <v>-9.154152358597896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.4761055374795986</v>
+        <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.790120872394658</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.086765689868254</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.144254471777577</v>
+        <v>-9.206938514198223</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.4961042098811732</v>
+        <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.885796358977055</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.030476187757372</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492101641297397</v>
+        <v>3.492101641297398</v>
       </c>
       <c r="C1885" t="n">
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.270291265145866</v>
+        <v>-9.332975307566512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5438251985993743</v>
+        <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.860544736167313</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.048320890072333</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573674025322541</v>
+        <v>3.573674025322542</v>
       </c>
       <c r="C1886" t="n">
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.213219493249936</v>
+        <v>-9.275903535670581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5170061541546009</v>
+        <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.860544736167313</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.052311225758733</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600038265158919</v>
+        <v>3.60003826515892</v>
       </c>
       <c r="C1887" t="n">
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.354891334974056</v>
+        <v>-9.417575377394702</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.5751501177429907</v>
+        <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.860544736167313</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.050835998859991</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691571733940716</v>
+        <v>3.691571733940717</v>
       </c>
       <c r="C1888" t="n">
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.305300490549222</v>
+        <v>-9.367984532969867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5402603698081849</v>
+        <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.810953891742479</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.095643915679764</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.156382156077365</v>
+        <v>-9.219066198498011</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.4937441696661251</v>
+        <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.779704301007306</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.101342536474185</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.930537003357955</v>
+        <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.3938270355421527</v>
+        <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.737777625420142</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.136077614862692</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684843823812101</v>
+        <v>3.684843823812102</v>
       </c>
       <c r="C1891" t="n">
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.805958347020363</v>
+        <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3428564284510567</v>
+        <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.737777625420142</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.137216759418751</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710935533646214</v>
+        <v>3.710935533646216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.85885363506465</v>
+        <v>-8.921537677485295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3613807695066638</v>
+        <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.732822279331696</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.142823741233926</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768951674611565</v>
+        <v>3.768951674611567</v>
       </c>
       <c r="C1893" t="n">
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.786720459776769</v>
+        <v>-8.849404502197414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.326793795152875</v>
+        <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.732822279331696</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.148557445472562</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728577929955324</v>
+        <v>3.728577929955326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.715354067167121</v>
+        <v>-8.778038109587767</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3079845005028812</v>
+        <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.661455886722048</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.181640018644486</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747702660232409</v>
+        <v>3.74770266023241</v>
       </c>
       <c r="C1895" t="n">
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.621895033181897</v>
+        <v>-8.684579075602542</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.2804843682216989</v>
+        <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.661455886722048</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.171756537331579</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766317079436225</v>
+        <v>3.766317079436226</v>
       </c>
       <c r="C1896" t="n">
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.354653232313499</v>
+        <v>-8.417337274734145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.1754222083737136</v>
+        <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.661455886722048</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.169921976832205</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784684521311944</v>
+        <v>3.784684521311946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.256746193637008</v>
+        <v>-8.319430236057654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1365597078765783</v>
+        <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.593470136861492</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.210413111775078</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800829354097239</v>
+        <v>3.800829354097241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.23279265266105</v>
+        <v>-8.295476695081696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1263097853407014</v>
+        <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.569516595885534</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.225453742506146</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789311112017767</v>
+        <v>3.789311112017769</v>
       </c>
       <c r="C1899" t="n">
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-7.968732714338254</v>
+        <v>-8.031416756758899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.03394612617333514</v>
+        <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.305456657562738</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.370629389338072</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45245,22 +45245,22 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833252747839721</v>
+        <v>3.833252747839722</v>
       </c>
       <c r="C1900" t="n">
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.261653090833416</v>
+        <v>-7.324337133254061</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2460986895682993</v>
+        <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.305456657562738</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.367842355677771</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45268,22 +45268,22 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839374447388724</v>
+        <v>3.839374447388725</v>
       </c>
       <c r="C1901" t="n">
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.221468792467226</v>
+        <v>-7.284152834887871</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2625160328026168</v>
+        <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.265272359196547</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.392296558585326</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45291,22 +45291,22 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.85616175162647</v>
+        <v>3.856161751626471</v>
       </c>
       <c r="C1902" t="n">
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.058068921527863</v>
+        <v>-7.120752963948508</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.3272428023991187</v>
+        <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.101872488257185</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.489703302369701</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45314,22 +45314,22 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.78733042929181</v>
+        <v>3.787330429291812</v>
       </c>
       <c r="C1903" t="n">
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.824587699298265</v>
+        <v>-6.88727174171891</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4285597201288107</v>
+        <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8683912660275861</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.637716464545313</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.67492130829075</v>
+        <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4855340662188574</v>
+        <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7754877747850502</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.690566348977875</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.542645834659863</v>
+        <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5338117424182389</v>
+        <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6432123011541635</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.765299119903434</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45383,22 +45383,22 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.78471879410595</v>
+        <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
         <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.386907502100121</v>
+        <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5989221361297723</v>
+        <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4874739685944219</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.861557180126916</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45406,22 +45406,22 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753882571960984</v>
+        <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
         <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.13790770341654</v>
+        <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.7114283968268635</v>
+        <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4874739685944219</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.874463521350574</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692931855607642</v>
+        <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
         <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.243497693189645</v>
+        <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5412164713184033</v>
+        <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.5930639583675263</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.683133597887493</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45452,22 +45452,22 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770422583987902</v>
+        <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
         <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.262232595308242</v>
+        <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5822668523480505</v>
+        <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.5986599680276576</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.7283203339685</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45475,22 +45475,22 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760333686710812</v>
+        <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
         <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.114292553900643</v>
+        <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.5215639462229227</v>
+        <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5783390521191001</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.620633960825467</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.061323031646654</v>
+        <v>-6.201259613402452</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.5340377688710403</v>
+        <v>0.4780631361687209</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.5253695298651112</v>
+        <v>-0.6113937884046511</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.643701687924382</v>
+        <v>2.592087132800659</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.017774624875964</v>
+        <v>-6.157711206631761</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.5444965194842233</v>
+        <v>0.4885218867819039</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.5253695298651112</v>
+        <v>-0.6113937884046511</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.636741075829289</v>
+        <v>2.585126520705566</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.78292253349342</v>
+        <v>3.782922533493419</v>
       </c>
       <c r="C1913" t="n">
         <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.775626231422105</v>
+        <v>-5.915562813177903</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.6558182312469096</v>
+        <v>0.5998435985445902</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.5253695298651112</v>
+        <v>-0.6113937884046511</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.651203430210432</v>
+        <v>2.599588875086709</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722817</v>
+        <v>3.828551486722816</v>
       </c>
       <c r="C1914" t="n">
         <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.667367094299584</v>
+        <v>-5.807303676055382</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6936540065551133</v>
+        <v>0.6376793738527939</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.5253695298651112</v>
+        <v>-0.6113937884046511</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.645735550669627</v>
+        <v>2.594120995545904</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.544075959482453</v>
+        <v>-5.684012541238251</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.7404685544925425</v>
+        <v>0.6844939217902235</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4020783950479807</v>
+        <v>-0.4881026535875206</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.717208325570483</v>
+        <v>2.665593770446759</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.52292676057901</v>
+        <v>-5.662863342334807</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.7566292122912448</v>
+        <v>0.7006545795889259</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.3809291961445374</v>
+        <v>-0.4669534546840772</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.737598823149874</v>
+        <v>2.68598426802615</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.279161318595565</v>
+        <v>-5.419097900351363</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.8499160974316733</v>
+        <v>0.7939414647293543</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.3809291961445374</v>
+        <v>-0.4669534546840772</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.733379531496924</v>
+        <v>2.681764976373201</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.17739849831827</v>
+        <v>-5.317335080074068</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8927455394626072</v>
+        <v>0.8367709067602882</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.3677101277521087</v>
+        <v>-0.4537343862916485</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.743435286452398</v>
+        <v>2.691820731328674</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-4.927548104369196</v>
+        <v>-5.067484686124994</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9854277720259392</v>
+        <v>0.9294531393236203</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.3677101277521087</v>
+        <v>-0.4537343862916485</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.7361773614361</v>
+        <v>2.684562806312376</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.751656011901764</v>
+        <v>-4.891592593657561</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.059383732533561</v>
+        <v>1.003409099831242</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.3677101277521087</v>
+        <v>-0.4537343862916485</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.739776484956749</v>
+        <v>2.688161929833025</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.5802095488793</v>
+        <v>-4.720146130635098</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.1412898237971</v>
+        <v>1.085315191094781</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.1962636647296455</v>
+        <v>-0.2822879232691854</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.85597186882478</v>
+        <v>2.804357313701056</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.505919983140961</v>
+        <v>-4.645856564896759</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.170026127708732</v>
+        <v>1.114051495006414</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.1219740989913062</v>
+        <v>-0.2079983575308461</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.899566085884081</v>
+        <v>2.847951530760357</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.442284240907027</v>
+        <v>-4.582220822662824</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.200175225656624</v>
+        <v>1.144200592954304</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.0583383567573717</v>
+        <v>-0.1443626152969116</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.942442332278759</v>
+        <v>2.890827777155035</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.330857481581107</v>
+        <v>-4.470794063336904</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.225940188170787</v>
+        <v>1.169965555468468</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.0583383567573717</v>
+        <v>-0.1443626152969116</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.923636591062555</v>
+        <v>2.87202203593883</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.090426984776246</v>
+        <v>-4.230363566532044</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.323855463517609</v>
+        <v>1.26788083081529</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.1820921400474886</v>
+        <v>0.0960678815079487</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.069637965770348</v>
+        <v>3.018023410646624</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.018184416605052</v>
+        <v>-4.158120998360849</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.356681804620907</v>
+        <v>1.300707171918588</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.1820921400474886</v>
+        <v>0.0960678815079487</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.073567279605168</v>
+        <v>3.021952724481444</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-3.965186094323663</v>
+        <v>-4.105122676079461</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.378559717450802</v>
+        <v>1.322585084748483</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.2374283990494274</v>
+        <v>0.1514041405098875</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.107447618923671</v>
+        <v>3.055833063799948</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.856381208843937</v>
+        <v>-3.996317790599735</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.419079742862686</v>
+        <v>1.363105110160367</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.2374283990494274</v>
+        <v>0.1514041405098875</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.104445690143665</v>
+        <v>3.052831135019941</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.636360410806926</v>
+        <v>-3.776296992562724</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.508667099088105</v>
+        <v>1.452692466385786</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.3786482441174077</v>
+        <v>0.2926239855778678</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.190756634195067</v>
+        <v>3.139142079071343</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.503492721743648</v>
+        <v>-3.643429303499446</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.57770835751524</v>
+        <v>1.52173372481292</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.3786482441174077</v>
+        <v>0.2926239855778678</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.20665081699689</v>
+        <v>3.155036261873167</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496258</v>
+        <v>3.845047386496257</v>
       </c>
       <c r="C1931" t="n">
         <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.383319638379149</v>
+        <v>-3.523256220134947</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.626923435301341</v>
+        <v>1.570948802599022</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4988213274819067</v>
+        <v>0.4127970689423667</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.279900511455892</v>
+        <v>3.228285956332168</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576995</v>
+        <v>3.791273551576993</v>
       </c>
       <c r="C1932" t="n">
         <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.238647493279411</v>
+        <v>-3.378584075035209</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.694880395902676</v>
+        <v>1.638905763200357</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.6434934725816441</v>
+        <v>0.5574692140421041</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.376791901077174</v>
+        <v>3.32517734595345</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.7358392229421</v>
+        <v>3.735839222942099</v>
       </c>
       <c r="C1933" t="n">
         <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.298522320637104</v>
+        <v>-3.438458902392902</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.656967956361024</v>
+        <v>1.600993323658706</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.583618645223952</v>
+        <v>0.497594386684412</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.326904496063985</v>
+        <v>3.275289940940261</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674512</v>
+        <v>3.762647477674511</v>
       </c>
       <c r="C1934" t="n">
         <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.178702089726266</v>
+        <v>-3.318638671482064</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.720185217959568</v>
+        <v>1.664210585257249</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.583618645223952</v>
+        <v>0.497594386684412</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.342193665298193</v>
+        <v>3.290579110174469</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.72914639843069</v>
+        <v>3.729146398430689</v>
       </c>
       <c r="C1935" t="n">
         <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.181171796188072</v>
+        <v>-3.32110837794387</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.626841534697287</v>
+        <v>1.570866901994968</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.5811489387621458</v>
+        <v>0.4951246802226059</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.248356040743551</v>
+        <v>3.196741485619827</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.7432201960036</v>
+        <v>3.743220196003598</v>
       </c>
       <c r="C1936" t="n">
         <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.249541982512082</v>
+        <v>-3.38947856426788</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.518755321652985</v>
+        <v>1.462780688950666</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5904246377983607</v>
+        <v>0.5044003792588209</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.173183321650582</v>
+        <v>3.121568766526857</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508367</v>
+        <v>3.714179139508365</v>
       </c>
       <c r="C1937" t="n">
         <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.263330035359129</v>
+        <v>-3.403266617114927</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.503676809146057</v>
+        <v>1.447702176443738</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5904246377983607</v>
+        <v>0.5044003792588209</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.163620030282473</v>
+        <v>3.112005475158749</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417701</v>
+        <v>3.710906731417699</v>
       </c>
       <c r="C1938" t="n">
         <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.294323194687834</v>
+        <v>-3.434259776443632</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.315989110454962</v>
+        <v>1.260014477752643</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5904246377983607</v>
+        <v>0.5044003792588209</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.98832959532286</v>
+        <v>2.936715040199136</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205896</v>
+        <v>3.746042526205894</v>
       </c>
       <c r="C1939" t="n">
         <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.118848934895365</v>
+        <v>-3.258785516651163</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.390746046363737</v>
+        <v>1.334771413661418</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5904246377983607</v>
+        <v>0.5044003792588209</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.992896827314647</v>
+        <v>2.941282272190923</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225441</v>
+        <v>3.765024323225439</v>
       </c>
       <c r="C1940" t="n">
         <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.229785187536613</v>
+        <v>-3.369721769292411</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.322113574068445</v>
+        <v>1.266138941366126</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5904246377983607</v>
+        <v>0.5044003792588209</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.968638856075855</v>
+        <v>2.91702430095213</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111294</v>
+        <v>3.773210297111291</v>
       </c>
       <c r="C1941" t="n">
         <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.196121642064332</v>
+        <v>-3.33605822382013</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.264117305658808</v>
+        <v>1.208142672956488</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.6240881832706426</v>
+        <v>0.5380639247311028</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.917375296760673</v>
+        <v>2.865760741636949</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264162</v>
+        <v>3.784343952264161</v>
       </c>
       <c r="C1942" t="n">
         <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.136269022860608</v>
+        <v>-3.372341929504335</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.298230739772429</v>
+        <v>1.203801577114939</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.6240881832706426</v>
+        <v>0.5380639247311028</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.927547683192806</v>
+        <v>2.875933128069082</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742299</v>
+        <v>3.786949957742297</v>
       </c>
       <c r="C1943" t="n">
         <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.050025559834231</v>
+        <v>-3.286098466477958</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.32767439555684</v>
+        <v>1.23324523289935</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.6240881832706426</v>
+        <v>0.5380639247311028</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.922493953766666</v>
+        <v>2.870879398642942</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316045</v>
+        <v>3.752027499316043</v>
       </c>
       <c r="C1944" t="n">
         <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.095332379233211</v>
+        <v>-3.331405285876937</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.301327443241774</v>
+        <v>1.206898280584284</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.5832780202614118</v>
+        <v>0.497253761721872</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.889783631405653</v>
+        <v>2.838169076281929</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803189</v>
+        <v>3.753571165803187</v>
       </c>
       <c r="C1945" t="n">
         <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.124365483935513</v>
+        <v>-3.360438390579239</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.290266074393955</v>
+        <v>1.195836911736464</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.5832780202614118</v>
+        <v>0.497253761721872</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.890335504438755</v>
+        <v>2.838720949315031</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809496</v>
+        <v>3.733390600809495</v>
       </c>
       <c r="C1946" t="n">
         <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.031555002484653</v>
+        <v>-3.26762790912838</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.256662958865664</v>
+        <v>1.162233796208174</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.6760885017122712</v>
+        <v>0.5900642431727313</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.875294485200636</v>
+        <v>2.823679930076912</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560423</v>
+        <v>3.748285816560422</v>
       </c>
       <c r="C1947" t="n">
         <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.075944471814081</v>
+        <v>-3.312017378457807</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.240780647058494</v>
+        <v>1.146351484401004</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.6316990323828435</v>
+        <v>0.5456747738433037</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.85053427952758</v>
+        <v>2.798919724403856</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472735</v>
+        <v>3.721077195472734</v>
       </c>
       <c r="C1948" t="n">
         <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-2.963273253577831</v>
+        <v>-3.199346160221557</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.280924842864717</v>
+        <v>1.186495680207227</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.7443702506190937</v>
+        <v>0.6583459920795538</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.913212718981053</v>
+        <v>2.861598163857329</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798534</v>
+        <v>3.743047603798533</v>
       </c>
       <c r="C1949" t="n">
         <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-2.850896252395158</v>
+        <v>-3.086969159038885</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.331366939168454</v>
+        <v>1.236937776510963</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.7443702506190937</v>
+        <v>0.6583459920795538</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.918704014811721</v>
+        <v>2.867089459687997</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.689597840498861</v>
+        <v>3.68959784049886</v>
       </c>
       <c r="C1950" t="n">
         <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-2.878676650296511</v>
+        <v>-3.114749556940238</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.331751981776451</v>
+        <v>1.237322819118961</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.7165898527177406</v>
+        <v>0.6305655941782007</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.913532977839448</v>
+        <v>2.861918422715724</v>
       </c>
     </row>
     <row r="1951">
@@ -46424,16 +46424,16 @@
         <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-2.96167793132179</v>
+        <v>-3.197750837965517</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.136907189366993</v>
+        <v>1.042478026709502</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.6980189681905669</v>
+        <v>0.611994709651027</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.740746167123797</v>
+        <v>2.689131612000073</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729267</v>
+        <v>3.682716310729266</v>
       </c>
       <c r="C1952" t="n">
         <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.070292009765121</v>
+        <v>-3.306364916408848</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.213611218708866</v>
+        <v>1.119182056051376</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.6980189681905669</v>
+        <v>0.611994709651027</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.860895827843002</v>
+        <v>2.809281272719279</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190765</v>
+        <v>3.733012441190764</v>
       </c>
       <c r="C1953" t="n">
         <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.034882971516979</v>
+        <v>-3.270955878160705</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.242287860110446</v>
+        <v>1.147858697452956</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.6980189681905669</v>
+        <v>0.611994709651027</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.875408853945325</v>
+        <v>2.823794298821602</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913423</v>
+        <v>3.741174069913422</v>
       </c>
       <c r="C1954" t="n">
         <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-2.996499308958827</v>
+        <v>-3.232572215602554</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.255060766476076</v>
+        <v>1.160631603818585</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.736402630748718</v>
+        <v>0.6503783722091782</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.895858492822585</v>
+        <v>2.844243937698861</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532482</v>
+        <v>3.751147197532481</v>
       </c>
       <c r="C1955" t="n">
         <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-2.819382978923661</v>
+        <v>-3.055455885567388</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.322636327335444</v>
+        <v>1.228207164677953</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.736402630748718</v>
+        <v>0.6503783722091782</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.892587521667886</v>
+        <v>2.840972966544163</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793899</v>
+        <v>3.741328448793898</v>
       </c>
       <c r="C1956" t="n">
         <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-2.864475223757207</v>
+        <v>-3.100548130400933</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.305282821163939</v>
+        <v>1.210853658506448</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.6745065875793282</v>
+        <v>0.5884823290397884</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.856133287528166</v>
+        <v>2.804518732404442</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.750729377011231</v>
+        <v>3.75072937701123</v>
       </c>
       <c r="C1957" t="n">
         <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.685099802518439</v>
+        <v>-2.921172709162166</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.37081996496586</v>
+        <v>1.276390802308369</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.8312833457500469</v>
+        <v>0.745259087210507</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.943986317737012</v>
+        <v>2.892371762613287</v>
       </c>
     </row>
     <row r="1958">
@@ -46585,16 +46585,16 @@
         <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.730114016039046</v>
+        <v>-2.966186922682772</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.333621734889207</v>
+        <v>1.239192572231717</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.8009344504354423</v>
+        <v>0.7149101918959024</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.906584435879839</v>
+        <v>2.854969880756114</v>
       </c>
     </row>
     <row r="1959">
@@ -46608,16 +46608,16 @@
         <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-2.997118526311481</v>
+        <v>-3.233191432955207</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.232511493119179</v>
+        <v>1.138082330461688</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.6065714123924937</v>
+        <v>0.5205471538529538</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.795658175393015</v>
+        <v>2.744043620269291</v>
       </c>
     </row>
     <row r="1960">
@@ -46631,16 +46631,16 @@
         <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.098316307748654</v>
+        <v>-3.33438921439238</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.191236302440811</v>
+        <v>1.096807139783321</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.5381625988471745</v>
+        <v>0.4521383403076346</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.753816809162325</v>
+        <v>2.702202254038601</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815453</v>
+        <v>3.705571661815452</v>
       </c>
       <c r="C1961" t="n">
         <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.091805341134341</v>
+        <v>-3.327878247778068</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.191440650640853</v>
+        <v>1.097011487983362</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.5381625988471745</v>
+        <v>0.4521383403076346</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.751416770716641</v>
+        <v>2.699802215592918</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378098</v>
+        <v>3.709510443378097</v>
       </c>
       <c r="C1962" t="n">
         <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.072767213427044</v>
+        <v>-3.30884012007077</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.195580620932017</v>
+        <v>1.101151458274526</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.47997898751598</v>
+        <v>0.3939547289764401</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.71303132312617</v>
+        <v>2.661416768002446</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131247</v>
+        <v>3.731064473131246</v>
       </c>
       <c r="C1963" t="n">
         <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.103893844577662</v>
+        <v>-3.339966751221388</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.36071183741045</v>
+        <v>1.26628267475296</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.47997898751598</v>
+        <v>0.3939547289764401</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.89061319206485</v>
+        <v>2.838998636941127</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067863</v>
+        <v>3.722447362067862</v>
       </c>
       <c r="C1964" t="n">
         <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.117760605911579</v>
+        <v>-3.353833512555306</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.355998461863017</v>
+        <v>1.261569299205526</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.4421210707821571</v>
+        <v>0.3560968122426171</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.86873177101069</v>
+        <v>2.817117215886966</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.78742558078912</v>
+        <v>3.787425580789119</v>
       </c>
       <c r="C1965" t="n">
         <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.072956434371649</v>
+        <v>-3.309029341015376</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.379928660875915</v>
+        <v>1.285499498218424</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.4421210707821571</v>
+        <v>0.3560968122426171</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.874740301407616</v>
+        <v>2.823125746283892</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519906</v>
+        <v>3.781501250519904</v>
       </c>
       <c r="C1966" t="n">
         <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-2.925213464136647</v>
+        <v>-3.161286370780374</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.336976070247115</v>
+        <v>1.242546907589624</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.6099284280170403</v>
+        <v>0.5239041694775003</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.873374937025746</v>
+        <v>2.821760381902021</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181167</v>
+        <v>3.802245929181165</v>
       </c>
       <c r="C1967" t="n">
         <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.027228146667868</v>
+        <v>-3.263301053311594</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.298963818766108</v>
+        <v>1.204534656108617</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.6099284280170403</v>
+        <v>0.5239041694775003</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.876168558557227</v>
+        <v>2.824554003433502</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394726</v>
+        <v>3.805608985394724</v>
       </c>
       <c r="C1968" t="n">
         <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.021075440615084</v>
+        <v>-3.25714834725881</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.30208724957888</v>
+        <v>1.207658086921389</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.6160811340698246</v>
+        <v>0.5300568755302846</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.880522530580556</v>
+        <v>2.828907975456831</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890607</v>
+        <v>3.798239794890605</v>
       </c>
       <c r="C1969" t="n">
         <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.037884738765585</v>
+        <v>-3.273957645409312</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.294444007058789</v>
+        <v>1.200014844401299</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.599271835919323</v>
+        <v>0.5132475773797829</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.869517428430365</v>
+        <v>2.817902873306641</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798424</v>
+        <v>3.867362636798422</v>
       </c>
       <c r="C1970" t="n">
         <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-2.975586739989463</v>
+        <v>-3.21165964663319</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.385698760366059</v>
+        <v>1.291269597708568</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.599271835919323</v>
+        <v>0.5132475773797829</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.935852982227185</v>
+        <v>2.884238427103462</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992188</v>
+        <v>3.848729139992186</v>
       </c>
       <c r="C1971" t="n">
         <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-2.773796542324305</v>
+        <v>-3.009869448968032</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.268706841146249</v>
+        <v>1.174277678488759</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7972900280884774</v>
+        <v>0.7112657695489373</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.856955899242805</v>
+        <v>2.805341344119081</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.841444817852421</v>
+        <v>3.84144481785242</v>
       </c>
       <c r="C1972" t="n">
         <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.608983539245458</v>
+        <v>-2.845056445889185</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.404922274699963</v>
+        <v>1.310493112042473</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.9621030311673243</v>
+        <v>0.8760787726277842</v>
       </c>
       <c r="G1972" t="n">
-        <v>3.026133933412289</v>
+        <v>2.974519378288565</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.819063300319542</v>
+        <v>3.81906330031954</v>
       </c>
       <c r="C1973" t="n">
         <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.706724083870433</v>
+        <v>-2.942796990514159</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.380453792966017</v>
+        <v>1.286024630308527</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.9462137530343442</v>
+        <v>0.8601894944948041</v>
       </c>
       <c r="G1973" t="n">
-        <v>3.031228102648544</v>
+        <v>2.97961354752482</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489381</v>
+        <v>3.831819032489379</v>
       </c>
       <c r="C1974" t="n">
         <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-2.883061843993362</v>
+        <v>-3.119134750637088</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.308454669741517</v>
+        <v>1.214025507084027</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.7698759929114147</v>
+        <v>0.6838517343718746</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.923961427399458</v>
+        <v>2.872346872275734</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397791</v>
+        <v>3.836411672397789</v>
       </c>
       <c r="C1975" t="n">
         <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-2.806639797561435</v>
+        <v>-3.042712704205162</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.337515106354217</v>
+        <v>1.243085943696726</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.7698759929114147</v>
+        <v>0.6838517343718746</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.922453045439387</v>
+        <v>2.870838490315663</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316246</v>
+        <v>3.833513460316244</v>
       </c>
       <c r="C1976" t="n">
         <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.762266665922867</v>
+        <v>-2.998339572566593</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.35512722644508</v>
+        <v>1.26069806378759</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.8142491245499833</v>
+        <v>0.7282248660104432</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.948939791857964</v>
+        <v>2.89732523673424</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105963</v>
+        <v>3.821562117105961</v>
       </c>
       <c r="C1977" t="n">
         <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.639432445035699</v>
+        <v>-2.875505351679426</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.398654708938537</v>
+        <v>1.304225546281047</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.8142491245499833</v>
+        <v>0.7282248660104432</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.943333585996555</v>
+        <v>2.891719030872831</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190321</v>
+        <v>3.833011148190319</v>
       </c>
       <c r="C1978" t="n">
         <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.591776714474643</v>
+        <v>-2.82784962111837</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.424098758190764</v>
+        <v>1.329669595533274</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.861904855111039</v>
+        <v>0.7758805965714989</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.978308781360993</v>
+        <v>2.926694226237269</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.822678210569613</v>
+        <v>3.82267821056961</v>
       </c>
       <c r="C1979" t="n">
         <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.491258555975889</v>
+        <v>-2.727331462619615</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.469198394964991</v>
+        <v>1.374769232307501</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.9624230136097935</v>
+        <v>0.8763987550702534</v>
       </c>
       <c r="G1979" t="n">
-        <v>3.04351204983497</v>
+        <v>2.991897494711246</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557289</v>
+        <v>3.828808877557286</v>
       </c>
       <c r="C1980" t="n">
         <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.551925146378278</v>
+        <v>-2.787998053022004</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.431686431279908</v>
+        <v>1.337257268622417</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.8807246968912599</v>
+        <v>0.7947004383517198</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.981247732279722</v>
+        <v>2.929633177155998</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932764</v>
+        <v>3.816837033932762</v>
       </c>
       <c r="C1981" t="n">
         <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.50708674476988</v>
+        <v>-2.743159651413606</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.453719494533896</v>
+        <v>1.359290331876405</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.8852681298361293</v>
+        <v>0.7992438712965892</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.988071494657273</v>
+        <v>2.936456939533548</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917047</v>
+        <v>3.817932354917045</v>
       </c>
       <c r="C1982" t="n">
         <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.607845380526878</v>
+        <v>-2.843918287170605</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.417576979862174</v>
+        <v>1.323147817204684</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7964425611091239</v>
+        <v>0.7104183025695838</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.938937093052147</v>
+        <v>2.887322537928423</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405955</v>
+        <v>3.826684745405953</v>
       </c>
       <c r="C1983" t="n">
         <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.563642543440978</v>
+        <v>-2.799715450084704</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.441137717224372</v>
+        <v>1.346708554566881</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.8406453981950244</v>
+        <v>0.7546211396554843</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.971338397831525</v>
+        <v>2.919723842707801</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265641</v>
+        <v>3.838199629265639</v>
       </c>
       <c r="C1984" t="n">
         <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.600621571104421</v>
+        <v>-2.836694477748147</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.424756106628242</v>
+        <v>1.330326943970751</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.8776192999863549</v>
+        <v>0.7915950414468148</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.991932739375571</v>
+        <v>2.940318184251847</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284875</v>
+        <v>3.863895080284873</v>
       </c>
       <c r="C1985" t="n">
         <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.442330153565149</v>
+        <v>-2.678403060208875</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.53932043882699</v>
+        <v>1.4448912761695</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.8776192999863549</v>
+        <v>0.7915950414468148</v>
       </c>
       <c r="G1985" t="n">
-        <v>3.04318050455861</v>
+        <v>2.991565949434886</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321017</v>
+        <v>3.865338681321015</v>
       </c>
       <c r="C1986" t="n">
         <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.234688149930673</v>
+        <v>-2.470761056574399</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.620817944875034</v>
+        <v>1.526388782217543</v>
       </c>
       <c r="F1986" t="n">
-        <v>1.085261303620831</v>
+        <v>0.9992370450812911</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.166206411333549</v>
+        <v>3.114591856209825</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475133</v>
+        <v>3.864489842475131</v>
       </c>
       <c r="C1987" t="n">
         <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.183656057208144</v>
+        <v>-2.419728963851871</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.636179010202315</v>
+        <v>1.541749847544825</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.136293396343359</v>
+        <v>1.050269137803819</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.191773895205336</v>
+        <v>3.140159340081612</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404848</v>
+        <v>3.842547360404846</v>
       </c>
       <c r="C1988" t="n">
         <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.118431876080939</v>
+        <v>-2.354504782724665</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.679456086745903</v>
+        <v>1.585026924088412</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.201517577470565</v>
+        <v>1.115493318931025</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.248095807974364</v>
+        <v>3.19648125285064</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882552</v>
+        <v>3.840061186882551</v>
       </c>
       <c r="C1989" t="n">
         <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.081004856009805</v>
+        <v>-2.317077762653531</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.690387867073636</v>
+        <v>1.595958704416146</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.206769115499747</v>
+        <v>1.120744856960207</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.247207703091154</v>
+        <v>3.19559314796743</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992655</v>
+        <v>3.845169808992654</v>
       </c>
       <c r="C1990" t="n">
         <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.101116512044513</v>
+        <v>-2.33718941868824</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.683599996990993</v>
+        <v>1.589170834333503</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.217796460497166</v>
+        <v>1.131772201957626</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.255080902420846</v>
+        <v>3.203466347297121</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.828661445636282</v>
+        <v>3.82866144563628</v>
       </c>
       <c r="C1991" t="n">
         <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.047371697617308</v>
+        <v>-2.283444604261035</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.865655693783086</v>
+        <v>1.771226531125595</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.227859769937628</v>
+        <v>1.141835511398088</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.421676659106334</v>
+        <v>3.37006210398261</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.81322282095762</v>
+        <v>3.813222820957618</v>
       </c>
       <c r="C1992" t="n">
         <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-1.972589436592296</v>
+        <v>-2.208662343236022</v>
       </c>
       <c r="E1992" t="n">
-        <v>2.015681507410908</v>
+        <v>1.921252344753418</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.302642030962641</v>
+        <v>1.2166177724231</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.586658924939158</v>
+        <v>3.535044369815434</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.81423072799875</v>
+        <v>3.814230727998748</v>
       </c>
       <c r="C1993" t="n">
         <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-1.946505352328488</v>
+        <v>-2.182578258972214</v>
       </c>
       <c r="E1993" t="n">
-        <v>2.01782311713029</v>
+        <v>1.9233939544728</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.302642030962641</v>
+        <v>1.2166177724231</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.578366900953017</v>
+        <v>3.526752345829293</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.803397818896922</v>
+        <v>3.80339781889692</v>
       </c>
       <c r="C1994" t="n">
         <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-1.868374171479541</v>
+        <v>-2.36247397184413</v>
       </c>
       <c r="E1994" t="n">
-        <v>2.047268785053649</v>
+        <v>1.849628864907813</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.376818841846325</v>
+        <v>1.249027558718284</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.621066183067008</v>
+        <v>3.544391413190183</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.796264143959851</v>
+        <v>3.79626414395985</v>
       </c>
       <c r="C1995" t="n">
         <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-1.859481710086258</v>
+        <v>-2.353581510450847</v>
       </c>
       <c r="E1995" t="n">
-        <v>2.068380175337753</v>
+        <v>1.870740255191917</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.376818841846325</v>
+        <v>1.249027558718284</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.638620588793799</v>
+        <v>3.561945818916974</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.794424941945361</v>
+        <v>3.79442494194536</v>
       </c>
       <c r="C1996" t="n">
         <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.027957827056136</v>
+        <v>-2.522057627420725</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.992844775954386</v>
+        <v>1.79520485580855</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.348871006129744</v>
+        <v>1.221079723001703</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.613706934768435</v>
+        <v>3.53703216489161</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782702</v>
+        <v>3.795574066782701</v>
       </c>
       <c r="C1997" t="n">
         <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.330158298194553</v>
+        <v>-1.824258098559142</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.253234284686881</v>
+        <v>2.055594364541045</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.278522946759334</v>
+        <v>1.150731663631292</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.55276779633405</v>
+        <v>3.476093026457225</v>
       </c>
     </row>
     <row r="1998">
@@ -47505,16 +47505,16 @@
         <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.3074371945114</v>
+        <v>-1.801536994875989</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.252986748657047</v>
+        <v>2.055346828511211</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.278522946759334</v>
+        <v>1.150731663631292</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.543431818830955</v>
+        <v>3.46675704895413</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777667</v>
+        <v>3.783205696777666</v>
       </c>
       <c r="C1999" t="n">
         <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.305712151221356</v>
+        <v>-1.799811951585945</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.412582891824233</v>
+        <v>2.214942971678397</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.280247990049378</v>
+        <v>1.152456706921336</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.70337297065615</v>
+        <v>3.626698200779325</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644407</v>
+        <v>3.779933725644406</v>
       </c>
       <c r="C2000" t="n">
         <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.460493157999612</v>
+        <v>-1.954592958364201</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.387748311606578</v>
+        <v>2.190108391460742</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.246880315994901</v>
+        <v>1.11908903286686</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.720430188717111</v>
+        <v>3.643755418840286</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799958</v>
+        <v>3.769443619799955</v>
       </c>
       <c r="C2001" t="n">
         <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.453438467784438</v>
+        <v>-1.947538268149027</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.387245543682192</v>
+        <v>2.189605623536357</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.253935006210075</v>
+        <v>1.126143723082033</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.72133835883576</v>
+        <v>3.644663588958935</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.766673496331111</v>
+        <v>3.76667349633111</v>
       </c>
       <c r="C2002" t="n">
         <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.42648724345795</v>
+        <v>-1.920587043822539</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.408032187057529</v>
+        <v>2.210392266911693</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.268815352237794</v>
+        <v>1.141024069109753</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.740272720097133</v>
+        <v>3.663597950220308</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784102</v>
+        <v>3.768052067784101</v>
       </c>
       <c r="C2003" t="n">
         <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.562440251514266</v>
+        <v>-2.056540051878855</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.537754115979963</v>
+        <v>2.340114195834127</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.268815352237794</v>
+        <v>1.141024069109753</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.924375852242093</v>
+        <v>3.847701082365268</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.74392550571442</v>
+        <v>3.743925505714419</v>
       </c>
       <c r="C2004" t="n">
         <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-1.584848369319138</v>
+        <v>-2.078948169683727</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.520907563761007</v>
+        <v>2.323267643615171</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.268815352237794</v>
+        <v>1.141024069109753</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.916492547145086</v>
+        <v>3.839817777268261</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155027</v>
+        <v>3.719118627155026</v>
       </c>
       <c r="C2005" t="n">
         <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-1.732854136798537</v>
+        <v>-2.222633902241719</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.463759256318884</v>
+        <v>2.267847350141612</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.268815352237794</v>
+        <v>1.103745700188279</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.918546546694723</v>
+        <v>3.819504755465014</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161972</v>
+        <v>3.729452285161971</v>
       </c>
       <c r="C2006" t="n">
         <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-1.742295062687067</v>
+        <v>-2.232074828130249</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.51623660368532</v>
+        <v>2.320324697508047</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.391242469781186</v>
+        <v>1.22617281773167</v>
       </c>
       <c r="G2006" t="n">
-        <v>4.048256534942605</v>
+        <v>3.949214743712896</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321629</v>
+        <v>3.714941193321628</v>
       </c>
       <c r="C2007" t="n">
         <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-1.794568670022708</v>
+        <v>-2.28434843546589</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.498218255296364</v>
+        <v>2.302306349119092</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.338968862445544</v>
+        <v>1.173899210396029</v>
       </c>
       <c r="G2007" t="n">
-        <v>4.019783465086522</v>
+        <v>3.920741673856813</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347698</v>
+        <v>3.727898186347696</v>
       </c>
       <c r="C2008" t="n">
         <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-1.870898647623614</v>
+        <v>-2.360678413066796</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.465798077149777</v>
+        <v>2.269886170972504</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.338968862445544</v>
+        <v>1.173899210396029</v>
       </c>
       <c r="G2008" t="n">
-        <v>4.017895277980297</v>
+        <v>3.918853486750588</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.710654104887742</v>
+        <v>3.71065410488774</v>
       </c>
       <c r="C2009" t="n">
         <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-1.982655600238916</v>
+        <v>-2.472435365682097</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.415915525706519</v>
+        <v>2.220003619529246</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.227211909830243</v>
+        <v>1.062142257780728</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.945661336013979</v>
+        <v>3.846619544784269</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.71289761234306</v>
+        <v>3.712897612343058</v>
       </c>
       <c r="C2010" t="n">
         <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-1.980814581180664</v>
+        <v>-2.470594346623846</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.415085943539971</v>
+        <v>2.219174037362699</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.228480136501712</v>
+        <v>1.063410484452196</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.944856282227011</v>
+        <v>3.845814490997302</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.7549119076471</v>
+        <v>3.754911907647098</v>
       </c>
       <c r="C2011" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.113115873278217</v>
+        <v>-2.602895638721399</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.375238833566869</v>
+        <v>2.179326927389596</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.228480136501712</v>
+        <v>1.063410484452196</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.95792968909293</v>
+        <v>3.858887897863221</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763527</v>
+        <v>3.749896851763524</v>
       </c>
       <c r="C2012" t="n">
         <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.114677516093077</v>
+        <v>-2.604457281536259</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.374614176440925</v>
+        <v>2.178702270263652</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.228480136501712</v>
+        <v>1.063410484452196</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.95792968909293</v>
+        <v>3.858887897863221</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.71583405539211</v>
+        <v>3.715834055392107</v>
       </c>
       <c r="C2013" t="n">
         <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.14257830320255</v>
+        <v>-2.632358068645732</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.361977902724138</v>
+        <v>2.166065996546865</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.193883212358777</v>
+        <v>1.028813560309262</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.935695575734171</v>
+        <v>3.836653784504462</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172521</v>
+        <v>3.684909939172519</v>
       </c>
       <c r="C2014" t="n">
         <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.145611300715224</v>
+        <v>-2.635391066158406</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.357529147696267</v>
+        <v>2.161617241518994</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.190850214846103</v>
+        <v>1.025780562796588</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.930640221203766</v>
+        <v>3.831598429974057</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971074</v>
+        <v>3.619362241971072</v>
       </c>
       <c r="C2015" t="n">
         <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.165672621991731</v>
+        <v>-2.655452387434913</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.416210578776168</v>
+        <v>2.220298672598895</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.170788893569596</v>
+        <v>1.005719241520081</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.985309388028365</v>
+        <v>3.886267596798656</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.6407642481998</v>
+        <v>3.640764248199798</v>
       </c>
       <c r="C2016" t="n">
         <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.422393439986555</v>
+        <v>-2.912173205429737</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.453833970580086</v>
+        <v>2.257922064402813</v>
       </c>
       <c r="F2016" t="n">
-        <v>1.062374319425781</v>
+        <v>0.8973046673762658</v>
       </c>
       <c r="G2016" t="n">
-        <v>4.060572362543923</v>
+        <v>3.961530571314214</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622231</v>
+        <v>3.668303164622229</v>
       </c>
       <c r="C2017" t="n">
         <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-2.576379857762695</v>
+        <v>-3.066159623205877</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.461219672615269</v>
+        <v>2.265307766437996</v>
       </c>
       <c r="F2017" t="n">
-        <v>1.062374319425781</v>
+        <v>0.8973046673762658</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.129552631689563</v>
+        <v>4.030510840459854</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808524</v>
+        <v>3.619937176808522</v>
       </c>
       <c r="C2018" t="n">
         <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.525857953935029</v>
+        <v>-3.015637719378212</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.467479636266456</v>
+        <v>2.271567730089183</v>
       </c>
       <c r="F2018" t="n">
-        <v>1.062374319425781</v>
+        <v>0.8973046673762658</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.115603833809685</v>
+        <v>4.016562042579975</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994888</v>
+        <v>3.656346893994887</v>
       </c>
       <c r="C2019" t="n">
         <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-2.778333107942754</v>
+        <v>-3.268112873385936</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.37836006371878</v>
+        <v>2.182448157541507</v>
       </c>
       <c r="F2019" t="n">
-        <v>1.062374319425781</v>
+        <v>0.8973046673762658</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.127474322865099</v>
+        <v>4.028432531635389</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.674042696358292</v>
+        <v>3.67404269635829</v>
       </c>
       <c r="C2020" t="n">
         <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.047805909864462</v>
+        <v>-3.537585675307644</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.271781477469041</v>
+        <v>2.075869571291768</v>
       </c>
       <c r="F2020" t="n">
-        <v>1.062374319425781</v>
+        <v>0.8973046673762658</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.128684857384042</v>
+        <v>4.029643066154333</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637081</v>
+        <v>3.663523617637079</v>
       </c>
       <c r="C2021" t="n">
         <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.205349981593903</v>
+        <v>-3.695129747037086</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.212885591004586</v>
+        <v>2.016973684827313</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.9954725142855065</v>
+        <v>0.8304028622359914</v>
       </c>
       <c r="G2021" t="n">
-        <v>4.092665516527198</v>
+        <v>3.993623725297489</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301338</v>
+        <v>3.652163313301336</v>
       </c>
       <c r="C2022" t="n">
         <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.33420053229595</v>
+        <v>-3.823980297739132</v>
       </c>
       <c r="E2022" t="n">
-        <v>2.156423223459957</v>
+        <v>1.960511317282684</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.954479105434785</v>
+        <v>0.7894094533852698</v>
       </c>
       <c r="G2022" t="n">
-        <v>4.063147323952955</v>
+        <v>3.964105532723246</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215464</v>
+        <v>3.667976467215462</v>
       </c>
       <c r="C2023" t="n">
         <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.451168224934841</v>
+        <v>-3.940947990378023</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.271840203103444</v>
+        <v>2.075928296926171</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.954479105434785</v>
+        <v>0.7894094533852698</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.225351380652</v>
+        <v>4.12630958942229</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456686</v>
+        <v>3.696553628456685</v>
       </c>
       <c r="C2024" t="n">
         <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.535886167155795</v>
+        <v>-4.025665932598977</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.232799664178877</v>
+        <v>2.036887758001604</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.8693630765067386</v>
+        <v>0.7042934244572234</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.169128401258986</v>
+        <v>4.070086610029277</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253282</v>
+        <v>3.750058176253281</v>
       </c>
       <c r="C2025" t="n">
         <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-3.617820985424678</v>
+        <v>-4.10760075086786</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.210255154439815</v>
+        <v>2.014343248262542</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.8594283309196584</v>
+        <v>0.6943586788701432</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.173396971475229</v>
+        <v>4.07435518024552</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717826</v>
+        <v>3.783647027717825</v>
       </c>
       <c r="C2026" t="n">
         <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.564082812024416</v>
+        <v>-4.053862577467598</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.240676062255822</v>
+        <v>2.044764156078549</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.9131665043199205</v>
+        <v>0.7480968522704053</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.214565513971288</v>
+        <v>4.115523722741579</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616943</v>
+        <v>3.798310944616941</v>
       </c>
       <c r="C2027" t="n">
         <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.454076528547194</v>
+        <v>-3.943856293990376</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.276831462890886</v>
+        <v>2.080919556713613</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.9363710762371957</v>
+        <v>0.7713014241876806</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.220641144365828</v>
+        <v>4.121599353136119</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203658</v>
+        <v>3.785578085203655</v>
       </c>
       <c r="C2028" t="n">
         <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.311016952806269</v>
+        <v>-3.469913355511006</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.338305303909231</v>
+        <v>2.274746742827336</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.944384502827175</v>
+        <v>0.7133742735244937</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.22969921104179</v>
+        <v>4.091093073460182</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.795385980328755</v>
+        <v>3.859268879435188</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.723832922524505</v>
+        <v>3.709403299959951</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.311016952806269</v>
+        <v>-3.469913355511006</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.338305303909231</v>
+        <v>2.274746742827336</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.944384502827175</v>
+        <v>0.7133742735244937</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.716896719510872</v>
+        <v>3.702467096946318</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240718.xlsx
+++ b/tame_output/ON/bt/strategyON_20240718.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>61.2%</t>
+          <t>48.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>66.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.8%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>18.9%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>79.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>60.6%</t>
+          <t>61.7%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>8.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.6%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.6%</t>
+          <t>38.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>52.6%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-72.8%</t>
+          <t>-73.0%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>111.3%</t>
+          <t>109.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.65</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.1%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>122.4%</t>
+          <t>122.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>96.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>23.5%</t>
+          <t>24.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-47.7%</t>
+          <t>-49.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-67.9%</t>
+          <t>-68.4%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>92.3%</t>
+          <t>90.8%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.7</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>456.9%</t>
+          <t>454.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-9.4%</t>
+          <t>-7.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-508.6%</t>
+          <t>-520.6%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>26.5%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.9%</t>
+          <t>56.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.49</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.4%</t>
+          <t>57.5%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>63.0%</t>
+          <t>62.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>51.9%</t>
+          <t>50.7%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-35.9%</t>
+          <t>-36.4%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.4%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>47.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1180,17 +1180,17 @@
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>80.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-11.0%</t>
+          <t>-10.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-148.7%</t>
+          <t>-155.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-11.2%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.17</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>63.9%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.3%</t>
+          <t>99.4%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.9%</t>
+          <t>10.6%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-27.8%</t>
+          <t>-28.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-8.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1333,7 +1333,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.1</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>-1.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-134.3%</t>
+          <t>-121.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-152.7%</t>
+          <t>-176.0%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>74.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>53.6%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.14</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.0%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>48.0%</t>
+          <t>47.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>93.5%</t>
+          <t>94.1%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1456,22 +1456,22 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-8.3%</t>
+          <t>-3.9%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.6%</t>
+          <t>-1.1%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-22.8%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,17 +1481,17 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>46.9%</t>
+          <t>44.7%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.6%</t>
+          <t>-17.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.6%</t>
+          <t>34.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-75.8%</t>
+          <t>-52.9%</t>
         </is>
       </c>
     </row>
@@ -43681,7 +43681,7 @@
         <v>45294</v>
       </c>
       <c r="B1832" t="n">
-        <v>3.301413393085798</v>
+        <v>3.301413393085799</v>
       </c>
       <c r="C1832" t="n">
         <v>3.130069279090508</v>
@@ -43727,7 +43727,7 @@
         <v>45296</v>
       </c>
       <c r="B1834" t="n">
-        <v>3.317575502045691</v>
+        <v>3.317575502045692</v>
       </c>
       <c r="C1834" t="n">
         <v>3.13991794227561</v>
@@ -43773,7 +43773,7 @@
         <v>45298</v>
       </c>
       <c r="B1836" t="n">
-        <v>3.311888301355687</v>
+        <v>3.311888301355689</v>
       </c>
       <c r="C1836" t="n">
         <v>3.118001050765402</v>
@@ -43796,7 +43796,7 @@
         <v>45299</v>
       </c>
       <c r="B1837" t="n">
-        <v>3.385382209279811</v>
+        <v>3.385382209279813</v>
       </c>
       <c r="C1837" t="n">
         <v>3.118490189491276</v>
@@ -43819,7 +43819,7 @@
         <v>45300</v>
       </c>
       <c r="B1838" t="n">
-        <v>3.367379938511402</v>
+        <v>3.367379938511403</v>
       </c>
       <c r="C1838" t="n">
         <v>3.122570172112943</v>
@@ -43842,7 +43842,7 @@
         <v>45301</v>
       </c>
       <c r="B1839" t="n">
-        <v>3.376932391386091</v>
+        <v>3.376932391386092</v>
       </c>
       <c r="C1839" t="n">
         <v>3.157511256610484</v>
@@ -43865,7 +43865,7 @@
         <v>45302</v>
       </c>
       <c r="B1840" t="n">
-        <v>3.367370539998558</v>
+        <v>3.367370539998559</v>
       </c>
       <c r="C1840" t="n">
         <v>3.156088696795822</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.5027903991417</v>
+        <v>3.502790399141701</v>
       </c>
       <c r="C1878" t="n">
         <v>3.140320092255247</v>
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499971739440633</v>
+        <v>3.499971739440634</v>
       </c>
       <c r="C1880" t="n">
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.640201116170417</v>
+        <v>-8.822165266762951</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.29626252254881</v>
+        <v>-0.3690481827858236</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.519393443186055</v>
+        <v>-1.70135759377859</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.248538282321471</v>
+        <v>2.13935979196595</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490059241608598</v>
+        <v>3.4900592416086</v>
       </c>
       <c r="C1881" t="n">
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.81532553355696</v>
+        <v>-8.997289684149495</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.3517570687559104</v>
+        <v>-0.4245427289929244</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.876482011165134</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.158018852637062</v>
+        <v>2.048840362281541</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.48587859441027</v>
+        <v>3.485878594410271</v>
       </c>
       <c r="C1882" t="n">
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.04977762757145</v>
+        <v>-9.231741778163984</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.4527570712633024</v>
+        <v>-0.5255427315003161</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.694517860572599</v>
+        <v>-1.876482011165134</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.150799687735466</v>
+        <v>2.041621197379945</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.154152358597896</v>
+        <v>-9.336116509190431</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5011791544478572</v>
+        <v>-0.5739648146848708</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.798892591599045</v>
+        <v>-1.98085674219158</v>
       </c>
       <c r="G1883" t="n">
-        <v>2.081502658345622</v>
+        <v>1.972324167990101</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493716014390584</v>
+        <v>3.493716014390585</v>
       </c>
       <c r="C1884" t="n">
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.206938514198223</v>
+        <v>-9.388902664790757</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5211778268494314</v>
+        <v>-0.5939634870864454</v>
       </c>
       <c r="F1884" t="n">
-        <v>-1.894568078181442</v>
+        <v>-2.076532228773977</v>
       </c>
       <c r="G1884" t="n">
-        <v>2.025213156234741</v>
+        <v>1.916034665879219</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.332975307566512</v>
+        <v>-9.514939458159047</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.5688988155676324</v>
+        <v>-0.6416844758046465</v>
       </c>
       <c r="F1885" t="n">
-        <v>-1.869316455371699</v>
+        <v>-2.051280605964235</v>
       </c>
       <c r="G1885" t="n">
-        <v>2.0430578585497</v>
+        <v>1.933879368194179</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.275903535670581</v>
+        <v>-9.457867686263116</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.5420797711228591</v>
+        <v>-0.6148654313598731</v>
       </c>
       <c r="F1886" t="n">
-        <v>-1.869316455371699</v>
+        <v>-2.051280605964235</v>
       </c>
       <c r="G1886" t="n">
-        <v>2.047048194236101</v>
+        <v>1.93786970388058</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.417575377394702</v>
+        <v>-9.599539527987236</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.6002237347112489</v>
+        <v>-0.673009394948263</v>
       </c>
       <c r="F1887" t="n">
-        <v>-1.869316455371699</v>
+        <v>-2.051280605964235</v>
       </c>
       <c r="G1887" t="n">
-        <v>2.045572967337359</v>
+        <v>1.936394476981838</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.367984532969867</v>
+        <v>-9.549948683562402</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.5653339867764431</v>
+        <v>-0.6381196470134571</v>
       </c>
       <c r="F1888" t="n">
-        <v>-1.819725610946866</v>
+        <v>-2.001689761539401</v>
       </c>
       <c r="G1888" t="n">
-        <v>2.090380884157132</v>
+        <v>1.981202393801611</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.219066198498011</v>
+        <v>-9.401030349090545</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5188177866343833</v>
+        <v>-0.5916034468713973</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.788476020211692</v>
+        <v>-1.970440170804228</v>
       </c>
       <c r="G1889" t="n">
-        <v>2.096079504951553</v>
+        <v>1.986901014596032</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-8.993221045778601</v>
+        <v>-9.175185196371135</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4189006525104109</v>
+        <v>-0.4916863127474245</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.928513495217064</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.13081458334006</v>
+        <v>2.021636092984539</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-8.868642389441009</v>
+        <v>-9.050606540033543</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.3679300454193153</v>
+        <v>-0.4407157056563289</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.746549344624529</v>
+        <v>-1.928513495217064</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.131953727896119</v>
+        <v>2.022775237540598</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-8.921537677485295</v>
+        <v>-9.10350182807783</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.3864543864749219</v>
+        <v>-0.459240046711936</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.923558149128618</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.137560709711294</v>
+        <v>2.028382219355773</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-8.849404502197414</v>
+        <v>-9.031368652789949</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.3518674121211331</v>
+        <v>-0.4246530723581472</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.741593998536083</v>
+        <v>-1.923558149128618</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.14329441394993</v>
+        <v>2.03411592359441</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.778038109587767</v>
+        <v>-8.960002260180302</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.3330581174711393</v>
+        <v>-0.4058437777081534</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.85219175651897</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.176376987121854</v>
+        <v>2.067198496766333</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.684579075602542</v>
+        <v>-8.866543226195077</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.305557985189957</v>
+        <v>-0.3783436454269711</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.85219175651897</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.166493505808947</v>
+        <v>2.057315015453425</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.417337274734145</v>
+        <v>-8.599301425326679</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2004958253419717</v>
+        <v>-0.2732814855789858</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.670227605926435</v>
+        <v>-1.85219175651897</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.164658945309573</v>
+        <v>2.055480454954052</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.319430236057654</v>
+        <v>-8.501394386650189</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.1616333248448365</v>
+        <v>-0.2344189850818501</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.602241856065878</v>
+        <v>-1.784206006658414</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.205150080252446</v>
+        <v>2.095971589896925</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.295476695081696</v>
+        <v>-8.477440845674231</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.1513834023089595</v>
+        <v>-0.2241690625459736</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.578288315089921</v>
+        <v>-1.760252465682456</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.220190710983514</v>
+        <v>2.111012220627993</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.031416756758899</v>
+        <v>-8.213380907351434</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.05901974314159286</v>
+        <v>-0.1318054033786069</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.49619252735966</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.365366357815439</v>
+        <v>2.256187867459919</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.324337133254061</v>
+        <v>-7.506301283846596</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.2210250726000416</v>
+        <v>0.1482394123630275</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.314228376767125</v>
+        <v>-1.49619252735966</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.362579324155138</v>
+        <v>2.253400833799618</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.284152834887871</v>
+        <v>-7.466116985480405</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.2374424158343591</v>
+        <v>0.1646567555973451</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.274044078400934</v>
+        <v>-1.456008228993469</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.387033527062695</v>
+        <v>2.277855036707173</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.120752963948508</v>
+        <v>-7.302717114541043</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.302169185430861</v>
+        <v>0.229383525193847</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.110644207461571</v>
+        <v>-1.292608358054106</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.484440270847069</v>
+        <v>2.375261780491548</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-6.88727174171891</v>
+        <v>-7.069235892311444</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.4034861031605526</v>
+        <v>0.330700442923539</v>
       </c>
       <c r="F1903" t="n">
-        <v>-0.8771629852319727</v>
+        <v>-1.059127135824508</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.632453433022681</v>
+        <v>2.523274942667159</v>
       </c>
     </row>
     <row r="1904">
@@ -45337,22 +45337,22 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801637122785786</v>
+        <v>3.801637122785787</v>
       </c>
       <c r="C1904" t="n">
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.737605350711394</v>
+        <v>-6.919569501303929</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.4604604492505997</v>
+        <v>0.3876747890135857</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.7842594939894367</v>
+        <v>-0.9662236445819719</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.685303317455243</v>
+        <v>2.576124827099722</v>
       </c>
     </row>
     <row r="1905">
@@ -45360,22 +45360,22 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763182248390426</v>
+        <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.151226500595932</v>
+        <v>3.123455680436313</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.605329877080508</v>
+        <v>-6.787294027673043</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.5087381254499812</v>
+        <v>0.4081816450533484</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.6519840203585501</v>
+        <v>-0.8339481709510852</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.760036088380802</v>
+        <v>2.623086777865662</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.154041561283568</v>
+        <v>3.12627074112395</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.449591544520766</v>
+        <v>-6.631555695113301</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.5738485191615146</v>
+        <v>0.4732920387648818</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.6782098383913436</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.856294148604284</v>
+        <v>2.719344838089144</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.166947902507227</v>
+        <v>3.139177082347608</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.200591745837185</v>
+        <v>-6.38255589642972</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.6863547798586058</v>
+        <v>0.585798299461973</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.4962456877988085</v>
+        <v>-0.6782098383913436</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.869200489827942</v>
+        <v>2.732251179312803</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.038971972908008</v>
+        <v>3.01120115274839</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.30618173561029</v>
+        <v>-6.488145886202824</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.5161428543501452</v>
+        <v>0.4155863739535128</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.6018356775719129</v>
+        <v>-0.783799828164448</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.677870566364861</v>
+        <v>2.540921255849721</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.087516314785095</v>
+        <v>3.059745494625476</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.324916637728887</v>
+        <v>-6.506880788321421</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.5571932353797928</v>
+        <v>0.45663675498316</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.6074316872320442</v>
+        <v>-0.7893958378245793</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.723057302445869</v>
+        <v>2.586107991930729</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.967637392096927</v>
+        <v>2.939866571937308</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.176976596321287</v>
+        <v>-6.358940746913822</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.496490329254665</v>
+        <v>0.3959338488580322</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.5871107713234867</v>
+        <v>-0.7690749219160218</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.615370929302836</v>
+        <v>2.478421618787696</v>
       </c>
     </row>
     <row r="1911">
@@ -45498,22 +45498,22 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723566229409204</v>
+        <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.958923405843449</v>
+        <v>2.93115258568383</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.201259613402452</v>
+        <v>-6.305971224659833</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4780631361687209</v>
+        <v>0.4084076715061498</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.6113937884046511</v>
+        <v>-0.7161053996620329</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.592087132800659</v>
+        <v>2.501489345886611</v>
       </c>
     </row>
     <row r="1912">
@@ -45521,22 +45521,22 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729969716098109</v>
+        <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.951962793748356</v>
+        <v>2.924191973588737</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.157711206631761</v>
+        <v>-6.262422817889143</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4885218867819039</v>
+        <v>0.4188664221193328</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.6113937884046511</v>
+        <v>-0.7161053996620329</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.585126520705566</v>
+        <v>2.494528733791518</v>
       </c>
     </row>
     <row r="1913">
@@ -45544,22 +45544,22 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782922533493419</v>
+        <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.966425148129499</v>
+        <v>2.93865432796988</v>
       </c>
       <c r="D1913" t="n">
-        <v>-5.915562813177903</v>
+        <v>-6.020274424435285</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5998435985445902</v>
+        <v>0.5301881338820191</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.6113937884046511</v>
+        <v>-0.7161053996620329</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.599588875086709</v>
+        <v>2.508991088172661</v>
       </c>
     </row>
     <row r="1914">
@@ -45567,22 +45567,22 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.828551486722816</v>
+        <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.960957268588694</v>
+        <v>2.933186448429075</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.807303676055382</v>
+        <v>-5.912015287312763</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.6376793738527939</v>
+        <v>0.5680239091902228</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.6113937884046511</v>
+        <v>-0.7161053996620329</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.594120995545904</v>
+        <v>2.503523208631856</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.958455362599271</v>
+        <v>2.930684542439652</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.684012541238251</v>
+        <v>-5.788724152495632</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6844939217902235</v>
+        <v>0.6148384571276519</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.4881026535875206</v>
+        <v>-0.5928142648449024</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.665593770446759</v>
+        <v>2.574995983532711</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.966156340836596</v>
+        <v>2.938385520676977</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.662863342334807</v>
+        <v>-5.767574953592189</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.7006545795889259</v>
+        <v>0.6309991149263543</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.4669534546840772</v>
+        <v>-0.571665065941459</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.68598426802615</v>
+        <v>2.595386481112102</v>
       </c>
     </row>
     <row r="1917">
@@ -45636,22 +45636,22 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748328408318091</v>
+        <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.961937049183647</v>
+        <v>2.934166229024028</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.419097900351363</v>
+        <v>-5.523809511608745</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7939414647293543</v>
+        <v>0.7242860000667828</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.4669534546840772</v>
+        <v>-0.571665065941459</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.681764976373201</v>
+        <v>2.591167189459153</v>
       </c>
     </row>
     <row r="1918">
@@ -45659,22 +45659,22 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.824311233057523</v>
+        <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.964061363103663</v>
+        <v>2.936290542944044</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.317335080074068</v>
+        <v>-5.42204669133145</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.8367709067602882</v>
+        <v>0.7671154420977166</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.4537343862916485</v>
+        <v>-0.5584459975490303</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.691820731328674</v>
+        <v>2.601222944414626</v>
       </c>
     </row>
     <row r="1919">
@@ -45682,22 +45682,22 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826354974279183</v>
+        <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.956803438087365</v>
+        <v>2.929032617927746</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.067484686124994</v>
+        <v>-5.172196297382375</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.9294531393236203</v>
+        <v>0.8597976746610487</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.4537343862916485</v>
+        <v>-0.5584459975490303</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.684562806312376</v>
+        <v>2.593965019398328</v>
       </c>
     </row>
     <row r="1920">
@@ -45705,22 +45705,22 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835957987011496</v>
+        <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.960402561608014</v>
+        <v>2.932631741448395</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.891592593657561</v>
+        <v>-4.996304204914942</v>
       </c>
       <c r="E1920" t="n">
-        <v>1.003409099831242</v>
+        <v>0.9337536351686708</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.4537343862916485</v>
+        <v>-0.5584459975490303</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.688161929833025</v>
+        <v>2.597564142918977</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780933911392985</v>
+        <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.973730067662567</v>
+        <v>2.945959247502949</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.720146130635098</v>
+        <v>-4.824857741892479</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.085315191094781</v>
+        <v>1.01565972643221</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.2822879232691854</v>
+        <v>-0.3869995345265672</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.804357313701056</v>
+        <v>2.713759526787009</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773765222632779</v>
+        <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.972750545278864</v>
+        <v>2.944979725119246</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.645856564896759</v>
+        <v>-4.75056817615414</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.114051495006414</v>
+        <v>1.044396030343842</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.2079983575308461</v>
+        <v>-0.3127099687882279</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.847951530760357</v>
+        <v>2.757353743846309</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764617879883071</v>
+        <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.977445346333182</v>
+        <v>2.949674526173563</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.582220822662824</v>
+        <v>-4.686932433920205</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.144200592954304</v>
+        <v>1.074545128291734</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.1443626152969116</v>
+        <v>-0.2490742265542934</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.890827777155035</v>
+        <v>2.800229990240987</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798814771074779</v>
+        <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.958639605116977</v>
+        <v>2.930868784957358</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.470794063336904</v>
+        <v>-4.575505674594285</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.169965555468468</v>
+        <v>1.100310090805897</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.1443626152969116</v>
+        <v>-0.2490742265542934</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.87202203593883</v>
+        <v>2.781424249024783</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769488424229</v>
+        <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.960382681741855</v>
+        <v>2.932611861582236</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.230363566532044</v>
+        <v>-4.335075177789425</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.26788083081529</v>
+        <v>1.198225366152719</v>
       </c>
       <c r="F1925" t="n">
-        <v>0.0960678815079487</v>
+        <v>-0.008643729749433116</v>
       </c>
       <c r="G1925" t="n">
-        <v>3.018023410646624</v>
+        <v>2.927425623732576</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82159350936768</v>
+        <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.964311995576675</v>
+        <v>2.936541175417056</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.158120998360849</v>
+        <v>-4.26283260961823</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.300707171918588</v>
+        <v>1.231051707256017</v>
       </c>
       <c r="F1926" t="n">
-        <v>0.0960678815079487</v>
+        <v>-0.008643729749433116</v>
       </c>
       <c r="G1926" t="n">
-        <v>3.021952724481444</v>
+        <v>2.931354937567396</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822326997879962</v>
+        <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.964990579494015</v>
+        <v>2.937219759334396</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.105122676079461</v>
+        <v>-4.209834287336842</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.322585084748483</v>
+        <v>1.252929620085912</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.1514041405098875</v>
+        <v>0.04669252925250572</v>
       </c>
       <c r="G1927" t="n">
-        <v>3.055833063799948</v>
+        <v>2.9652352768859</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848616626502334</v>
+        <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.961988650714008</v>
+        <v>2.93421783055439</v>
       </c>
       <c r="D1928" t="n">
-        <v>-3.996317790599735</v>
+        <v>-4.101029401857115</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.363105110160367</v>
+        <v>1.293449645497796</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.1514041405098875</v>
+        <v>0.04669252925250572</v>
       </c>
       <c r="G1928" t="n">
-        <v>3.052831135019941</v>
+        <v>2.962233348105893</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818668951675934</v>
+        <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.963567687724622</v>
+        <v>2.935796867565004</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.776296992562724</v>
+        <v>-3.881008603820104</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.452692466385786</v>
+        <v>1.383037001723215</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.2926239855778678</v>
+        <v>0.187912374320486</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.139142079071343</v>
+        <v>3.048544292157295</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843274527539946</v>
+        <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.979461870526446</v>
+        <v>2.951691050366827</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.643429303499446</v>
+        <v>-3.748140914756826</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.52173372481292</v>
+        <v>1.452078260150349</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.2926239855778678</v>
+        <v>0.187912374320486</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.155036261873167</v>
+        <v>3.064438474959119</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845047386496257</v>
+        <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.980607714966748</v>
+        <v>2.952836894807129</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.523256220134947</v>
+        <v>-3.627967831392327</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.570948802599022</v>
+        <v>1.501293337936451</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.4127970689423667</v>
+        <v>0.3080854576849849</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.228285956332168</v>
+        <v>3.13768816941812</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791273551576993</v>
+        <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.990695817528187</v>
+        <v>2.962924997368569</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.378584075035209</v>
+        <v>-3.669908621602938</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.638905763200357</v>
+        <v>1.494605124413646</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.5574692140421041</v>
+        <v>0.2661446674743738</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.32517734595345</v>
+        <v>3.122611797853193</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735839222942099</v>
+        <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.976733308929613</v>
+        <v>2.948962488769995</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.438458902392902</v>
+        <v>-3.729783448960631</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.600993323658706</v>
+        <v>1.456692684871995</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.497594386684412</v>
+        <v>0.2062698401166817</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.275289940940261</v>
+        <v>3.072724392840004</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762647477674511</v>
+        <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.992022478163822</v>
+        <v>2.964251658004203</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.318638671482064</v>
+        <v>-3.609963218049793</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.664210585257249</v>
+        <v>1.519909946470539</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.497594386684412</v>
+        <v>0.2062698401166817</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.290579110174469</v>
+        <v>3.088013562074212</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729146398430689</v>
+        <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.899666677486263</v>
+        <v>2.871895857326645</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.32110837794387</v>
+        <v>-3.612432924511599</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.570866901994968</v>
+        <v>1.426566263208258</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.4951246802226059</v>
+        <v>0.2038001336548755</v>
       </c>
       <c r="G1935" t="n">
-        <v>3.196741485619827</v>
+        <v>2.99417593751957</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.743220196003598</v>
+        <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.818928538971565</v>
+        <v>2.791157718811946</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.38947856426788</v>
+        <v>-3.680803110835609</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.462780688950666</v>
+        <v>1.318480050163955</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.5044003792588209</v>
+        <v>0.2130758326910905</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.121568766526857</v>
+        <v>2.919003218426601</v>
       </c>
     </row>
     <row r="1937">
@@ -46096,22 +46096,22 @@
         <v>45399</v>
       </c>
       <c r="B1937" t="n">
-        <v>3.714179139508365</v>
+        <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.809365247603456</v>
+        <v>2.781594427443837</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.403266617114927</v>
+        <v>-3.694591163682656</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.447702176443738</v>
+        <v>1.303401537657028</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.5044003792588209</v>
+        <v>0.2130758326910905</v>
       </c>
       <c r="G1937" t="n">
-        <v>3.112005475158749</v>
+        <v>2.909439927058492</v>
       </c>
     </row>
     <row r="1938">
@@ -46119,22 +46119,22 @@
         <v>45400</v>
       </c>
       <c r="B1938" t="n">
-        <v>3.710906731417699</v>
+        <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.634074812643843</v>
+        <v>2.606303992484224</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.434259776443632</v>
+        <v>-3.725584323011361</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.260014477752643</v>
+        <v>1.115713838965932</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.5044003792588209</v>
+        <v>0.2130758326910905</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.936715040199136</v>
+        <v>2.734149492098879</v>
       </c>
     </row>
     <row r="1939">
@@ -46142,22 +46142,22 @@
         <v>45401</v>
       </c>
       <c r="B1939" t="n">
-        <v>3.746042526205894</v>
+        <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.638642044635631</v>
+        <v>2.610871224476012</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.258785516651163</v>
+        <v>-3.550110063218892</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.334771413661418</v>
+        <v>1.190470774874708</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.5044003792588209</v>
+        <v>0.2130758326910905</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.941282272190923</v>
+        <v>2.738716724090667</v>
       </c>
     </row>
     <row r="1940">
@@ -46165,22 +46165,22 @@
         <v>45402</v>
       </c>
       <c r="B1940" t="n">
-        <v>3.765024323225439</v>
+        <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.614384073396838</v>
+        <v>2.586613253237219</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.369721769292411</v>
+        <v>-3.661046315860141</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.266138941366126</v>
+        <v>1.121838302579416</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.5044003792588209</v>
+        <v>0.2130758326910905</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.91702430095213</v>
+        <v>2.714458752851874</v>
       </c>
     </row>
     <row r="1941">
@@ -46188,22 +46188,22 @@
         <v>45403</v>
       </c>
       <c r="B1941" t="n">
-        <v>3.773210297111291</v>
+        <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.542922386798288</v>
+        <v>2.515151566638669</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.33605822382013</v>
+        <v>-3.627382770387859</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.208142672956488</v>
+        <v>1.063842034169778</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.5380639247311028</v>
+        <v>0.2467393781633723</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.865760741636949</v>
+        <v>2.663195193536692</v>
       </c>
     </row>
     <row r="1942">
@@ -46211,22 +46211,22 @@
         <v>45404</v>
       </c>
       <c r="B1942" t="n">
-        <v>3.784343952264161</v>
+        <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.55309477323042</v>
+        <v>2.525323953070801</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.372341929504335</v>
+        <v>-3.567530151184136</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.203801577114939</v>
+        <v>1.0979554682834</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.5380639247311028</v>
+        <v>0.2467393781633723</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.875933128069082</v>
+        <v>2.673367579968825</v>
       </c>
     </row>
     <row r="1943">
@@ -46234,22 +46234,22 @@
         <v>45405</v>
       </c>
       <c r="B1943" t="n">
-        <v>3.786949957742297</v>
+        <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.54804104380428</v>
+        <v>2.520270223644661</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.286098466477958</v>
+        <v>-3.481286688157758</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.23324523289935</v>
+        <v>1.127399124067811</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.5380639247311028</v>
+        <v>0.2467393781633723</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.870879398642942</v>
+        <v>2.668313850542685</v>
       </c>
     </row>
     <row r="1944">
@@ -46257,22 +46257,22 @@
         <v>45406</v>
       </c>
       <c r="B1944" t="n">
-        <v>3.752027499316043</v>
+        <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.539816819248806</v>
+        <v>2.512045999089187</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.331405285876937</v>
+        <v>-3.526593507556738</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.206898280584284</v>
+        <v>1.101052171752745</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.497253761721872</v>
+        <v>0.2059292151541415</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.838169076281929</v>
+        <v>2.635603528181672</v>
       </c>
     </row>
     <row r="1945">
@@ -46280,22 +46280,22 @@
         <v>45407</v>
       </c>
       <c r="B1945" t="n">
-        <v>3.753571165803187</v>
+        <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.540368692281907</v>
+        <v>2.512597872122289</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.360438390579239</v>
+        <v>-3.55562661225904</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.195836911736464</v>
+        <v>1.089990802904925</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.497253761721872</v>
+        <v>0.2059292151541415</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.838720949315031</v>
+        <v>2.636155401214774</v>
       </c>
     </row>
     <row r="1946">
@@ -46303,22 +46303,22 @@
         <v>45408</v>
       </c>
       <c r="B1946" t="n">
-        <v>3.733390600809495</v>
+        <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.469641384173273</v>
+        <v>2.441870564013654</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.26762790912838</v>
+        <v>-3.46281613080818</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.162233796208174</v>
+        <v>1.056387687376635</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.5900642431727313</v>
+        <v>0.2987396966050009</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.823679930076912</v>
+        <v>2.621114381976655</v>
       </c>
     </row>
     <row r="1947">
@@ -46326,22 +46326,22 @@
         <v>45409</v>
       </c>
       <c r="B1947" t="n">
-        <v>3.748285816560422</v>
+        <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.471514860097874</v>
+        <v>2.443744039938255</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.312017378457807</v>
+        <v>-3.507205600137608</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.146351484401004</v>
+        <v>1.040505375569465</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.5456747738433037</v>
+        <v>0.2543502272755732</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.798919724403856</v>
+        <v>2.596354176303599</v>
       </c>
     </row>
     <row r="1948">
@@ -46349,22 +46349,22 @@
         <v>45410</v>
       </c>
       <c r="B1948" t="n">
-        <v>3.721077195472734</v>
+        <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.466590568609597</v>
+        <v>2.438819748449978</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.199346160221557</v>
+        <v>-3.394534381901358</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.186495680207227</v>
+        <v>1.080649571375688</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.6583459920795538</v>
+        <v>0.3670214455118234</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.861598163857329</v>
+        <v>2.659032615757072</v>
       </c>
     </row>
     <row r="1949">
@@ -46372,22 +46372,22 @@
         <v>45411</v>
       </c>
       <c r="B1949" t="n">
-        <v>3.743047603798533</v>
+        <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.472081864440264</v>
+        <v>2.444311044280645</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.086969159038885</v>
+        <v>-3.282157380718685</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.236937776510963</v>
+        <v>1.131091667679424</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.6583459920795538</v>
+        <v>0.3670214455118234</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.867089459687997</v>
+        <v>2.664523911587739</v>
       </c>
     </row>
     <row r="1950">
@@ -46395,22 +46395,22 @@
         <v>45412</v>
       </c>
       <c r="B1950" t="n">
-        <v>3.68959784049886</v>
+        <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.483579066208803</v>
+        <v>2.455808246049184</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.114749556940238</v>
+        <v>-3.309937778620038</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.237322819118961</v>
+        <v>1.131476710287422</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.6305655941782007</v>
+        <v>0.3392410476104704</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.861918422715724</v>
+        <v>2.659352874615467</v>
       </c>
     </row>
     <row r="1951">
@@ -46418,22 +46418,22 @@
         <v>45413</v>
       </c>
       <c r="B1951" t="n">
-        <v>3.643069621705322</v>
+        <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.321934786209456</v>
+        <v>2.294163966049838</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.197750837965517</v>
+        <v>-3.392939059645317</v>
       </c>
       <c r="E1951" t="n">
-        <v>1.042478026709502</v>
+        <v>0.9366319178779634</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.611994709651027</v>
+        <v>0.3206701630832966</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.689131612000073</v>
+        <v>2.486566063899816</v>
       </c>
     </row>
     <row r="1952">
@@ -46441,22 +46441,22 @@
         <v>45414</v>
       </c>
       <c r="B1952" t="n">
-        <v>3.682716310729266</v>
+        <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.442084446928662</v>
+        <v>2.414313626769043</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.306364916408848</v>
+        <v>-3.501553138088648</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.119182056051376</v>
+        <v>1.013335947219837</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.611994709651027</v>
+        <v>0.3206701630832966</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.809281272719279</v>
+        <v>2.606715724619022</v>
       </c>
     </row>
     <row r="1953">
@@ -46464,22 +46464,22 @@
         <v>45415</v>
       </c>
       <c r="B1953" t="n">
-        <v>3.733012441190764</v>
+        <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.456597473030985</v>
+        <v>2.428826652871366</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.270955878160705</v>
+        <v>-3.466144099840506</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.147858697452956</v>
+        <v>1.042012588621417</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.611994709651027</v>
+        <v>0.3206701630832966</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.823794298821602</v>
+        <v>2.621228750721345</v>
       </c>
     </row>
     <row r="1954">
@@ -46487,22 +46487,22 @@
         <v>45416</v>
       </c>
       <c r="B1954" t="n">
-        <v>3.741174069913422</v>
+        <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.454016914373354</v>
+        <v>2.426246094213735</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.232572215602554</v>
+        <v>-3.427760437282354</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.160631603818585</v>
+        <v>1.054785494987046</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.6503783722091782</v>
+        <v>0.3590538256414478</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.844243937698861</v>
+        <v>2.641678389598604</v>
       </c>
     </row>
     <row r="1955">
@@ -46510,22 +46510,22 @@
         <v>45417</v>
       </c>
       <c r="B1955" t="n">
-        <v>3.751147197532481</v>
+        <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.450745943218656</v>
+        <v>2.422975123059037</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.055455885567388</v>
+        <v>-3.250644107247188</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.228207164677953</v>
+        <v>1.122361055846414</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.6503783722091782</v>
+        <v>0.3590538256414478</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.840972966544163</v>
+        <v>2.638407418443906</v>
       </c>
     </row>
     <row r="1956">
@@ -46533,22 +46533,22 @@
         <v>45418</v>
       </c>
       <c r="B1956" t="n">
-        <v>3.741328448793898</v>
+        <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.451429334980569</v>
+        <v>2.42365851482095</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.100548130400933</v>
+        <v>-3.295736352080734</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.210853658506448</v>
+        <v>1.105007549674909</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.5884823290397884</v>
+        <v>0.297157782472058</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.804518732404442</v>
+        <v>2.601953184304185</v>
       </c>
     </row>
     <row r="1957">
@@ -46556,22 +46556,22 @@
         <v>45419</v>
       </c>
       <c r="B1957" t="n">
-        <v>3.75072937701123</v>
+        <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.445216310286983</v>
+        <v>2.417445490127364</v>
       </c>
       <c r="D1957" t="n">
-        <v>-2.921172709162166</v>
+        <v>-3.116360930841966</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.276390802308369</v>
+        <v>1.17054469347683</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.745259087210507</v>
+        <v>0.4539345406427767</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.892371762613287</v>
+        <v>2.68980621451303</v>
       </c>
     </row>
     <row r="1958">
@@ -46579,22 +46579,22 @@
         <v>45420</v>
       </c>
       <c r="B1958" t="n">
-        <v>3.716991718982225</v>
+        <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.426023765618573</v>
+        <v>2.398252945458954</v>
       </c>
       <c r="D1958" t="n">
-        <v>-2.966186922682772</v>
+        <v>-3.161375144362573</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.239192572231717</v>
+        <v>1.133346463400178</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.7149101918959024</v>
+        <v>0.4235856453281721</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.854969880756114</v>
+        <v>2.652404332655858</v>
       </c>
     </row>
     <row r="1959">
@@ -46602,22 +46602,22 @@
         <v>45421</v>
       </c>
       <c r="B1959" t="n">
-        <v>3.737026608509533</v>
+        <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.431715327957519</v>
+        <v>2.4039445077979</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.233191432955207</v>
+        <v>-3.428379654635008</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.138082330461688</v>
+        <v>1.032236221630149</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.5205471538529538</v>
+        <v>0.2292226072852235</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.744043620269291</v>
+        <v>2.541478072169034</v>
       </c>
     </row>
     <row r="1960">
@@ -46625,22 +46625,22 @@
         <v>45422</v>
       </c>
       <c r="B1960" t="n">
-        <v>3.702309454760808</v>
+        <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.43091924985402</v>
+        <v>2.403148429694401</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.33438921439238</v>
+        <v>-3.529577436072181</v>
       </c>
       <c r="E1960" t="n">
-        <v>1.096807139783321</v>
+        <v>0.9909610309517816</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.4521383403076346</v>
+        <v>0.1608137937399043</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.702202254038601</v>
+        <v>2.499636705938344</v>
       </c>
     </row>
     <row r="1961">
@@ -46648,22 +46648,22 @@
         <v>45423</v>
       </c>
       <c r="B1961" t="n">
-        <v>3.705571661815452</v>
+        <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.428519211408337</v>
+        <v>2.400748391248718</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.327878247778068</v>
+        <v>-3.523066469457868</v>
       </c>
       <c r="E1961" t="n">
-        <v>1.097011487983362</v>
+        <v>0.9911653791518233</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.4521383403076346</v>
+        <v>0.1608137937399043</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.699802215592918</v>
+        <v>2.497236667492661</v>
       </c>
     </row>
     <row r="1962">
@@ -46671,22 +46671,22 @@
         <v>45424</v>
       </c>
       <c r="B1962" t="n">
-        <v>3.709510443378097</v>
+        <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.425043930616582</v>
+        <v>2.397273110456963</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.30884012007077</v>
+        <v>-3.504028341750571</v>
       </c>
       <c r="E1962" t="n">
-        <v>1.101151458274526</v>
+        <v>0.9953053494429873</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.3939547289764401</v>
+        <v>0.1026301824087097</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.661416768002446</v>
+        <v>2.458851219902189</v>
       </c>
     </row>
     <row r="1963">
@@ -46694,22 +46694,22 @@
         <v>45425</v>
       </c>
       <c r="B1963" t="n">
-        <v>3.731064473131246</v>
+        <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.602625799555262</v>
+        <v>2.574854979395643</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.339966751221388</v>
+        <v>-3.535154972901189</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.26628267475296</v>
+        <v>1.160436565921421</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.3939547289764401</v>
+        <v>0.1026301824087097</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.838998636941127</v>
+        <v>2.63643308884087</v>
       </c>
     </row>
     <row r="1964">
@@ -46717,22 +46717,22 @@
         <v>45426</v>
       </c>
       <c r="B1964" t="n">
-        <v>3.722447362067862</v>
+        <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.603459128541396</v>
+        <v>2.575688308381777</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.353833512555306</v>
+        <v>-3.549021734235106</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.261569299205526</v>
+        <v>1.155723190373987</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.3560968122426171</v>
+        <v>0.06477226567488681</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.817117215886966</v>
+        <v>2.614551667786709</v>
       </c>
     </row>
     <row r="1965">
@@ -46740,22 +46740,22 @@
         <v>45427</v>
       </c>
       <c r="B1965" t="n">
-        <v>3.787425580789119</v>
+        <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.609467658938322</v>
+        <v>2.581696838778703</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.309029341015376</v>
+        <v>-3.504217562695176</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.285499498218424</v>
+        <v>1.179653389386885</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.3560968122426171</v>
+        <v>0.06477226567488681</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.823125746283892</v>
+        <v>2.620560198183635</v>
       </c>
     </row>
     <row r="1966">
@@ -46763,22 +46763,22 @@
         <v>45428</v>
       </c>
       <c r="B1966" t="n">
-        <v>3.781501250519904</v>
+        <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.507417880215521</v>
+        <v>2.479647060055902</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.161286370780374</v>
+        <v>-3.356474592460174</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.242546907589624</v>
+        <v>1.136700798758085</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.5239041694775003</v>
+        <v>0.23257962290977</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.821760381902021</v>
+        <v>2.619194833801765</v>
       </c>
     </row>
     <row r="1967">
@@ -46786,22 +46786,22 @@
         <v>45429</v>
       </c>
       <c r="B1967" t="n">
-        <v>3.802245929181165</v>
+        <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.510211501747002</v>
+        <v>2.482440681587383</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.263301053311594</v>
+        <v>-3.458489274991395</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.204534656108617</v>
+        <v>1.098688547277078</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.5239041694775003</v>
+        <v>0.23257962290977</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.824554003433502</v>
+        <v>2.621988455333246</v>
       </c>
     </row>
     <row r="1968">
@@ -46809,22 +46809,22 @@
         <v>45430</v>
       </c>
       <c r="B1968" t="n">
-        <v>3.805608985394724</v>
+        <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.51087385013866</v>
+        <v>2.483103029979042</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.25714834725881</v>
+        <v>-3.452336568938611</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.207658086921389</v>
+        <v>1.10181197808985</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.5300568755302846</v>
+        <v>0.2387323289625543</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.828907975456831</v>
+        <v>2.626342427356575</v>
       </c>
     </row>
     <row r="1969">
@@ -46832,22 +46832,22 @@
         <v>45431</v>
       </c>
       <c r="B1969" t="n">
-        <v>3.798239794890605</v>
+        <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.509954326878771</v>
+        <v>2.482183506719152</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.273957645409312</v>
+        <v>-3.469145867089112</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.200014844401299</v>
+        <v>1.09416873556976</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.5132475773797829</v>
+        <v>0.2219230308120526</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.817902873306641</v>
+        <v>2.615337325206384</v>
       </c>
     </row>
     <row r="1970">
@@ -46855,22 +46855,22 @@
         <v>45432</v>
       </c>
       <c r="B1970" t="n">
-        <v>3.867362636798422</v>
+        <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.576289880675592</v>
+        <v>2.548519060515973</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.21165964663319</v>
+        <v>-3.40684786831299</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.291269597708568</v>
+        <v>1.185423488877029</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.5132475773797829</v>
+        <v>0.2219230308120526</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.884238427103462</v>
+        <v>2.681672879003205</v>
       </c>
     </row>
     <row r="1971">
@@ -46878,22 +46878,22 @@
         <v>45433</v>
       </c>
       <c r="B1971" t="n">
-        <v>3.848729139992186</v>
+        <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.378581882389719</v>
+        <v>2.3508110622301</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.009869448968032</v>
+        <v>-3.205057670647832</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.174277678488759</v>
+        <v>1.06843156965722</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.7112657695489373</v>
+        <v>0.419941222981207</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.805341344119081</v>
+        <v>2.602775796018824</v>
       </c>
     </row>
     <row r="1972">
@@ -46901,22 +46901,22 @@
         <v>45434</v>
       </c>
       <c r="B1972" t="n">
-        <v>3.84144481785242</v>
+        <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.448872114711894</v>
+        <v>2.421101294552275</v>
       </c>
       <c r="D1972" t="n">
-        <v>-2.845056445889185</v>
+        <v>-3.040244667568985</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.310493112042473</v>
+        <v>1.204647003210934</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.8760787726277842</v>
+        <v>0.584754226060054</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.974519378288565</v>
+        <v>2.771953830188308</v>
       </c>
     </row>
     <row r="1973">
@@ -46924,22 +46924,22 @@
         <v>45435</v>
       </c>
       <c r="B1973" t="n">
-        <v>3.81906330031954</v>
+        <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.463499850827938</v>
+        <v>2.435729030668319</v>
       </c>
       <c r="D1973" t="n">
-        <v>-2.942796990514159</v>
+        <v>-3.13798521219396</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.286024630308527</v>
+        <v>1.180178521476988</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.8601894944948041</v>
+        <v>0.5688649479270738</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.97961354752482</v>
+        <v>2.777047999424563</v>
       </c>
     </row>
     <row r="1974">
@@ -46947,22 +46947,22 @@
         <v>45436</v>
       </c>
       <c r="B1974" t="n">
-        <v>3.831819032489379</v>
+        <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.462035831652609</v>
+        <v>2.43426501149299</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.119134750637088</v>
+        <v>-3.314322972316889</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.214025507084027</v>
+        <v>1.108179398252488</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.6838517343718746</v>
+        <v>0.3925271878041444</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.872346872275734</v>
+        <v>2.669781324175478</v>
       </c>
     </row>
     <row r="1975">
@@ -46970,22 +46970,22 @@
         <v>45437</v>
       </c>
       <c r="B1975" t="n">
-        <v>3.836411672397789</v>
+        <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.460527449692538</v>
+        <v>2.432756629532919</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.042712704205162</v>
+        <v>-3.237900925884962</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.243085943696726</v>
+        <v>1.137239834865187</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.6838517343718746</v>
+        <v>0.3925271878041444</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.870838490315663</v>
+        <v>2.668272942215406</v>
       </c>
     </row>
     <row r="1976">
@@ -46993,22 +46993,22 @@
         <v>45438</v>
       </c>
       <c r="B1976" t="n">
-        <v>3.833513460316244</v>
+        <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.460390317127974</v>
+        <v>2.432619496968355</v>
       </c>
       <c r="D1976" t="n">
-        <v>-2.998339572566593</v>
+        <v>-3.193527794246394</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.26069806378759</v>
+        <v>1.154851954956051</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.7282248660104432</v>
+        <v>0.436900319442713</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.89732523673424</v>
+        <v>2.694759688633983</v>
       </c>
     </row>
     <row r="1977">
@@ -47016,22 +47016,22 @@
         <v>45439</v>
       </c>
       <c r="B1977" t="n">
-        <v>3.821562117105961</v>
+        <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.454784111266564</v>
+        <v>2.427013291106946</v>
       </c>
       <c r="D1977" t="n">
-        <v>-2.875505351679426</v>
+        <v>-3.070693573359226</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.304225546281047</v>
+        <v>1.198379437449508</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.7282248660104432</v>
+        <v>0.436900319442713</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.891719030872831</v>
+        <v>2.689153482772574</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190319</v>
+        <v>3.833011148190324</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.461165868294369</v>
+        <v>2.43339504813475</v>
       </c>
       <c r="D1978" t="n">
-        <v>-2.82784962111837</v>
+        <v>-3.02303784279817</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.329669595533274</v>
+        <v>1.223823486701735</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.7758805965714989</v>
+        <v>0.4845560500037686</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.926694226237269</v>
+        <v>2.724128678137012</v>
       </c>
     </row>
     <row r="1979">
@@ -47062,22 +47062,22 @@
         <v>45441</v>
       </c>
       <c r="B1979" t="n">
-        <v>3.82267821056961</v>
+        <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.466058241669094</v>
+        <v>2.438287421509475</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.727331462619615</v>
+        <v>-2.922519684299416</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.374769232307501</v>
+        <v>1.268923123475962</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.8763987550702534</v>
+        <v>0.5850742085025231</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.991897494711246</v>
+        <v>2.789331946610989</v>
       </c>
     </row>
     <row r="1980">
@@ -47085,22 +47085,22 @@
         <v>45442</v>
       </c>
       <c r="B1980" t="n">
-        <v>3.828808877557286</v>
+        <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.452812914144966</v>
+        <v>2.425042093985347</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.787998053022004</v>
+        <v>-2.983186274701805</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.337257268622417</v>
+        <v>1.231411159790878</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.7947004383517198</v>
+        <v>0.5033758917839894</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.929633177155998</v>
+        <v>2.727067629055741</v>
       </c>
     </row>
     <row r="1981">
@@ -47108,22 +47108,22 @@
         <v>45443</v>
       </c>
       <c r="B1981" t="n">
-        <v>3.816837033932762</v>
+        <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.456910616755595</v>
+        <v>2.429139796595976</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.743159651413606</v>
+        <v>-2.938347873093407</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.359290331876405</v>
+        <v>1.253444223044866</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.7992438712965892</v>
+        <v>0.5079193247288589</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.936456939533548</v>
+        <v>2.733891391433292</v>
       </c>
     </row>
     <row r="1982">
@@ -47131,22 +47131,22 @@
         <v>45444</v>
       </c>
       <c r="B1982" t="n">
-        <v>3.817932354917045</v>
+        <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.461071556386673</v>
+        <v>2.433300736227054</v>
       </c>
       <c r="D1982" t="n">
-        <v>-2.843918287170605</v>
+        <v>-3.039106508850405</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.323147817204684</v>
+        <v>1.217301708373145</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.7104183025695838</v>
+        <v>0.4190937560018535</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.887322537928423</v>
+        <v>2.684756989828166</v>
       </c>
     </row>
     <row r="1983">
@@ -47154,22 +47154,22 @@
         <v>45445</v>
       </c>
       <c r="B1983" t="n">
-        <v>3.826684745405953</v>
+        <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.46695115891451</v>
+        <v>2.439180338754891</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.799715450084704</v>
+        <v>-2.994903671764505</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.346708554566881</v>
+        <v>1.240862445735342</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.7546211396554843</v>
+        <v>0.4632965930877539</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.919723842707801</v>
+        <v>2.717158294607544</v>
       </c>
     </row>
     <row r="1984">
@@ -47177,22 +47177,22 @@
         <v>45446</v>
       </c>
       <c r="B1984" t="n">
-        <v>3.838199629265639</v>
+        <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.465361159383757</v>
+        <v>2.437590339224139</v>
       </c>
       <c r="D1984" t="n">
-        <v>-2.836694477748147</v>
+        <v>-3.031882699427948</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.330326943970751</v>
+        <v>1.224480835139212</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.7915950414468148</v>
+        <v>0.5002704948790845</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.940318184251847</v>
+        <v>2.73775263615159</v>
       </c>
     </row>
     <row r="1985">
@@ -47200,22 +47200,22 @@
         <v>45447</v>
       </c>
       <c r="B1985" t="n">
-        <v>3.863895080284873</v>
+        <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.516608924566797</v>
+        <v>2.488838104407178</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.678403060208875</v>
+        <v>-2.873591281888676</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.4448912761695</v>
+        <v>1.339045167337961</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.7915950414468148</v>
+        <v>0.5002704948790845</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.991565949434886</v>
+        <v>2.789000401334629</v>
       </c>
     </row>
     <row r="1986">
@@ -47223,22 +47223,22 @@
         <v>45448</v>
       </c>
       <c r="B1986" t="n">
-        <v>3.865338681321015</v>
+        <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.51504962916105</v>
+        <v>2.487278809001432</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.470761056574399</v>
+        <v>-2.6659492782542</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.526388782217543</v>
+        <v>1.420542673386004</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.9992370450812911</v>
+        <v>0.7079124985135606</v>
       </c>
       <c r="G1986" t="n">
-        <v>3.114591856209825</v>
+        <v>2.912026308109568</v>
       </c>
     </row>
     <row r="1987">
@@ -47246,22 +47246,22 @@
         <v>45449</v>
       </c>
       <c r="B1987" t="n">
-        <v>3.864489842475131</v>
+        <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.50999785739932</v>
+        <v>2.482227037239702</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.419728963851871</v>
+        <v>-2.614917185531672</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.541749847544825</v>
+        <v>1.435903738713286</v>
       </c>
       <c r="F1987" t="n">
-        <v>1.050269137803819</v>
+        <v>0.7589445912360886</v>
       </c>
       <c r="G1987" t="n">
-        <v>3.140159340081612</v>
+        <v>2.937593791981355</v>
       </c>
     </row>
     <row r="1988">
@@ -47269,22 +47269,22 @@
         <v>45450</v>
       </c>
       <c r="B1988" t="n">
-        <v>3.842547360404846</v>
+        <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.527185261492025</v>
+        <v>2.499414441332406</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.354504782724665</v>
+        <v>-2.549693004404466</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.585026924088412</v>
+        <v>1.479180815256873</v>
       </c>
       <c r="F1988" t="n">
-        <v>1.115493318931025</v>
+        <v>0.8241687723632942</v>
       </c>
       <c r="G1988" t="n">
-        <v>3.19648125285064</v>
+        <v>2.993915704750383</v>
       </c>
     </row>
     <row r="1989">
@@ -47292,22 +47292,22 @@
         <v>45451</v>
       </c>
       <c r="B1989" t="n">
-        <v>3.840061186882551</v>
+        <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.523146233791306</v>
+        <v>2.495375413631687</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.317077762653531</v>
+        <v>-2.512265984333332</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.595958704416146</v>
+        <v>1.490112595584607</v>
       </c>
       <c r="F1989" t="n">
-        <v>1.120744856960207</v>
+        <v>0.8294203103924759</v>
       </c>
       <c r="G1989" t="n">
-        <v>3.19559314796743</v>
+        <v>2.993027599867172</v>
       </c>
     </row>
     <row r="1990">
@@ -47315,22 +47315,22 @@
         <v>45452</v>
       </c>
       <c r="B1990" t="n">
-        <v>3.845169808992654</v>
+        <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.524403026122546</v>
+        <v>2.496632205962927</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.33718941868824</v>
+        <v>-2.53237764036804</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.589170834333503</v>
+        <v>1.483324725501964</v>
       </c>
       <c r="F1990" t="n">
-        <v>1.131772201957626</v>
+        <v>0.8404476553898951</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.203466347297121</v>
+        <v>3.000900799196864</v>
       </c>
     </row>
     <row r="1991">
@@ -47338,22 +47338,22 @@
         <v>45453</v>
       </c>
       <c r="B1991" t="n">
-        <v>3.82866144563628</v>
+        <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.684960797143757</v>
+        <v>2.657189976984138</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.283444604261035</v>
+        <v>-2.478632825940835</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.771226531125595</v>
+        <v>1.665380422294056</v>
       </c>
       <c r="F1991" t="n">
-        <v>1.141835511398088</v>
+        <v>0.850510964830357</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.37006210398261</v>
+        <v>3.167496555882352</v>
       </c>
     </row>
     <row r="1992">
@@ -47361,22 +47361,22 @@
         <v>45454</v>
       </c>
       <c r="B1992" t="n">
-        <v>3.813222820957618</v>
+        <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.805073706361574</v>
+        <v>2.777302886201955</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.208662343236022</v>
+        <v>-2.403850564915823</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.921252344753418</v>
+        <v>1.815406235921879</v>
       </c>
       <c r="F1992" t="n">
-        <v>1.2166177724231</v>
+        <v>0.9252932258553697</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.535044369815434</v>
+        <v>3.332478821715177</v>
       </c>
     </row>
     <row r="1993">
@@ -47384,22 +47384,22 @@
         <v>45455</v>
       </c>
       <c r="B1993" t="n">
-        <v>3.814230727998748</v>
+        <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.796781682375433</v>
+        <v>2.769010862215814</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.182578258972214</v>
+        <v>-2.377766480652015</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.9233939544728</v>
+        <v>1.817547845641261</v>
       </c>
       <c r="F1993" t="n">
-        <v>1.2166177724231</v>
+        <v>0.9252932258553697</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.526752345829293</v>
+        <v>3.324186797729036</v>
       </c>
     </row>
     <row r="1994">
@@ -47407,22 +47407,22 @@
         <v>45456</v>
       </c>
       <c r="B1994" t="n">
-        <v>3.80339781889692</v>
+        <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.794974877959212</v>
+        <v>2.767204057799594</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.36247397184413</v>
+        <v>-2.299635299803068</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.849628864907813</v>
+        <v>1.846993513564619</v>
       </c>
       <c r="F1994" t="n">
-        <v>1.249027558718284</v>
+        <v>0.9994700367390541</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.544391413190183</v>
+        <v>3.366886079843026</v>
       </c>
     </row>
     <row r="1995">
@@ -47430,22 +47430,22 @@
         <v>45457</v>
       </c>
       <c r="B1995" t="n">
-        <v>3.79626414395985</v>
+        <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.812529283686004</v>
+        <v>2.784758463526385</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.353581510450847</v>
+        <v>-2.290742838409785</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.870740255191917</v>
+        <v>1.868104903848724</v>
       </c>
       <c r="F1995" t="n">
-        <v>1.249027558718284</v>
+        <v>0.9994700367390541</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.561945818916974</v>
+        <v>3.384440485569818</v>
       </c>
     </row>
     <row r="1996">
@@ -47453,22 +47453,22 @@
         <v>45458</v>
       </c>
       <c r="B1996" t="n">
-        <v>3.79442494194536</v>
+        <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.804384331090588</v>
+        <v>2.776613510930969</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.522057627420725</v>
+        <v>-2.459218955379663</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.79520485580855</v>
+        <v>1.792569504465356</v>
       </c>
       <c r="F1996" t="n">
-        <v>1.221079723001703</v>
+        <v>0.9715222010224733</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.53703216489161</v>
+        <v>3.359526831544453</v>
       </c>
     </row>
     <row r="1997">
@@ -47476,22 +47476,22 @@
         <v>45459</v>
       </c>
       <c r="B1997" t="n">
-        <v>3.795574066782701</v>
+        <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.785654028278449</v>
+        <v>2.757883208118831</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.824258098559142</v>
+        <v>-1.76141942651808</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.055594364541045</v>
+        <v>2.052959013197852</v>
       </c>
       <c r="F1997" t="n">
-        <v>1.150731663631292</v>
+        <v>0.9011741416520627</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.476093026457225</v>
+        <v>3.298587693110068</v>
       </c>
     </row>
     <row r="1998">
@@ -47499,22 +47499,22 @@
         <v>45460</v>
       </c>
       <c r="B1998" t="n">
-        <v>3.78467134563263</v>
+        <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.776318050775354</v>
+        <v>2.748547230615735</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.801536994875989</v>
+        <v>-1.738698322834927</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.055346828511211</v>
+        <v>2.052711477168017</v>
       </c>
       <c r="F1998" t="n">
-        <v>1.150731663631292</v>
+        <v>0.9011741416520627</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.46675704895413</v>
+        <v>3.289251715606973</v>
       </c>
     </row>
     <row r="1999">
@@ -47522,22 +47522,22 @@
         <v>45461</v>
       </c>
       <c r="B1999" t="n">
-        <v>3.783205696777666</v>
+        <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.935224176626523</v>
+        <v>2.907453356466904</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.799811951585945</v>
+        <v>-1.736973279544883</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.214942971678397</v>
+        <v>2.212307620335204</v>
       </c>
       <c r="F1999" t="n">
-        <v>1.152456706921336</v>
+        <v>0.9028991849421064</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.626698200779325</v>
+        <v>3.449192867432168</v>
       </c>
     </row>
     <row r="2000">
@@ -47545,22 +47545,22 @@
         <v>45462</v>
       </c>
       <c r="B2000" t="n">
-        <v>3.779933725644406</v>
+        <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.97230199912017</v>
+        <v>2.944531178960551</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.954592958364201</v>
+        <v>-1.891754286323139</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.190108391460742</v>
+        <v>2.187473040117548</v>
       </c>
       <c r="F2000" t="n">
-        <v>1.11908903286686</v>
+        <v>0.8695315108876303</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.643755418840286</v>
+        <v>3.466250085493129</v>
       </c>
     </row>
     <row r="2001">
@@ -47568,22 +47568,22 @@
         <v>45463</v>
       </c>
       <c r="B2001" t="n">
-        <v>3.769443619799955</v>
+        <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.968977355109715</v>
+        <v>2.941206534950096</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.947538268149027</v>
+        <v>-1.884699596107965</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.189605623536357</v>
+        <v>2.186970272193163</v>
       </c>
       <c r="F2001" t="n">
-        <v>1.126143723082033</v>
+        <v>0.8765862011028041</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.644663588958935</v>
+        <v>3.467158255611779</v>
       </c>
     </row>
     <row r="2002">
@@ -47591,22 +47591,22 @@
         <v>45464</v>
       </c>
       <c r="B2002" t="n">
-        <v>3.76667349633111</v>
+        <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.978983508754456</v>
+        <v>2.951212688594838</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.920587043822539</v>
+        <v>-1.857748371781477</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.210392266911693</v>
+        <v>2.2077569155685</v>
       </c>
       <c r="F2002" t="n">
-        <v>1.141024069109753</v>
+        <v>0.8914665471305232</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.663597950220308</v>
+        <v>3.486092616873152</v>
       </c>
     </row>
     <row r="2003">
@@ -47614,22 +47614,22 @@
         <v>45465</v>
       </c>
       <c r="B2003" t="n">
-        <v>3.768052067784101</v>
+        <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.163086640899416</v>
+        <v>3.135315820739797</v>
       </c>
       <c r="D2003" t="n">
-        <v>-2.056540051878855</v>
+        <v>-1.993701379837793</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.340114195834127</v>
+        <v>2.337478844490933</v>
       </c>
       <c r="F2003" t="n">
-        <v>1.141024069109753</v>
+        <v>0.8914665471305232</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.847701082365268</v>
+        <v>3.670195749018112</v>
       </c>
     </row>
     <row r="2004">
@@ -47637,22 +47637,22 @@
         <v>45466</v>
       </c>
       <c r="B2004" t="n">
-        <v>3.743925505714419</v>
+        <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.155203335802409</v>
+        <v>3.12743251564279</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.078948169683727</v>
+        <v>-2.016109497642665</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.323267643615171</v>
+        <v>2.320632292271977</v>
       </c>
       <c r="F2004" t="n">
-        <v>1.141024069109753</v>
+        <v>0.8914665471305232</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.839817777268261</v>
+        <v>3.662312443921105</v>
       </c>
     </row>
     <row r="2005">
@@ -47660,22 +47660,22 @@
         <v>45467</v>
       </c>
       <c r="B2005" t="n">
-        <v>3.719118627155026</v>
+        <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.157257335352047</v>
+        <v>3.129486515192428</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.222633902241719</v>
+        <v>-2.164115265122065</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.267847350141612</v>
+        <v>2.263483984829855</v>
       </c>
       <c r="F2005" t="n">
-        <v>1.103745700188279</v>
+        <v>0.8047395382669817</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.819504755465014</v>
+        <v>3.612330238152617</v>
       </c>
     </row>
     <row r="2006">
@@ -47683,22 +47683,22 @@
         <v>45468</v>
       </c>
       <c r="B2006" t="n">
-        <v>3.729452285161971</v>
+        <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.213511053073894</v>
+        <v>3.185740232914275</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.232074828130249</v>
+        <v>-2.173556191010594</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.320324697508047</v>
+        <v>2.31596133219629</v>
       </c>
       <c r="F2006" t="n">
-        <v>1.22617281773167</v>
+        <v>0.9271666558103732</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.949214743712896</v>
+        <v>3.742040226400499</v>
       </c>
     </row>
     <row r="2007">
@@ -47706,22 +47706,22 @@
         <v>45469</v>
       </c>
       <c r="B2007" t="n">
-        <v>3.714941193321628</v>
+        <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.216402147619195</v>
+        <v>3.188631327459576</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.28434843546589</v>
+        <v>-2.225829798346236</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.302306349119092</v>
+        <v>2.297942983807334</v>
       </c>
       <c r="F2007" t="n">
-        <v>1.173899210396029</v>
+        <v>0.8748930484747319</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.920741673856813</v>
+        <v>3.713567156544415</v>
       </c>
     </row>
     <row r="2008">
@@ -47729,22 +47729,22 @@
         <v>45470</v>
       </c>
       <c r="B2008" t="n">
-        <v>3.727898186347696</v>
+        <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.21451396051297</v>
+        <v>3.186743140353351</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.360678413066796</v>
+        <v>-2.302159775947142</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.269886170972504</v>
+        <v>2.265522805660747</v>
       </c>
       <c r="F2008" t="n">
-        <v>1.173899210396029</v>
+        <v>0.8748930484747319</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.918853486750588</v>
+        <v>3.71167896943819</v>
       </c>
     </row>
     <row r="2009">
@@ -47752,22 +47752,22 @@
         <v>45471</v>
       </c>
       <c r="B2009" t="n">
-        <v>3.71065410488774</v>
+        <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.209334190115832</v>
+        <v>3.181563369956213</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.472435365682097</v>
+        <v>-2.413916728562443</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.220003619529246</v>
+        <v>2.215640254217489</v>
       </c>
       <c r="F2009" t="n">
-        <v>1.062142257780728</v>
+        <v>0.7631360958594309</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.846619544784269</v>
+        <v>3.639445027471872</v>
       </c>
     </row>
     <row r="2010">
@@ -47775,22 +47775,22 @@
         <v>45472</v>
       </c>
       <c r="B2010" t="n">
-        <v>3.712897612343058</v>
+        <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.207768200325984</v>
+        <v>3.179997380166366</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.470594346623846</v>
+        <v>-2.412075709504192</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.219174037362699</v>
+        <v>2.214810672050942</v>
       </c>
       <c r="F2010" t="n">
-        <v>1.063410484452196</v>
+        <v>0.7644043225308993</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.845814490997302</v>
+        <v>3.638639973684906</v>
       </c>
     </row>
     <row r="2011">
@@ -47798,22 +47798,22 @@
         <v>45473</v>
       </c>
       <c r="B2011" t="n">
-        <v>3.754911907647098</v>
+        <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.220841607191903</v>
+        <v>3.193070787032284</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.602895638721399</v>
+        <v>-2.544377001601745</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.179326927389596</v>
+        <v>2.174963562077839</v>
       </c>
       <c r="F2011" t="n">
-        <v>1.063410484452196</v>
+        <v>0.7644043225308993</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.858887897863221</v>
+        <v>3.651713380550824</v>
       </c>
     </row>
     <row r="2012">
@@ -47821,22 +47821,22 @@
         <v>45474</v>
       </c>
       <c r="B2012" t="n">
-        <v>3.749896851763524</v>
+        <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.220841607191903</v>
+        <v>3.193070787032284</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.604457281536259</v>
+        <v>-2.545938644416605</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.178702270263652</v>
+        <v>2.174338904951895</v>
       </c>
       <c r="F2012" t="n">
-        <v>1.063410484452196</v>
+        <v>0.7644043225308993</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.858887897863221</v>
+        <v>3.651713380550824</v>
       </c>
     </row>
     <row r="2013">
@@ -47844,22 +47844,22 @@
         <v>45475</v>
       </c>
       <c r="B2013" t="n">
-        <v>3.715834055392107</v>
+        <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.219365648318905</v>
+        <v>3.191594828159286</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.632358068645732</v>
+        <v>-2.573839431526078</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.166065996546865</v>
+        <v>2.161702631235108</v>
       </c>
       <c r="F2013" t="n">
-        <v>1.028813560309262</v>
+        <v>0.7298073983879645</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.836653784504462</v>
+        <v>3.629479267192065</v>
       </c>
     </row>
     <row r="2014">
@@ -47867,22 +47867,22 @@
         <v>45476</v>
       </c>
       <c r="B2014" t="n">
-        <v>3.684909939172519</v>
+        <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.216130092296104</v>
+        <v>3.188359272136485</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.635391066158406</v>
+        <v>-2.576872429038752</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.161617241518994</v>
+        <v>2.157253876207237</v>
       </c>
       <c r="F2014" t="n">
-        <v>1.025780562796588</v>
+        <v>0.7267744008752905</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.831598429974057</v>
+        <v>3.62442391266166</v>
       </c>
     </row>
     <row r="2015">
@@ -47890,22 +47890,22 @@
         <v>45477</v>
       </c>
       <c r="B2015" t="n">
-        <v>3.619362241971072</v>
+        <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.282836051886608</v>
+        <v>3.255065231726989</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.655452387434913</v>
+        <v>-2.596933750315259</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.220298672598895</v>
+        <v>2.215935307287138</v>
       </c>
       <c r="F2015" t="n">
-        <v>1.005719241520081</v>
+        <v>0.7067130795987835</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.886267596798656</v>
+        <v>3.679093079486259</v>
       </c>
     </row>
     <row r="2016">
@@ -47913,22 +47913,22 @@
         <v>45478</v>
       </c>
       <c r="B2016" t="n">
-        <v>3.640764248199798</v>
+        <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.423147770888455</v>
+        <v>3.395376950728836</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.912173205429737</v>
+        <v>-2.853654568310083</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.257922064402813</v>
+        <v>2.253558699091055</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.8973046673762658</v>
+        <v>0.5982985054549687</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.961530571314214</v>
+        <v>3.754356054001817</v>
       </c>
     </row>
     <row r="2017">
@@ -47936,22 +47936,22 @@
         <v>45479</v>
       </c>
       <c r="B2017" t="n">
-        <v>3.668303164622229</v>
+        <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.492128040034094</v>
+        <v>3.464357219874476</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.066159623205877</v>
+        <v>-3.007640986086223</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.265307766437996</v>
+        <v>2.260944401126239</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.8973046673762658</v>
+        <v>0.5982985054549687</v>
       </c>
       <c r="G2017" t="n">
-        <v>4.030510840459854</v>
+        <v>3.823336323147457</v>
       </c>
     </row>
     <row r="2018">
@@ -47959,22 +47959,22 @@
         <v>45480</v>
       </c>
       <c r="B2018" t="n">
-        <v>3.619937176808522</v>
+        <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.478179242154215</v>
+        <v>3.450408421994597</v>
       </c>
       <c r="D2018" t="n">
-        <v>-3.015637719378212</v>
+        <v>-2.957119082258557</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.271567730089183</v>
+        <v>2.267204364777426</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.8973046673762658</v>
+        <v>0.5982985054549687</v>
       </c>
       <c r="G2018" t="n">
-        <v>4.016562042579975</v>
+        <v>3.809387525267578</v>
       </c>
     </row>
     <row r="2019">
@@ -47982,22 +47982,22 @@
         <v>45481</v>
       </c>
       <c r="B2019" t="n">
-        <v>3.656346893994887</v>
+        <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.490049731209629</v>
+        <v>3.462278911050011</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.268112873385936</v>
+        <v>-3.209594236266282</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.182448157541507</v>
+        <v>2.17808479222975</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.8973046673762658</v>
+        <v>0.5982985054549687</v>
       </c>
       <c r="G2019" t="n">
-        <v>4.028432531635389</v>
+        <v>3.821258014322992</v>
       </c>
     </row>
     <row r="2020">
@@ -48005,22 +48005,22 @@
         <v>45482</v>
       </c>
       <c r="B2020" t="n">
-        <v>3.67404269635829</v>
+        <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.491260265728573</v>
+        <v>3.463489445568954</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.537585675307644</v>
+        <v>-3.47906703818799</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.075869571291768</v>
+        <v>2.071506205980011</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.8973046673762658</v>
+        <v>0.5982985054549687</v>
       </c>
       <c r="G2020" t="n">
-        <v>4.029643066154333</v>
+        <v>3.822468548841936</v>
       </c>
     </row>
     <row r="2021">
@@ -48028,22 +48028,22 @@
         <v>45483</v>
       </c>
       <c r="B2021" t="n">
-        <v>3.663523617637079</v>
+        <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.495382007955894</v>
+        <v>3.467611187796276</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.695129747037086</v>
+        <v>-3.636611109917431</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.016973684827313</v>
+        <v>2.012610319515556</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.8304028622359914</v>
+        <v>0.5313967003146942</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.993623725297489</v>
+        <v>3.786449207985092</v>
       </c>
     </row>
     <row r="2022">
@@ -48051,22 +48051,22 @@
         <v>45484</v>
       </c>
       <c r="B2022" t="n">
-        <v>3.652163313301336</v>
+        <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.490459860692084</v>
+        <v>3.462689040532465</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.823980297739132</v>
+        <v>-3.765461660619478</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.960511317282684</v>
+        <v>1.956147951970927</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.7894094533852698</v>
+        <v>0.4904032914639727</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.964105532723246</v>
+        <v>3.756931015410849</v>
       </c>
     </row>
     <row r="2023">
@@ -48074,22 +48074,22 @@
         <v>45485</v>
       </c>
       <c r="B2023" t="n">
-        <v>3.667976467215462</v>
+        <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.652663917391128</v>
+        <v>3.624893097231509</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.940947990378023</v>
+        <v>-3.882429353258369</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.075928296926171</v>
+        <v>2.071564931614414</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.7894094533852698</v>
+        <v>0.4904032914639727</v>
       </c>
       <c r="G2023" t="n">
-        <v>4.12630958942229</v>
+        <v>3.919135072109893</v>
       </c>
     </row>
     <row r="2024">
@@ -48097,22 +48097,22 @@
         <v>45486</v>
       </c>
       <c r="B2024" t="n">
-        <v>3.696553628456685</v>
+        <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.647510555354942</v>
+        <v>3.619739735195323</v>
       </c>
       <c r="D2024" t="n">
-        <v>-4.025665932598977</v>
+        <v>-3.967147295479323</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.036887758001604</v>
+        <v>2.032524392689847</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.7042934244572234</v>
+        <v>0.4052872625359263</v>
       </c>
       <c r="G2024" t="n">
-        <v>4.070086610029277</v>
+        <v>3.862912092716879</v>
       </c>
     </row>
     <row r="2025">
@@ -48120,22 +48120,22 @@
         <v>45487</v>
       </c>
       <c r="B2025" t="n">
-        <v>3.750058176253281</v>
+        <v>3.750058176253286</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.657739972923433</v>
+        <v>3.629969152763814</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.10760075086786</v>
+        <v>-4.049082113748206</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.014343248262542</v>
+        <v>2.009979882950785</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.6943586788701432</v>
+        <v>0.3953525169488461</v>
       </c>
       <c r="G2025" t="n">
-        <v>4.07435518024552</v>
+        <v>3.867180662933122</v>
       </c>
     </row>
     <row r="2026">
@@ -48143,22 +48143,22 @@
         <v>45488</v>
       </c>
       <c r="B2026" t="n">
-        <v>3.783647027717825</v>
+        <v>3.78364702771783</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.666665611379336</v>
+        <v>3.638894791219717</v>
       </c>
       <c r="D2026" t="n">
-        <v>-4.053862577467598</v>
+        <v>-3.995343940347944</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.044764156078549</v>
+        <v>2.040400790766792</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.7480968522704053</v>
+        <v>0.4490906903491082</v>
       </c>
       <c r="G2026" t="n">
-        <v>4.115523722741579</v>
+        <v>3.908349205429182</v>
       </c>
     </row>
     <row r="2027">
@@ -48166,22 +48166,22 @@
         <v>45489</v>
       </c>
       <c r="B2027" t="n">
-        <v>3.798310944616941</v>
+        <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.658818498623511</v>
+        <v>3.631047678463892</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.943856293990376</v>
+        <v>-3.885337656870722</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.080919556713613</v>
+        <v>2.076556191401856</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.7713014241876806</v>
+        <v>0.4722952622663834</v>
       </c>
       <c r="G2027" t="n">
-        <v>4.121599353136119</v>
+        <v>3.914424835823723</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.785578085203655</v>
+        <v>3.470304620271417</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.663068509345485</v>
+        <v>3.635297689185867</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.469913355511006</v>
+        <v>-3.742278081129796</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.274746742827336</v>
+        <v>2.138030032420201</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.7133742735244937</v>
+        <v>0.4803086888563627</v>
       </c>
       <c r="G2028" t="n">
-        <v>4.091093073460182</v>
+        <v>3.923482902499685</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.859268879435188</v>
+        <v>3.470169176307394</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.709403299959951</v>
+        <v>3.642558572068403</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.469913355511006</v>
+        <v>-3.590122696647164</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.274746742827336</v>
+        <v>2.20615306909579</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.7133742735244937</v>
+        <v>0.4803086888563627</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.702467096946318</v>
+        <v>3.93074378538222</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240718.xlsx
+++ b/tame_output/ON/bt/strategyON_20240718.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>48.5%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,7 +633,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -681,7 +681,7 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.3%</t>
+          <t>-12.4%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>18.9%</t>
+          <t>18.3%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>79.1%</t>
+          <t>81.4%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,17 +791,17 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>37.4%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>61.7%</t>
+          <t>60.6%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>8.9%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-7.7%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>68.3%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>30.9%</t>
+          <t>31.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-7.5%</t>
+          <t>-7.7%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>59.8%</t>
         </is>
       </c>
     </row>
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-73.0%</t>
+          <t>-71.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>109.6%</t>
+          <t>109.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.65</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>96.6%</t>
+          <t>97.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>24.1%</t>
+          <t>24.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-49.0%</t>
+          <t>-48.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-68.4%</t>
+          <t>-66.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>90.8%</t>
+          <t>90.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.8</t>
+          <t>-0.7</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>454.8%</t>
+          <t>455.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-7.9%</t>
+          <t>-7.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-520.6%</t>
+          <t>-488.9%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>26.5%</t>
+          <t>30.9%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>56.2%</t>
+          <t>56.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.5%</t>
+          <t>57.6%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>62.9%</t>
+          <t>63.0%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>50.7%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>13.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-36.4%</t>
+          <t>-35.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>28.3%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>47.0%</t>
+          <t>47.2%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>77.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-10.0%</t>
+          <t>-12.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-155.6%</t>
+          <t>-135.8%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-14.9%</t>
+          <t>-8.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>65.2%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-0.13</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.8%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,17 +1265,17 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>64.0%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>68.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>99.4%</t>
+          <t>99.3%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>10.6%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-28.4%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-8.7%</t>
+          <t>-0.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>54.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-1.2%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-121.7%</t>
+          <t>-137.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-176.0%</t>
+          <t>-135.3%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>74.5%</t>
+          <t>84.3%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.6%</t>
+          <t>53.9%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,12 +1428,12 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>47.5%</t>
+          <t>48.3%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>94.1%</t>
+          <t>93.5%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-24.4%</t>
+          <t>-23.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>79.3%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.7%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.1%</t>
+          <t>-18.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.4%</t>
+          <t>34.1%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-52.9%</t>
+          <t>-21.4%</t>
         </is>
       </c>
     </row>
@@ -44791,16 +44791,16 @@
         <v>3.160174348233104</v>
       </c>
       <c r="D1880" t="n">
-        <v>-8.822165266762951</v>
+        <v>-8.640201116170417</v>
       </c>
       <c r="E1880" t="n">
-        <v>-0.3690481827858236</v>
+        <v>-0.29626252254881</v>
       </c>
       <c r="F1880" t="n">
-        <v>-1.70135759377859</v>
+        <v>-1.519393443186055</v>
       </c>
       <c r="G1880" t="n">
-        <v>2.13935979196595</v>
+        <v>2.248538282321471</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.174729568980621</v>
       </c>
       <c r="D1881" t="n">
-        <v>-8.997289684149495</v>
+        <v>-8.81532553355696</v>
       </c>
       <c r="E1881" t="n">
-        <v>-0.4245427289929244</v>
+        <v>-0.3517570687559104</v>
       </c>
       <c r="F1881" t="n">
-        <v>-1.876482011165134</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1881" t="n">
-        <v>2.048840362281541</v>
+        <v>2.158018852637062</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.167510404079025</v>
       </c>
       <c r="D1882" t="n">
-        <v>-9.231741778163984</v>
+        <v>-9.04977762757145</v>
       </c>
       <c r="E1882" t="n">
-        <v>-0.5255427315003161</v>
+        <v>-0.4527570712633024</v>
       </c>
       <c r="F1882" t="n">
-        <v>-1.876482011165134</v>
+        <v>-1.694517860572599</v>
       </c>
       <c r="G1882" t="n">
-        <v>2.041621197379945</v>
+        <v>2.150799687735466</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.160838213305049</v>
       </c>
       <c r="D1883" t="n">
-        <v>-9.336116509190431</v>
+        <v>-9.154152358597896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-0.5739648146848708</v>
+        <v>-0.5011791544478572</v>
       </c>
       <c r="F1883" t="n">
-        <v>-1.98085674219158</v>
+        <v>-1.798892591599045</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.972324167990101</v>
+        <v>2.081502658345622</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.161954003143605</v>
       </c>
       <c r="D1884" t="n">
-        <v>-9.388902664790757</v>
+        <v>-9.206938514198223</v>
       </c>
       <c r="E1884" t="n">
-        <v>-0.5939634870864454</v>
+        <v>-0.5211778268494314</v>
       </c>
       <c r="F1884" t="n">
-        <v>-2.076532228773977</v>
+        <v>-1.894568078181442</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.916034665879219</v>
+        <v>2.025213156234741</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.16464773177272</v>
       </c>
       <c r="D1885" t="n">
-        <v>-9.514939458159047</v>
+        <v>-9.332975307566512</v>
       </c>
       <c r="E1885" t="n">
-        <v>-0.6416844758046465</v>
+        <v>-0.5688988155676324</v>
       </c>
       <c r="F1885" t="n">
-        <v>-2.051280605964235</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1885" t="n">
-        <v>1.933879368194179</v>
+        <v>2.0430578585497</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.168638067459121</v>
       </c>
       <c r="D1886" t="n">
-        <v>-9.457867686263116</v>
+        <v>-9.275903535670581</v>
       </c>
       <c r="E1886" t="n">
-        <v>-0.6148654313598731</v>
+        <v>-0.5420797711228591</v>
       </c>
       <c r="F1886" t="n">
-        <v>-2.051280605964235</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1886" t="n">
-        <v>1.93786970388058</v>
+        <v>2.047048194236101</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.167162840560379</v>
       </c>
       <c r="D1887" t="n">
-        <v>-9.599539527987236</v>
+        <v>-9.417575377394702</v>
       </c>
       <c r="E1887" t="n">
-        <v>-0.673009394948263</v>
+        <v>-0.6002237347112489</v>
       </c>
       <c r="F1887" t="n">
-        <v>-2.051280605964235</v>
+        <v>-1.869316455371699</v>
       </c>
       <c r="G1887" t="n">
-        <v>1.936394476981838</v>
+        <v>2.045572967337359</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.182216250725251</v>
       </c>
       <c r="D1888" t="n">
-        <v>-9.549948683562402</v>
+        <v>-9.367984532969867</v>
       </c>
       <c r="E1888" t="n">
-        <v>-0.6381196470134571</v>
+        <v>-0.5653339867764431</v>
       </c>
       <c r="F1888" t="n">
-        <v>-2.001689761539401</v>
+        <v>-1.819725610946866</v>
       </c>
       <c r="G1888" t="n">
-        <v>1.981202393801611</v>
+        <v>2.090380884157132</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.169165117078568</v>
       </c>
       <c r="D1889" t="n">
-        <v>-9.401030349090545</v>
+        <v>-9.219066198498011</v>
       </c>
       <c r="E1889" t="n">
-        <v>-0.5916034468713973</v>
+        <v>-0.5188177866343833</v>
       </c>
       <c r="F1889" t="n">
-        <v>-1.970440170804228</v>
+        <v>-1.788476020211692</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.986901014596032</v>
+        <v>2.096079504951553</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.178744190114777</v>
       </c>
       <c r="D1890" t="n">
-        <v>-9.175185196371135</v>
+        <v>-8.993221045778601</v>
       </c>
       <c r="E1890" t="n">
-        <v>-0.4916863127474245</v>
+        <v>-0.4189006525104109</v>
       </c>
       <c r="F1890" t="n">
-        <v>-1.928513495217064</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1890" t="n">
-        <v>2.021636092984539</v>
+        <v>2.13081458334006</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.179883334670836</v>
       </c>
       <c r="D1891" t="n">
-        <v>-9.050606540033543</v>
+        <v>-8.868642389441009</v>
       </c>
       <c r="E1891" t="n">
-        <v>-0.4407157056563289</v>
+        <v>-0.3679300454193153</v>
       </c>
       <c r="F1891" t="n">
-        <v>-1.928513495217064</v>
+        <v>-1.746549344624529</v>
       </c>
       <c r="G1891" t="n">
-        <v>2.022775237540598</v>
+        <v>2.131953727896119</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.182517108832943</v>
       </c>
       <c r="D1892" t="n">
-        <v>-9.10350182807783</v>
+        <v>-8.921537677485295</v>
       </c>
       <c r="E1892" t="n">
-        <v>-0.459240046711936</v>
+        <v>-0.3864543864749219</v>
       </c>
       <c r="F1892" t="n">
-        <v>-1.923558149128618</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1892" t="n">
-        <v>2.028382219355773</v>
+        <v>2.137560709711294</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.18825081307158</v>
       </c>
       <c r="D1893" t="n">
-        <v>-9.031368652789949</v>
+        <v>-8.849404502197414</v>
       </c>
       <c r="E1893" t="n">
-        <v>-0.4246530723581472</v>
+        <v>-0.3518674121211331</v>
       </c>
       <c r="F1893" t="n">
-        <v>-1.923558149128618</v>
+        <v>-1.741593998536083</v>
       </c>
       <c r="G1893" t="n">
-        <v>2.03411592359441</v>
+        <v>2.14329441394993</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.178513550677715</v>
       </c>
       <c r="D1894" t="n">
-        <v>-8.960002260180302</v>
+        <v>-8.778038109587767</v>
       </c>
       <c r="E1894" t="n">
-        <v>-0.4058437777081534</v>
+        <v>-0.3330581174711393</v>
       </c>
       <c r="F1894" t="n">
-        <v>-1.85219175651897</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1894" t="n">
-        <v>2.067198496766333</v>
+        <v>2.176376987121854</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.168630069364807</v>
       </c>
       <c r="D1895" t="n">
-        <v>-8.866543226195077</v>
+        <v>-8.684579075602542</v>
       </c>
       <c r="E1895" t="n">
-        <v>-0.3783436454269711</v>
+        <v>-0.305557985189957</v>
       </c>
       <c r="F1895" t="n">
-        <v>-1.85219175651897</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1895" t="n">
-        <v>2.057315015453425</v>
+        <v>2.166493505808947</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.166795508865433</v>
       </c>
       <c r="D1896" t="n">
-        <v>-8.599301425326679</v>
+        <v>-8.417337274734145</v>
       </c>
       <c r="E1896" t="n">
-        <v>-0.2732814855789858</v>
+        <v>-0.2004958253419717</v>
       </c>
       <c r="F1896" t="n">
-        <v>-1.85219175651897</v>
+        <v>-1.670227605926435</v>
       </c>
       <c r="G1896" t="n">
-        <v>2.055480454954052</v>
+        <v>2.164658945309573</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.166495193891973</v>
       </c>
       <c r="D1897" t="n">
-        <v>-8.501394386650189</v>
+        <v>-8.319430236057654</v>
       </c>
       <c r="E1897" t="n">
-        <v>-0.2344189850818501</v>
+        <v>-0.1616333248448365</v>
       </c>
       <c r="F1897" t="n">
-        <v>-1.784206006658414</v>
+        <v>-1.602241856065878</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.095971589896925</v>
+        <v>2.205150080252446</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.167163700037466</v>
       </c>
       <c r="D1898" t="n">
-        <v>-8.477440845674231</v>
+        <v>-8.295476695081696</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.2241690625459736</v>
+        <v>-0.1513834023089595</v>
       </c>
       <c r="F1898" t="n">
-        <v>-1.760252465682456</v>
+        <v>-1.578288315089921</v>
       </c>
       <c r="G1898" t="n">
-        <v>2.111012220627993</v>
+        <v>2.220190710983514</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.153903383875714</v>
       </c>
       <c r="D1899" t="n">
-        <v>-8.213380907351434</v>
+        <v>-8.031416756758899</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.1318054033786069</v>
+        <v>-0.05901974314159286</v>
       </c>
       <c r="F1899" t="n">
-        <v>-1.49619252735966</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1899" t="n">
-        <v>2.256187867459919</v>
+        <v>2.365366357815439</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.151116350215413</v>
       </c>
       <c r="D1900" t="n">
-        <v>-7.506301283846596</v>
+        <v>-7.324337133254061</v>
       </c>
       <c r="E1900" t="n">
-        <v>0.1482394123630275</v>
+        <v>0.2210250726000416</v>
       </c>
       <c r="F1900" t="n">
-        <v>-1.49619252735966</v>
+        <v>-1.314228376767125</v>
       </c>
       <c r="G1900" t="n">
-        <v>2.253400833799618</v>
+        <v>2.362579324155138</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.151459974103255</v>
       </c>
       <c r="D1901" t="n">
-        <v>-7.466116985480405</v>
+        <v>-7.284152834887871</v>
       </c>
       <c r="E1901" t="n">
-        <v>0.1646567555973451</v>
+        <v>0.2374424158343591</v>
       </c>
       <c r="F1901" t="n">
-        <v>-1.456008228993469</v>
+        <v>-1.274044078400934</v>
       </c>
       <c r="G1901" t="n">
-        <v>2.277855036707173</v>
+        <v>2.387033527062695</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.150826795324011</v>
       </c>
       <c r="D1902" t="n">
-        <v>-7.302717114541043</v>
+        <v>-7.120752963948508</v>
       </c>
       <c r="E1902" t="n">
-        <v>0.229383525193847</v>
+        <v>0.302169185430861</v>
       </c>
       <c r="F1902" t="n">
-        <v>-1.292608358054106</v>
+        <v>-1.110644207461571</v>
       </c>
       <c r="G1902" t="n">
-        <v>2.375261780491548</v>
+        <v>2.484440270847069</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.158751224161864</v>
       </c>
       <c r="D1903" t="n">
-        <v>-7.069235892311444</v>
+        <v>-6.88727174171891</v>
       </c>
       <c r="E1903" t="n">
-        <v>0.330700442923539</v>
+        <v>0.4034861031605526</v>
       </c>
       <c r="F1903" t="n">
-        <v>-1.059127135824508</v>
+        <v>-0.8771629852319727</v>
       </c>
       <c r="G1903" t="n">
-        <v>2.523274942667159</v>
+        <v>2.632453433022681</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.155859013848905</v>
       </c>
       <c r="D1904" t="n">
-        <v>-6.919569501303929</v>
+        <v>-6.737605350711394</v>
       </c>
       <c r="E1904" t="n">
-        <v>0.3876747890135857</v>
+        <v>0.4604604492505997</v>
       </c>
       <c r="F1904" t="n">
-        <v>-0.9662236445819719</v>
+        <v>-0.7842594939894367</v>
       </c>
       <c r="G1904" t="n">
-        <v>2.576124827099722</v>
+        <v>2.685303317455243</v>
       </c>
     </row>
     <row r="1905">
@@ -45363,19 +45363,19 @@
         <v>3.763182248390428</v>
       </c>
       <c r="C1905" t="n">
-        <v>3.123455680436313</v>
+        <v>3.151226500595932</v>
       </c>
       <c r="D1905" t="n">
-        <v>-6.787294027673043</v>
+        <v>-6.605329877080508</v>
       </c>
       <c r="E1905" t="n">
-        <v>0.4081816450533484</v>
+        <v>0.5087381254499812</v>
       </c>
       <c r="F1905" t="n">
-        <v>-0.8339481709510852</v>
+        <v>-0.6519840203585501</v>
       </c>
       <c r="G1905" t="n">
-        <v>2.623086777865662</v>
+        <v>2.760036088380802</v>
       </c>
     </row>
     <row r="1906">
@@ -45386,19 +45386,19 @@
         <v>3.784718794105951</v>
       </c>
       <c r="C1906" t="n">
-        <v>3.12627074112395</v>
+        <v>3.154041561283568</v>
       </c>
       <c r="D1906" t="n">
-        <v>-6.631555695113301</v>
+        <v>-6.449591544520766</v>
       </c>
       <c r="E1906" t="n">
-        <v>0.4732920387648818</v>
+        <v>0.5738485191615146</v>
       </c>
       <c r="F1906" t="n">
-        <v>-0.6782098383913436</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1906" t="n">
-        <v>2.719344838089144</v>
+        <v>2.856294148604284</v>
       </c>
     </row>
     <row r="1907">
@@ -45409,19 +45409,19 @@
         <v>3.753882571960986</v>
       </c>
       <c r="C1907" t="n">
-        <v>3.139177082347608</v>
+        <v>3.166947902507227</v>
       </c>
       <c r="D1907" t="n">
-        <v>-6.38255589642972</v>
+        <v>-6.200591745837185</v>
       </c>
       <c r="E1907" t="n">
-        <v>0.585798299461973</v>
+        <v>0.6863547798586058</v>
       </c>
       <c r="F1907" t="n">
-        <v>-0.6782098383913436</v>
+        <v>-0.4962456877988085</v>
       </c>
       <c r="G1907" t="n">
-        <v>2.732251179312803</v>
+        <v>2.869200489827942</v>
       </c>
     </row>
     <row r="1908">
@@ -45432,19 +45432,19 @@
         <v>3.692931855607644</v>
       </c>
       <c r="C1908" t="n">
-        <v>3.01120115274839</v>
+        <v>3.038971972908008</v>
       </c>
       <c r="D1908" t="n">
-        <v>-6.488145886202824</v>
+        <v>-6.30618173561029</v>
       </c>
       <c r="E1908" t="n">
-        <v>0.4155863739535128</v>
+        <v>0.5161428543501452</v>
       </c>
       <c r="F1908" t="n">
-        <v>-0.783799828164448</v>
+        <v>-0.6018356775719129</v>
       </c>
       <c r="G1908" t="n">
-        <v>2.540921255849721</v>
+        <v>2.677870566364861</v>
       </c>
     </row>
     <row r="1909">
@@ -45455,19 +45455,19 @@
         <v>3.770422583987903</v>
       </c>
       <c r="C1909" t="n">
-        <v>3.059745494625476</v>
+        <v>3.087516314785095</v>
       </c>
       <c r="D1909" t="n">
-        <v>-6.506880788321421</v>
+        <v>-6.324916637728887</v>
       </c>
       <c r="E1909" t="n">
-        <v>0.45663675498316</v>
+        <v>0.5571932353797928</v>
       </c>
       <c r="F1909" t="n">
-        <v>-0.7893958378245793</v>
+        <v>-0.6074316872320442</v>
       </c>
       <c r="G1909" t="n">
-        <v>2.586107991930729</v>
+        <v>2.723057302445869</v>
       </c>
     </row>
     <row r="1910">
@@ -45478,19 +45478,19 @@
         <v>3.760333686710813</v>
       </c>
       <c r="C1910" t="n">
-        <v>2.939866571937308</v>
+        <v>2.967637392096927</v>
       </c>
       <c r="D1910" t="n">
-        <v>-6.358940746913822</v>
+        <v>-6.176976596321287</v>
       </c>
       <c r="E1910" t="n">
-        <v>0.3959338488580322</v>
+        <v>0.496490329254665</v>
       </c>
       <c r="F1910" t="n">
-        <v>-0.7690749219160218</v>
+        <v>-0.5871107713234867</v>
       </c>
       <c r="G1910" t="n">
-        <v>2.478421618787696</v>
+        <v>2.615370929302836</v>
       </c>
     </row>
     <row r="1911">
@@ -45501,19 +45501,19 @@
         <v>3.723566229409205</v>
       </c>
       <c r="C1911" t="n">
-        <v>2.93115258568383</v>
+        <v>2.958923405843449</v>
       </c>
       <c r="D1911" t="n">
-        <v>-6.305971224659833</v>
+        <v>-6.124007074067299</v>
       </c>
       <c r="E1911" t="n">
-        <v>0.4084076715061498</v>
+        <v>0.5089641519027821</v>
       </c>
       <c r="F1911" t="n">
-        <v>-0.7161053996620329</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1911" t="n">
-        <v>2.501489345886611</v>
+        <v>2.638438656401751</v>
       </c>
     </row>
     <row r="1912">
@@ -45524,19 +45524,19 @@
         <v>3.72996971609811</v>
       </c>
       <c r="C1912" t="n">
-        <v>2.924191973588737</v>
+        <v>2.951962793748356</v>
       </c>
       <c r="D1912" t="n">
-        <v>-6.262422817889143</v>
+        <v>-6.080458667296608</v>
       </c>
       <c r="E1912" t="n">
-        <v>0.4188664221193328</v>
+        <v>0.5194229025159651</v>
       </c>
       <c r="F1912" t="n">
-        <v>-0.7161053996620329</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1912" t="n">
-        <v>2.494528733791518</v>
+        <v>2.631478044306657</v>
       </c>
     </row>
     <row r="1913">
@@ -45547,19 +45547,19 @@
         <v>3.782922533493421</v>
       </c>
       <c r="C1913" t="n">
-        <v>2.93865432796988</v>
+        <v>2.966425148129499</v>
       </c>
       <c r="D1913" t="n">
-        <v>-6.020274424435285</v>
+        <v>-5.83831027384275</v>
       </c>
       <c r="E1913" t="n">
-        <v>0.5301881338820191</v>
+        <v>0.6307446142786515</v>
       </c>
       <c r="F1913" t="n">
-        <v>-0.7161053996620329</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1913" t="n">
-        <v>2.508991088172661</v>
+        <v>2.645940398687801</v>
       </c>
     </row>
     <row r="1914">
@@ -45570,19 +45570,19 @@
         <v>3.828551486722818</v>
       </c>
       <c r="C1914" t="n">
-        <v>2.933186448429075</v>
+        <v>2.960957268588694</v>
       </c>
       <c r="D1914" t="n">
-        <v>-5.912015287312763</v>
+        <v>-5.730051136720228</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.5680239091902228</v>
+        <v>0.6685803895868552</v>
       </c>
       <c r="F1914" t="n">
-        <v>-0.7161053996620329</v>
+        <v>-0.5341412490694978</v>
       </c>
       <c r="G1914" t="n">
-        <v>2.503523208631856</v>
+        <v>2.640472519146996</v>
       </c>
     </row>
     <row r="1915">
@@ -45593,19 +45593,19 @@
         <v>3.828052928792046</v>
       </c>
       <c r="C1915" t="n">
-        <v>2.930684542439652</v>
+        <v>2.958455362599271</v>
       </c>
       <c r="D1915" t="n">
-        <v>-5.788724152495632</v>
+        <v>-5.606760001903098</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.6148384571276519</v>
+        <v>0.7153949375242847</v>
       </c>
       <c r="F1915" t="n">
-        <v>-0.5928142648449024</v>
+        <v>-0.4108501142523673</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.574995983532711</v>
+        <v>2.711945294047851</v>
       </c>
     </row>
     <row r="1916">
@@ -45616,19 +45616,19 @@
         <v>3.812453678919907</v>
       </c>
       <c r="C1916" t="n">
-        <v>2.938385520676977</v>
+        <v>2.966156340836596</v>
       </c>
       <c r="D1916" t="n">
-        <v>-5.767574953592189</v>
+        <v>-5.585610802999654</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.6309991149263543</v>
+        <v>0.7315555953229871</v>
       </c>
       <c r="F1916" t="n">
-        <v>-0.571665065941459</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.595386481112102</v>
+        <v>2.732335791627242</v>
       </c>
     </row>
     <row r="1917">
@@ -45639,19 +45639,19 @@
         <v>3.748328408318093</v>
       </c>
       <c r="C1917" t="n">
-        <v>2.934166229024028</v>
+        <v>2.961937049183647</v>
       </c>
       <c r="D1917" t="n">
-        <v>-5.523809511608745</v>
+        <v>-5.34184536101621</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.7242860000667828</v>
+        <v>0.8248424804634156</v>
       </c>
       <c r="F1917" t="n">
-        <v>-0.571665065941459</v>
+        <v>-0.3897009153489239</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.591167189459153</v>
+        <v>2.728116499974293</v>
       </c>
     </row>
     <row r="1918">
@@ -45662,19 +45662,19 @@
         <v>3.824311233057525</v>
       </c>
       <c r="C1918" t="n">
-        <v>2.936290542944044</v>
+        <v>2.964061363103663</v>
       </c>
       <c r="D1918" t="n">
-        <v>-5.42204669133145</v>
+        <v>-5.240082540738915</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.7671154420977166</v>
+        <v>0.8676719224943494</v>
       </c>
       <c r="F1918" t="n">
-        <v>-0.5584459975490303</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.601222944414626</v>
+        <v>2.738172254929766</v>
       </c>
     </row>
     <row r="1919">
@@ -45685,19 +45685,19 @@
         <v>3.826354974279185</v>
       </c>
       <c r="C1919" t="n">
-        <v>2.929032617927746</v>
+        <v>2.956803438087365</v>
       </c>
       <c r="D1919" t="n">
-        <v>-5.172196297382375</v>
+        <v>-4.990232146789841</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.8597976746610487</v>
+        <v>0.9603541550576815</v>
       </c>
       <c r="F1919" t="n">
-        <v>-0.5584459975490303</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.593965019398328</v>
+        <v>2.730914329913468</v>
       </c>
     </row>
     <row r="1920">
@@ -45708,19 +45708,19 @@
         <v>3.835957987011498</v>
       </c>
       <c r="C1920" t="n">
-        <v>2.932631741448395</v>
+        <v>2.960402561608014</v>
       </c>
       <c r="D1920" t="n">
-        <v>-4.996304204914942</v>
+        <v>-4.814340054322408</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.9337536351686708</v>
+        <v>1.034310115565303</v>
       </c>
       <c r="F1920" t="n">
-        <v>-0.5584459975490303</v>
+        <v>-0.3764818469564952</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.597564142918977</v>
+        <v>2.734513453434117</v>
       </c>
     </row>
     <row r="1921">
@@ -45731,19 +45731,19 @@
         <v>3.780933911392987</v>
       </c>
       <c r="C1921" t="n">
-        <v>2.945959247502949</v>
+        <v>2.973730067662567</v>
       </c>
       <c r="D1921" t="n">
-        <v>-4.824857741892479</v>
+        <v>-4.642893591299944</v>
       </c>
       <c r="E1921" t="n">
-        <v>1.01565972643221</v>
+        <v>1.116216206828842</v>
       </c>
       <c r="F1921" t="n">
-        <v>-0.3869995345265672</v>
+        <v>-0.2050353839340321</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.713759526787009</v>
+        <v>2.850708837302149</v>
       </c>
     </row>
     <row r="1922">
@@ -45754,19 +45754,19 @@
         <v>3.773765222632781</v>
       </c>
       <c r="C1922" t="n">
-        <v>2.944979725119246</v>
+        <v>2.972750545278864</v>
       </c>
       <c r="D1922" t="n">
-        <v>-4.75056817615414</v>
+        <v>-4.568604025561605</v>
       </c>
       <c r="E1922" t="n">
-        <v>1.044396030343842</v>
+        <v>1.144952510740475</v>
       </c>
       <c r="F1922" t="n">
-        <v>-0.3127099687882279</v>
+        <v>-0.1307458181956928</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.757353743846309</v>
+        <v>2.894303054361449</v>
       </c>
     </row>
     <row r="1923">
@@ -45777,19 +45777,19 @@
         <v>3.764617879883073</v>
       </c>
       <c r="C1923" t="n">
-        <v>2.949674526173563</v>
+        <v>2.977445346333182</v>
       </c>
       <c r="D1923" t="n">
-        <v>-4.686932433920205</v>
+        <v>-4.504968283327671</v>
       </c>
       <c r="E1923" t="n">
-        <v>1.074545128291734</v>
+        <v>1.175101608688366</v>
       </c>
       <c r="F1923" t="n">
-        <v>-0.2490742265542934</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.800229990240987</v>
+        <v>2.937179300756127</v>
       </c>
     </row>
     <row r="1924">
@@ -45800,19 +45800,19 @@
         <v>3.798814771074781</v>
       </c>
       <c r="C1924" t="n">
-        <v>2.930868784957358</v>
+        <v>2.958639605116977</v>
       </c>
       <c r="D1924" t="n">
-        <v>-4.575505674594285</v>
+        <v>-4.39354152400175</v>
       </c>
       <c r="E1924" t="n">
-        <v>1.100310090805897</v>
+        <v>1.20086657120253</v>
       </c>
       <c r="F1924" t="n">
-        <v>-0.2490742265542934</v>
+        <v>-0.06711007596175828</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.781424249024783</v>
+        <v>2.918373559539923</v>
       </c>
     </row>
     <row r="1925">
@@ -45823,19 +45823,19 @@
         <v>3.797694884242292</v>
       </c>
       <c r="C1925" t="n">
-        <v>2.932611861582236</v>
+        <v>2.960382681741855</v>
       </c>
       <c r="D1925" t="n">
-        <v>-4.335075177789425</v>
+        <v>-4.15311102719689</v>
       </c>
       <c r="E1925" t="n">
-        <v>1.198225366152719</v>
+        <v>1.298781846549351</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.008643729749433116</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.927425623732576</v>
+        <v>3.064374934247716</v>
       </c>
     </row>
     <row r="1926">
@@ -45846,19 +45846,19 @@
         <v>3.821593509367682</v>
       </c>
       <c r="C1926" t="n">
-        <v>2.936541175417056</v>
+        <v>2.964311995576675</v>
       </c>
       <c r="D1926" t="n">
-        <v>-4.26283260961823</v>
+        <v>-4.080868459025695</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.231051707256017</v>
+        <v>1.331608187652649</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.008643729749433116</v>
+        <v>0.173320420843102</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.931354937567396</v>
+        <v>3.068304248082536</v>
       </c>
     </row>
     <row r="1927">
@@ -45869,19 +45869,19 @@
         <v>3.822326997879964</v>
       </c>
       <c r="C1927" t="n">
-        <v>2.937219759334396</v>
+        <v>2.964990579494015</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.209834287336842</v>
+        <v>-4.027870136744307</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.252929620085912</v>
+        <v>1.353486100482544</v>
       </c>
       <c r="F1927" t="n">
-        <v>0.04669252925250572</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.9652352768859</v>
+        <v>3.10218458740104</v>
       </c>
     </row>
     <row r="1928">
@@ -45892,19 +45892,19 @@
         <v>3.848616626502336</v>
       </c>
       <c r="C1928" t="n">
-        <v>2.93421783055439</v>
+        <v>2.961988650714008</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.101029401857115</v>
+        <v>-3.919065251264581</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.293449645497796</v>
+        <v>1.394006125894429</v>
       </c>
       <c r="F1928" t="n">
-        <v>0.04669252925250572</v>
+        <v>0.2286566798450408</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.962233348105893</v>
+        <v>3.099182658621033</v>
       </c>
     </row>
     <row r="1929">
@@ -45915,19 +45915,19 @@
         <v>3.818668951675936</v>
       </c>
       <c r="C1929" t="n">
-        <v>2.935796867565004</v>
+        <v>2.963567687724622</v>
       </c>
       <c r="D1929" t="n">
-        <v>-3.881008603820104</v>
+        <v>-3.69904445322757</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.383037001723215</v>
+        <v>1.483593482119847</v>
       </c>
       <c r="F1929" t="n">
-        <v>0.187912374320486</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1929" t="n">
-        <v>3.048544292157295</v>
+        <v>3.185493602672435</v>
       </c>
     </row>
     <row r="1930">
@@ -45938,19 +45938,19 @@
         <v>3.843274527539948</v>
       </c>
       <c r="C1930" t="n">
-        <v>2.951691050366827</v>
+        <v>2.979461870526446</v>
       </c>
       <c r="D1930" t="n">
-        <v>-3.748140914756826</v>
+        <v>-3.566176764164292</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.452078260150349</v>
+        <v>1.552634740546982</v>
       </c>
       <c r="F1930" t="n">
-        <v>0.187912374320486</v>
+        <v>0.3698765249130211</v>
       </c>
       <c r="G1930" t="n">
-        <v>3.064438474959119</v>
+        <v>3.201387785474259</v>
       </c>
     </row>
     <row r="1931">
@@ -45961,19 +45961,19 @@
         <v>3.84504738649626</v>
       </c>
       <c r="C1931" t="n">
-        <v>2.952836894807129</v>
+        <v>2.980607714966748</v>
       </c>
       <c r="D1931" t="n">
-        <v>-3.627967831392327</v>
+        <v>-3.446003680799793</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.501293337936451</v>
+        <v>1.601849818333083</v>
       </c>
       <c r="F1931" t="n">
-        <v>0.3080854576849849</v>
+        <v>0.4900496082775201</v>
       </c>
       <c r="G1931" t="n">
-        <v>3.13768816941812</v>
+        <v>3.27463747993326</v>
       </c>
     </row>
     <row r="1932">
@@ -45984,19 +45984,19 @@
         <v>3.791273551576997</v>
       </c>
       <c r="C1932" t="n">
-        <v>2.962924997368569</v>
+        <v>2.990695817528187</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.669908621602938</v>
+        <v>-3.301331535700055</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.494605124413646</v>
+        <v>1.669806778934418</v>
       </c>
       <c r="F1932" t="n">
-        <v>0.2661446674743738</v>
+        <v>0.6347217533772576</v>
       </c>
       <c r="G1932" t="n">
-        <v>3.122611797853193</v>
+        <v>3.371528869554542</v>
       </c>
     </row>
     <row r="1933">
@@ -46007,19 +46007,19 @@
         <v>3.735839222942102</v>
       </c>
       <c r="C1933" t="n">
-        <v>2.948962488769995</v>
+        <v>2.976733308929613</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.729783448960631</v>
+        <v>-3.361206363057748</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.456692684871995</v>
+        <v>1.631894339392767</v>
       </c>
       <c r="F1933" t="n">
-        <v>0.2062698401166817</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1933" t="n">
-        <v>3.072724392840004</v>
+        <v>3.321641464541353</v>
       </c>
     </row>
     <row r="1934">
@@ -46030,19 +46030,19 @@
         <v>3.762647477674514</v>
       </c>
       <c r="C1934" t="n">
-        <v>2.964251658004203</v>
+        <v>2.992022478163822</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.609963218049793</v>
+        <v>-3.24138613214691</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.519909946470539</v>
+        <v>1.695111600991311</v>
       </c>
       <c r="F1934" t="n">
-        <v>0.2062698401166817</v>
+        <v>0.5748469260195654</v>
       </c>
       <c r="G1934" t="n">
-        <v>3.088013562074212</v>
+        <v>3.336930633775562</v>
       </c>
     </row>
     <row r="1935">
@@ -46053,19 +46053,19 @@
         <v>3.729146398430692</v>
       </c>
       <c r="C1935" t="n">
-        <v>2.871895857326645</v>
+        <v>2.899666677486263</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.612432924511599</v>
+        <v>-3.243855838608716</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.426566263208258</v>
+        <v>1.60176791772903</v>
       </c>
       <c r="F1935" t="n">
-        <v>0.2038001336548755</v>
+        <v>0.5723772195577592</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.99417593751957</v>
+        <v>3.243093009220919</v>
       </c>
     </row>
     <row r="1936">
@@ -46076,19 +46076,19 @@
         <v>3.743220196003602</v>
       </c>
       <c r="C1936" t="n">
-        <v>2.791157718811946</v>
+        <v>2.818928538971565</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.680803110835609</v>
+        <v>-3.312226024932726</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.318480050163955</v>
+        <v>1.493681704684727</v>
       </c>
       <c r="F1936" t="n">
-        <v>0.2130758326910905</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.919003218426601</v>
+        <v>3.16792029012795</v>
       </c>
     </row>
     <row r="1937">
@@ -46099,19 +46099,19 @@
         <v>3.714179139508369</v>
       </c>
       <c r="C1937" t="n">
-        <v>2.781594427443837</v>
+        <v>2.809365247603456</v>
       </c>
       <c r="D1937" t="n">
-        <v>-3.694591163682656</v>
+        <v>-3.326014077779773</v>
       </c>
       <c r="E1937" t="n">
-        <v>1.303401537657028</v>
+        <v>1.4786031921778</v>
       </c>
       <c r="F1937" t="n">
-        <v>0.2130758326910905</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1937" t="n">
-        <v>2.909439927058492</v>
+        <v>3.158356998759841</v>
       </c>
     </row>
     <row r="1938">
@@ -46122,19 +46122,19 @@
         <v>3.710906731417703</v>
       </c>
       <c r="C1938" t="n">
-        <v>2.606303992484224</v>
+        <v>2.634074812643843</v>
       </c>
       <c r="D1938" t="n">
-        <v>-3.725584323011361</v>
+        <v>-3.357007237108478</v>
       </c>
       <c r="E1938" t="n">
-        <v>1.115713838965932</v>
+        <v>1.290915493486704</v>
       </c>
       <c r="F1938" t="n">
-        <v>0.2130758326910905</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1938" t="n">
-        <v>2.734149492098879</v>
+        <v>2.983066563800228</v>
       </c>
     </row>
     <row r="1939">
@@ -46145,19 +46145,19 @@
         <v>3.746042526205898</v>
       </c>
       <c r="C1939" t="n">
-        <v>2.610871224476012</v>
+        <v>2.638642044635631</v>
       </c>
       <c r="D1939" t="n">
-        <v>-3.550110063218892</v>
+        <v>-3.181532977316009</v>
       </c>
       <c r="E1939" t="n">
-        <v>1.190470774874708</v>
+        <v>1.36567242939548</v>
       </c>
       <c r="F1939" t="n">
-        <v>0.2130758326910905</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1939" t="n">
-        <v>2.738716724090667</v>
+        <v>2.987633795792016</v>
       </c>
     </row>
     <row r="1940">
@@ -46168,19 +46168,19 @@
         <v>3.765024323225442</v>
       </c>
       <c r="C1940" t="n">
-        <v>2.586613253237219</v>
+        <v>2.614384073396838</v>
       </c>
       <c r="D1940" t="n">
-        <v>-3.661046315860141</v>
+        <v>-3.292469229957257</v>
       </c>
       <c r="E1940" t="n">
-        <v>1.121838302579416</v>
+        <v>1.297039957100188</v>
       </c>
       <c r="F1940" t="n">
-        <v>0.2130758326910905</v>
+        <v>0.5816529185939742</v>
       </c>
       <c r="G1940" t="n">
-        <v>2.714458752851874</v>
+        <v>2.963375824553223</v>
       </c>
     </row>
     <row r="1941">
@@ -46191,19 +46191,19 @@
         <v>3.773210297111294</v>
       </c>
       <c r="C1941" t="n">
-        <v>2.515151566638669</v>
+        <v>2.542922386798288</v>
       </c>
       <c r="D1941" t="n">
-        <v>-3.627382770387859</v>
+        <v>-3.258805684484976</v>
       </c>
       <c r="E1941" t="n">
-        <v>1.063842034169778</v>
+        <v>1.23904368869055</v>
       </c>
       <c r="F1941" t="n">
-        <v>0.2467393781633723</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1941" t="n">
-        <v>2.663195193536692</v>
+        <v>2.912112265238041</v>
       </c>
     </row>
     <row r="1942">
@@ -46214,19 +46214,19 @@
         <v>3.784343952264164</v>
       </c>
       <c r="C1942" t="n">
-        <v>2.525323953070801</v>
+        <v>2.55309477323042</v>
       </c>
       <c r="D1942" t="n">
-        <v>-3.567530151184136</v>
+        <v>-3.198953065281252</v>
       </c>
       <c r="E1942" t="n">
-        <v>1.0979554682834</v>
+        <v>1.273157122804172</v>
       </c>
       <c r="F1942" t="n">
-        <v>0.2467393781633723</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1942" t="n">
-        <v>2.673367579968825</v>
+        <v>2.922284651670174</v>
       </c>
     </row>
     <row r="1943">
@@ -46237,19 +46237,19 @@
         <v>3.7869499577423</v>
       </c>
       <c r="C1943" t="n">
-        <v>2.520270223644661</v>
+        <v>2.54804104380428</v>
       </c>
       <c r="D1943" t="n">
-        <v>-3.481286688157758</v>
+        <v>-3.112709602254875</v>
       </c>
       <c r="E1943" t="n">
-        <v>1.127399124067811</v>
+        <v>1.302600778588583</v>
       </c>
       <c r="F1943" t="n">
-        <v>0.2467393781633723</v>
+        <v>0.6153164640662561</v>
       </c>
       <c r="G1943" t="n">
-        <v>2.668313850542685</v>
+        <v>2.917230922244034</v>
       </c>
     </row>
     <row r="1944">
@@ -46260,19 +46260,19 @@
         <v>3.752027499316047</v>
       </c>
       <c r="C1944" t="n">
-        <v>2.512045999089187</v>
+        <v>2.539816819248806</v>
       </c>
       <c r="D1944" t="n">
-        <v>-3.526593507556738</v>
+        <v>-3.158016421653855</v>
       </c>
       <c r="E1944" t="n">
-        <v>1.101052171752745</v>
+        <v>1.276253826273517</v>
       </c>
       <c r="F1944" t="n">
-        <v>0.2059292151541415</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1944" t="n">
-        <v>2.635603528181672</v>
+        <v>2.884520599883021</v>
       </c>
     </row>
     <row r="1945">
@@ -46283,19 +46283,19 @@
         <v>3.753571165803192</v>
       </c>
       <c r="C1945" t="n">
-        <v>2.512597872122289</v>
+        <v>2.540368692281907</v>
       </c>
       <c r="D1945" t="n">
-        <v>-3.55562661225904</v>
+        <v>-3.247056704749392</v>
       </c>
       <c r="E1945" t="n">
-        <v>1.089990802904925</v>
+        <v>1.241189586068403</v>
       </c>
       <c r="F1945" t="n">
-        <v>0.2059292151541415</v>
+        <v>0.5745063010570253</v>
       </c>
       <c r="G1945" t="n">
-        <v>2.636155401214774</v>
+        <v>2.885072472916123</v>
       </c>
     </row>
     <row r="1946">
@@ -46306,19 +46306,19 @@
         <v>3.7333906008095</v>
       </c>
       <c r="C1946" t="n">
-        <v>2.441870564013654</v>
+        <v>2.469641384173273</v>
       </c>
       <c r="D1946" t="n">
-        <v>-3.46281613080818</v>
+        <v>-3.154246223298533</v>
       </c>
       <c r="E1946" t="n">
-        <v>1.056387687376635</v>
+        <v>1.207586470540112</v>
       </c>
       <c r="F1946" t="n">
-        <v>0.2987396966050009</v>
+        <v>0.6673167825078846</v>
       </c>
       <c r="G1946" t="n">
-        <v>2.621114381976655</v>
+        <v>2.870031453678004</v>
       </c>
     </row>
     <row r="1947">
@@ -46329,19 +46329,19 @@
         <v>3.748285816560426</v>
       </c>
       <c r="C1947" t="n">
-        <v>2.443744039938255</v>
+        <v>2.471514860097874</v>
       </c>
       <c r="D1947" t="n">
-        <v>-3.507205600137608</v>
+        <v>-3.198635692627961</v>
       </c>
       <c r="E1947" t="n">
-        <v>1.040505375569465</v>
+        <v>1.191704158732942</v>
       </c>
       <c r="F1947" t="n">
-        <v>0.2543502272755732</v>
+        <v>0.622927313178457</v>
       </c>
       <c r="G1947" t="n">
-        <v>2.596354176303599</v>
+        <v>2.845271248004948</v>
       </c>
     </row>
     <row r="1948">
@@ -46352,19 +46352,19 @@
         <v>3.721077195472739</v>
       </c>
       <c r="C1948" t="n">
-        <v>2.438819748449978</v>
+        <v>2.466590568609597</v>
       </c>
       <c r="D1948" t="n">
-        <v>-3.394534381901358</v>
+        <v>-3.085964474391711</v>
       </c>
       <c r="E1948" t="n">
-        <v>1.080649571375688</v>
+        <v>1.231848354539165</v>
       </c>
       <c r="F1948" t="n">
-        <v>0.3670214455118234</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1948" t="n">
-        <v>2.659032615757072</v>
+        <v>2.907949687458421</v>
       </c>
     </row>
     <row r="1949">
@@ -46375,19 +46375,19 @@
         <v>3.743047603798537</v>
       </c>
       <c r="C1949" t="n">
-        <v>2.444311044280645</v>
+        <v>2.472081864440264</v>
       </c>
       <c r="D1949" t="n">
-        <v>-3.282157380718685</v>
+        <v>-2.973587473209038</v>
       </c>
       <c r="E1949" t="n">
-        <v>1.131091667679424</v>
+        <v>1.282290450842902</v>
       </c>
       <c r="F1949" t="n">
-        <v>0.3670214455118234</v>
+        <v>0.7355985314147071</v>
       </c>
       <c r="G1949" t="n">
-        <v>2.664523911587739</v>
+        <v>2.913440983289088</v>
       </c>
     </row>
     <row r="1950">
@@ -46398,19 +46398,19 @@
         <v>3.689597840498865</v>
       </c>
       <c r="C1950" t="n">
-        <v>2.455808246049184</v>
+        <v>2.483579066208803</v>
       </c>
       <c r="D1950" t="n">
-        <v>-3.309937778620038</v>
+        <v>-3.001367871110391</v>
       </c>
       <c r="E1950" t="n">
-        <v>1.131476710287422</v>
+        <v>1.282675493450899</v>
       </c>
       <c r="F1950" t="n">
-        <v>0.3392410476104704</v>
+        <v>0.707818133513354</v>
       </c>
       <c r="G1950" t="n">
-        <v>2.659352874615467</v>
+        <v>2.908269946316816</v>
       </c>
     </row>
     <row r="1951">
@@ -46421,19 +46421,19 @@
         <v>3.643069621705326</v>
       </c>
       <c r="C1951" t="n">
-        <v>2.294163966049838</v>
+        <v>2.321934786209456</v>
       </c>
       <c r="D1951" t="n">
-        <v>-3.392939059645317</v>
+        <v>-3.08436915213567</v>
       </c>
       <c r="E1951" t="n">
-        <v>0.9366319178779634</v>
+        <v>1.087830701041441</v>
       </c>
       <c r="F1951" t="n">
-        <v>0.3206701630832966</v>
+        <v>0.6892472489861803</v>
       </c>
       <c r="G1951" t="n">
-        <v>2.486566063899816</v>
+        <v>2.735483135601165</v>
       </c>
     </row>
     <row r="1952">
@@ -46444,19 +46444,19 @@
         <v>3.682716310729271</v>
       </c>
       <c r="C1952" t="n">
-        <v>2.414313626769043</v>
+        <v>2.442084446928662</v>
       </c>
       <c r="D1952" t="n">
-        <v>-3.501553138088648</v>
+        <v>-3.192983230579001</v>
       </c>
       <c r="E1952" t="n">
-        <v>1.013335947219837</v>
+        <v>1.164534730383314</v>
       </c>
       <c r="F1952" t="n">
-        <v>0.3206701630832966</v>
+        <v>0.6892472489861803</v>
       </c>
       <c r="G1952" t="n">
-        <v>2.606715724619022</v>
+        <v>2.85563279632037</v>
       </c>
     </row>
     <row r="1953">
@@ -46467,19 +46467,19 @@
         <v>3.733012441190769</v>
       </c>
       <c r="C1953" t="n">
-        <v>2.428826652871366</v>
+        <v>2.456597473030985</v>
       </c>
       <c r="D1953" t="n">
-        <v>-3.466144099840506</v>
+        <v>-3.157574192330858</v>
       </c>
       <c r="E1953" t="n">
-        <v>1.042012588621417</v>
+        <v>1.193211371784894</v>
       </c>
       <c r="F1953" t="n">
-        <v>0.3206701630832966</v>
+        <v>0.6892472489861803</v>
       </c>
       <c r="G1953" t="n">
-        <v>2.621228750721345</v>
+        <v>2.870145822422693</v>
       </c>
     </row>
     <row r="1954">
@@ -46490,19 +46490,19 @@
         <v>3.741174069913426</v>
       </c>
       <c r="C1954" t="n">
-        <v>2.426246094213735</v>
+        <v>2.454016914373354</v>
       </c>
       <c r="D1954" t="n">
-        <v>-3.427760437282354</v>
+        <v>-3.119190529772707</v>
       </c>
       <c r="E1954" t="n">
-        <v>1.054785494987046</v>
+        <v>1.205984278150523</v>
       </c>
       <c r="F1954" t="n">
-        <v>0.3590538256414478</v>
+        <v>0.7276309115443315</v>
       </c>
       <c r="G1954" t="n">
-        <v>2.641678389598604</v>
+        <v>2.890595461299953</v>
       </c>
     </row>
     <row r="1955">
@@ -46513,19 +46513,19 @@
         <v>3.751147197532486</v>
       </c>
       <c r="C1955" t="n">
-        <v>2.422975123059037</v>
+        <v>2.450745943218656</v>
       </c>
       <c r="D1955" t="n">
-        <v>-3.250644107247188</v>
+        <v>-2.942074199737541</v>
       </c>
       <c r="E1955" t="n">
-        <v>1.122361055846414</v>
+        <v>1.273559839009892</v>
       </c>
       <c r="F1955" t="n">
-        <v>0.3590538256414478</v>
+        <v>0.7276309115443315</v>
       </c>
       <c r="G1955" t="n">
-        <v>2.638407418443906</v>
+        <v>2.887324490145255</v>
       </c>
     </row>
     <row r="1956">
@@ -46536,19 +46536,19 @@
         <v>3.741328448793903</v>
       </c>
       <c r="C1956" t="n">
-        <v>2.42365851482095</v>
+        <v>2.451429334980569</v>
       </c>
       <c r="D1956" t="n">
-        <v>-3.295736352080734</v>
+        <v>-2.987166444571087</v>
       </c>
       <c r="E1956" t="n">
-        <v>1.105007549674909</v>
+        <v>1.256206332838387</v>
       </c>
       <c r="F1956" t="n">
-        <v>0.297157782472058</v>
+        <v>0.6657348683749417</v>
       </c>
       <c r="G1956" t="n">
-        <v>2.601953184304185</v>
+        <v>2.850870256005534</v>
       </c>
     </row>
     <row r="1957">
@@ -46559,19 +46559,19 @@
         <v>3.750729377011234</v>
       </c>
       <c r="C1957" t="n">
-        <v>2.417445490127364</v>
+        <v>2.445216310286983</v>
       </c>
       <c r="D1957" t="n">
-        <v>-3.116360930841966</v>
+        <v>-2.807791023332319</v>
       </c>
       <c r="E1957" t="n">
-        <v>1.17054469347683</v>
+        <v>1.321743476640308</v>
       </c>
       <c r="F1957" t="n">
-        <v>0.4539345406427767</v>
+        <v>0.8225116265456603</v>
       </c>
       <c r="G1957" t="n">
-        <v>2.68980621451303</v>
+        <v>2.93872328621438</v>
       </c>
     </row>
     <row r="1958">
@@ -46582,19 +46582,19 @@
         <v>3.716991718982229</v>
       </c>
       <c r="C1958" t="n">
-        <v>2.398252945458954</v>
+        <v>2.426023765618573</v>
       </c>
       <c r="D1958" t="n">
-        <v>-3.161375144362573</v>
+        <v>-2.852805236852925</v>
       </c>
       <c r="E1958" t="n">
-        <v>1.133346463400178</v>
+        <v>1.284545246563656</v>
       </c>
       <c r="F1958" t="n">
-        <v>0.4235856453281721</v>
+        <v>0.7921627312310557</v>
       </c>
       <c r="G1958" t="n">
-        <v>2.652404332655858</v>
+        <v>2.901321404357207</v>
       </c>
     </row>
     <row r="1959">
@@ -46605,19 +46605,19 @@
         <v>3.737026608509536</v>
       </c>
       <c r="C1959" t="n">
-        <v>2.4039445077979</v>
+        <v>2.431715327957519</v>
       </c>
       <c r="D1959" t="n">
-        <v>-3.428379654635008</v>
+        <v>-3.119809747125361</v>
       </c>
       <c r="E1959" t="n">
-        <v>1.032236221630149</v>
+        <v>1.183435004793627</v>
       </c>
       <c r="F1959" t="n">
-        <v>0.2292226072852235</v>
+        <v>0.5977996931881071</v>
       </c>
       <c r="G1959" t="n">
-        <v>2.541478072169034</v>
+        <v>2.790395143870383</v>
       </c>
     </row>
     <row r="1960">
@@ -46628,19 +46628,19 @@
         <v>3.702309454760812</v>
       </c>
       <c r="C1960" t="n">
-        <v>2.403148429694401</v>
+        <v>2.43091924985402</v>
       </c>
       <c r="D1960" t="n">
-        <v>-3.529577436072181</v>
+        <v>-3.221007528562533</v>
       </c>
       <c r="E1960" t="n">
-        <v>0.9909610309517816</v>
+        <v>1.142159814115259</v>
       </c>
       <c r="F1960" t="n">
-        <v>0.1608137937399043</v>
+        <v>0.529390879642788</v>
       </c>
       <c r="G1960" t="n">
-        <v>2.499636705938344</v>
+        <v>2.748553777639693</v>
       </c>
     </row>
     <row r="1961">
@@ -46651,19 +46651,19 @@
         <v>3.705571661815457</v>
       </c>
       <c r="C1961" t="n">
-        <v>2.400748391248718</v>
+        <v>2.428519211408337</v>
       </c>
       <c r="D1961" t="n">
-        <v>-3.523066469457868</v>
+        <v>-3.214496561948221</v>
       </c>
       <c r="E1961" t="n">
-        <v>0.9911653791518233</v>
+        <v>1.142364162315301</v>
       </c>
       <c r="F1961" t="n">
-        <v>0.1608137937399043</v>
+        <v>0.529390879642788</v>
       </c>
       <c r="G1961" t="n">
-        <v>2.497236667492661</v>
+        <v>2.74615373919401</v>
       </c>
     </row>
     <row r="1962">
@@ -46674,19 +46674,19 @@
         <v>3.709510443378101</v>
       </c>
       <c r="C1962" t="n">
-        <v>2.397273110456963</v>
+        <v>2.425043930616582</v>
       </c>
       <c r="D1962" t="n">
-        <v>-3.504028341750571</v>
+        <v>-3.195458434240924</v>
       </c>
       <c r="E1962" t="n">
-        <v>0.9953053494429873</v>
+        <v>1.146504132606465</v>
       </c>
       <c r="F1962" t="n">
-        <v>0.1026301824087097</v>
+        <v>0.4712072683115934</v>
       </c>
       <c r="G1962" t="n">
-        <v>2.458851219902189</v>
+        <v>2.707768291603538</v>
       </c>
     </row>
     <row r="1963">
@@ -46697,19 +46697,19 @@
         <v>3.731064473131251</v>
       </c>
       <c r="C1963" t="n">
-        <v>2.574854979395643</v>
+        <v>2.602625799555262</v>
       </c>
       <c r="D1963" t="n">
-        <v>-3.535154972901189</v>
+        <v>-3.226585065391542</v>
       </c>
       <c r="E1963" t="n">
-        <v>1.160436565921421</v>
+        <v>1.311635349084898</v>
       </c>
       <c r="F1963" t="n">
-        <v>0.1026301824087097</v>
+        <v>0.4712072683115934</v>
       </c>
       <c r="G1963" t="n">
-        <v>2.63643308884087</v>
+        <v>2.885350160542218</v>
       </c>
     </row>
     <row r="1964">
@@ -46720,19 +46720,19 @@
         <v>3.722447362067866</v>
       </c>
       <c r="C1964" t="n">
-        <v>2.575688308381777</v>
+        <v>2.603459128541396</v>
       </c>
       <c r="D1964" t="n">
-        <v>-3.549021734235106</v>
+        <v>-3.240451826725459</v>
       </c>
       <c r="E1964" t="n">
-        <v>1.155723190373987</v>
+        <v>1.306921973537465</v>
       </c>
       <c r="F1964" t="n">
-        <v>0.06477226567488681</v>
+        <v>0.4333493515777705</v>
       </c>
       <c r="G1964" t="n">
-        <v>2.614551667786709</v>
+        <v>2.863468739488058</v>
       </c>
     </row>
     <row r="1965">
@@ -46743,19 +46743,19 @@
         <v>3.787425580789123</v>
       </c>
       <c r="C1965" t="n">
-        <v>2.581696838778703</v>
+        <v>2.609467658938322</v>
       </c>
       <c r="D1965" t="n">
-        <v>-3.504217562695176</v>
+        <v>-3.195647655185529</v>
       </c>
       <c r="E1965" t="n">
-        <v>1.179653389386885</v>
+        <v>1.330852172550363</v>
       </c>
       <c r="F1965" t="n">
-        <v>0.06477226567488681</v>
+        <v>0.4333493515777705</v>
       </c>
       <c r="G1965" t="n">
-        <v>2.620560198183635</v>
+        <v>2.869477269884984</v>
       </c>
     </row>
     <row r="1966">
@@ -46766,19 +46766,19 @@
         <v>3.781501250519909</v>
       </c>
       <c r="C1966" t="n">
-        <v>2.479647060055902</v>
+        <v>2.507417880215521</v>
       </c>
       <c r="D1966" t="n">
-        <v>-3.356474592460174</v>
+        <v>-3.047904684950527</v>
       </c>
       <c r="E1966" t="n">
-        <v>1.136700798758085</v>
+        <v>1.287899581921563</v>
       </c>
       <c r="F1966" t="n">
-        <v>0.23257962290977</v>
+        <v>0.6011567088126537</v>
       </c>
       <c r="G1966" t="n">
-        <v>2.619194833801765</v>
+        <v>2.868111905503114</v>
       </c>
     </row>
     <row r="1967">
@@ -46789,19 +46789,19 @@
         <v>3.80224592918117</v>
       </c>
       <c r="C1967" t="n">
-        <v>2.482440681587383</v>
+        <v>2.510211501747002</v>
       </c>
       <c r="D1967" t="n">
-        <v>-3.458489274991395</v>
+        <v>-3.149919367481748</v>
       </c>
       <c r="E1967" t="n">
-        <v>1.098688547277078</v>
+        <v>1.249887330440556</v>
       </c>
       <c r="F1967" t="n">
-        <v>0.23257962290977</v>
+        <v>0.6011567088126537</v>
       </c>
       <c r="G1967" t="n">
-        <v>2.621988455333246</v>
+        <v>2.870905527034595</v>
       </c>
     </row>
     <row r="1968">
@@ -46812,19 +46812,19 @@
         <v>3.80560898539473</v>
       </c>
       <c r="C1968" t="n">
-        <v>2.483103029979042</v>
+        <v>2.51087385013866</v>
       </c>
       <c r="D1968" t="n">
-        <v>-3.452336568938611</v>
+        <v>-3.143766661428963</v>
       </c>
       <c r="E1968" t="n">
-        <v>1.10181197808985</v>
+        <v>1.253010761253328</v>
       </c>
       <c r="F1968" t="n">
-        <v>0.2387323289625543</v>
+        <v>0.607309414865438</v>
       </c>
       <c r="G1968" t="n">
-        <v>2.626342427356575</v>
+        <v>2.875259499057924</v>
       </c>
     </row>
     <row r="1969">
@@ -46835,19 +46835,19 @@
         <v>3.798239794890611</v>
       </c>
       <c r="C1969" t="n">
-        <v>2.482183506719152</v>
+        <v>2.509954326878771</v>
       </c>
       <c r="D1969" t="n">
-        <v>-3.469145867089112</v>
+        <v>-3.160575959579465</v>
       </c>
       <c r="E1969" t="n">
-        <v>1.09416873556976</v>
+        <v>1.245367518733238</v>
       </c>
       <c r="F1969" t="n">
-        <v>0.2219230308120526</v>
+        <v>0.5905001167149364</v>
       </c>
       <c r="G1969" t="n">
-        <v>2.615337325206384</v>
+        <v>2.864254396907733</v>
       </c>
     </row>
     <row r="1970">
@@ -46858,19 +46858,19 @@
         <v>3.867362636798427</v>
       </c>
       <c r="C1970" t="n">
-        <v>2.548519060515973</v>
+        <v>2.576289880675592</v>
       </c>
       <c r="D1970" t="n">
-        <v>-3.40684786831299</v>
+        <v>-3.098277960803343</v>
       </c>
       <c r="E1970" t="n">
-        <v>1.185423488877029</v>
+        <v>1.336622272040507</v>
       </c>
       <c r="F1970" t="n">
-        <v>0.2219230308120526</v>
+        <v>0.5905001167149364</v>
       </c>
       <c r="G1970" t="n">
-        <v>2.681672879003205</v>
+        <v>2.930589950704554</v>
       </c>
     </row>
     <row r="1971">
@@ -46881,19 +46881,19 @@
         <v>3.848729139992192</v>
       </c>
       <c r="C1971" t="n">
-        <v>2.3508110622301</v>
+        <v>2.378581882389719</v>
       </c>
       <c r="D1971" t="n">
-        <v>-3.205057670647832</v>
+        <v>-2.896487763138185</v>
       </c>
       <c r="E1971" t="n">
-        <v>1.06843156965722</v>
+        <v>1.219630352820697</v>
       </c>
       <c r="F1971" t="n">
-        <v>0.419941222981207</v>
+        <v>0.7885183088840908</v>
       </c>
       <c r="G1971" t="n">
-        <v>2.602775796018824</v>
+        <v>2.851692867720173</v>
       </c>
     </row>
     <row r="1972">
@@ -46904,19 +46904,19 @@
         <v>3.841444817852425</v>
       </c>
       <c r="C1972" t="n">
-        <v>2.421101294552275</v>
+        <v>2.448872114711894</v>
       </c>
       <c r="D1972" t="n">
-        <v>-3.040244667568985</v>
+        <v>-2.731674760059338</v>
       </c>
       <c r="E1972" t="n">
-        <v>1.204647003210934</v>
+        <v>1.355845786374412</v>
       </c>
       <c r="F1972" t="n">
-        <v>0.584754226060054</v>
+        <v>0.9533313119629377</v>
       </c>
       <c r="G1972" t="n">
-        <v>2.771953830188308</v>
+        <v>3.020870901889657</v>
       </c>
     </row>
     <row r="1973">
@@ -46927,19 +46927,19 @@
         <v>3.819063300319545</v>
       </c>
       <c r="C1973" t="n">
-        <v>2.435729030668319</v>
+        <v>2.463499850827938</v>
       </c>
       <c r="D1973" t="n">
-        <v>-3.13798521219396</v>
+        <v>-2.829415304684312</v>
       </c>
       <c r="E1973" t="n">
-        <v>1.180178521476988</v>
+        <v>1.331377304640465</v>
       </c>
       <c r="F1973" t="n">
-        <v>0.5688649479270738</v>
+        <v>0.9374420338299576</v>
       </c>
       <c r="G1973" t="n">
-        <v>2.777047999424563</v>
+        <v>3.025965071125913</v>
       </c>
     </row>
     <row r="1974">
@@ -46950,19 +46950,19 @@
         <v>3.831819032489385</v>
       </c>
       <c r="C1974" t="n">
-        <v>2.43426501149299</v>
+        <v>2.462035831652609</v>
       </c>
       <c r="D1974" t="n">
-        <v>-3.314322972316889</v>
+        <v>-3.005753064807242</v>
       </c>
       <c r="E1974" t="n">
-        <v>1.108179398252488</v>
+        <v>1.259378181415965</v>
       </c>
       <c r="F1974" t="n">
-        <v>0.3925271878041444</v>
+        <v>0.7611042737070282</v>
       </c>
       <c r="G1974" t="n">
-        <v>2.669781324175478</v>
+        <v>2.918698395876826</v>
       </c>
     </row>
     <row r="1975">
@@ -46973,19 +46973,19 @@
         <v>3.836411672397794</v>
       </c>
       <c r="C1975" t="n">
-        <v>2.432756629532919</v>
+        <v>2.460527449692538</v>
       </c>
       <c r="D1975" t="n">
-        <v>-3.237900925884962</v>
+        <v>-2.929331018375315</v>
       </c>
       <c r="E1975" t="n">
-        <v>1.137239834865187</v>
+        <v>1.288438618028665</v>
       </c>
       <c r="F1975" t="n">
-        <v>0.3925271878041444</v>
+        <v>0.7611042737070282</v>
       </c>
       <c r="G1975" t="n">
-        <v>2.668272942215406</v>
+        <v>2.917190013916755</v>
       </c>
     </row>
     <row r="1976">
@@ -46996,19 +46996,19 @@
         <v>3.833513460316249</v>
       </c>
       <c r="C1976" t="n">
-        <v>2.432619496968355</v>
+        <v>2.460390317127974</v>
       </c>
       <c r="D1976" t="n">
-        <v>-3.193527794246394</v>
+        <v>-2.884957886736746</v>
       </c>
       <c r="E1976" t="n">
-        <v>1.154851954956051</v>
+        <v>1.306050738119528</v>
       </c>
       <c r="F1976" t="n">
-        <v>0.436900319442713</v>
+        <v>0.8054774053455968</v>
       </c>
       <c r="G1976" t="n">
-        <v>2.694759688633983</v>
+        <v>2.943676760335332</v>
       </c>
     </row>
     <row r="1977">
@@ -47019,19 +47019,19 @@
         <v>3.821562117105966</v>
       </c>
       <c r="C1977" t="n">
-        <v>2.427013291106946</v>
+        <v>2.454784111266564</v>
       </c>
       <c r="D1977" t="n">
-        <v>-3.070693573359226</v>
+        <v>-2.762123665849579</v>
       </c>
       <c r="E1977" t="n">
-        <v>1.198379437449508</v>
+        <v>1.349578220612986</v>
       </c>
       <c r="F1977" t="n">
-        <v>0.436900319442713</v>
+        <v>0.8054774053455968</v>
       </c>
       <c r="G1977" t="n">
-        <v>2.689153482772574</v>
+        <v>2.938070554473923</v>
       </c>
     </row>
     <row r="1978">
@@ -47039,22 +47039,22 @@
         <v>45440</v>
       </c>
       <c r="B1978" t="n">
-        <v>3.833011148190324</v>
+        <v>3.833011148190325</v>
       </c>
       <c r="C1978" t="n">
-        <v>2.43339504813475</v>
+        <v>2.461165868294369</v>
       </c>
       <c r="D1978" t="n">
-        <v>-3.02303784279817</v>
+        <v>-2.714467935288523</v>
       </c>
       <c r="E1978" t="n">
-        <v>1.223823486701735</v>
+        <v>1.375022269865213</v>
       </c>
       <c r="F1978" t="n">
-        <v>0.4845560500037686</v>
+        <v>0.8531331359066524</v>
       </c>
       <c r="G1978" t="n">
-        <v>2.724128678137012</v>
+        <v>2.973045749838361</v>
       </c>
     </row>
     <row r="1979">
@@ -47065,19 +47065,19 @@
         <v>3.822678210569617</v>
       </c>
       <c r="C1979" t="n">
-        <v>2.438287421509475</v>
+        <v>2.466058241669094</v>
       </c>
       <c r="D1979" t="n">
-        <v>-2.922519684299416</v>
+        <v>-2.613949776789768</v>
       </c>
       <c r="E1979" t="n">
-        <v>1.268923123475962</v>
+        <v>1.420121906639439</v>
       </c>
       <c r="F1979" t="n">
-        <v>0.5850742085025231</v>
+        <v>0.953651294405407</v>
       </c>
       <c r="G1979" t="n">
-        <v>2.789331946610989</v>
+        <v>3.038249018312338</v>
       </c>
     </row>
     <row r="1980">
@@ -47088,19 +47088,19 @@
         <v>3.828808877557292</v>
       </c>
       <c r="C1980" t="n">
-        <v>2.425042093985347</v>
+        <v>2.452812914144966</v>
       </c>
       <c r="D1980" t="n">
-        <v>-2.983186274701805</v>
+        <v>-2.674616367192157</v>
       </c>
       <c r="E1980" t="n">
-        <v>1.231411159790878</v>
+        <v>1.382609942954356</v>
       </c>
       <c r="F1980" t="n">
-        <v>0.5033758917839894</v>
+        <v>0.8719529776868733</v>
       </c>
       <c r="G1980" t="n">
-        <v>2.727067629055741</v>
+        <v>2.975984700757091</v>
       </c>
     </row>
     <row r="1981">
@@ -47111,19 +47111,19 @@
         <v>3.816837033932767</v>
       </c>
       <c r="C1981" t="n">
-        <v>2.429139796595976</v>
+        <v>2.456910616755595</v>
       </c>
       <c r="D1981" t="n">
-        <v>-2.938347873093407</v>
+        <v>-2.629777965583759</v>
       </c>
       <c r="E1981" t="n">
-        <v>1.253444223044866</v>
+        <v>1.404643006208344</v>
       </c>
       <c r="F1981" t="n">
-        <v>0.5079193247288589</v>
+        <v>0.8764964106317428</v>
       </c>
       <c r="G1981" t="n">
-        <v>2.733891391433292</v>
+        <v>2.982808463134641</v>
       </c>
     </row>
     <row r="1982">
@@ -47134,19 +47134,19 @@
         <v>3.81793235491705</v>
       </c>
       <c r="C1982" t="n">
-        <v>2.433300736227054</v>
+        <v>2.461071556386673</v>
       </c>
       <c r="D1982" t="n">
-        <v>-3.039106508850405</v>
+        <v>-2.730536601340758</v>
       </c>
       <c r="E1982" t="n">
-        <v>1.217301708373145</v>
+        <v>1.368500491536622</v>
       </c>
       <c r="F1982" t="n">
-        <v>0.4190937560018535</v>
+        <v>0.7876708419047374</v>
       </c>
       <c r="G1982" t="n">
-        <v>2.684756989828166</v>
+        <v>2.933674061529516</v>
       </c>
     </row>
     <row r="1983">
@@ -47157,19 +47157,19 @@
         <v>3.826684745405958</v>
       </c>
       <c r="C1983" t="n">
-        <v>2.439180338754891</v>
+        <v>2.46695115891451</v>
       </c>
       <c r="D1983" t="n">
-        <v>-2.994903671764505</v>
+        <v>-2.686333764254857</v>
       </c>
       <c r="E1983" t="n">
-        <v>1.240862445735342</v>
+        <v>1.39206122889882</v>
       </c>
       <c r="F1983" t="n">
-        <v>0.4632965930877539</v>
+        <v>0.8318736789906378</v>
       </c>
       <c r="G1983" t="n">
-        <v>2.717158294607544</v>
+        <v>2.966075366308893</v>
       </c>
     </row>
     <row r="1984">
@@ -47180,19 +47180,19 @@
         <v>3.838199629265644</v>
       </c>
       <c r="C1984" t="n">
-        <v>2.437590339224139</v>
+        <v>2.465361159383757</v>
       </c>
       <c r="D1984" t="n">
-        <v>-3.031882699427948</v>
+        <v>-2.723312791918301</v>
       </c>
       <c r="E1984" t="n">
-        <v>1.224480835139212</v>
+        <v>1.37567961830269</v>
       </c>
       <c r="F1984" t="n">
-        <v>0.5002704948790845</v>
+        <v>0.8688475807819683</v>
       </c>
       <c r="G1984" t="n">
-        <v>2.73775263615159</v>
+        <v>2.986669707852939</v>
       </c>
     </row>
     <row r="1985">
@@ -47203,19 +47203,19 @@
         <v>3.863895080284879</v>
       </c>
       <c r="C1985" t="n">
-        <v>2.488838104407178</v>
+        <v>2.516608924566797</v>
       </c>
       <c r="D1985" t="n">
-        <v>-2.873591281888676</v>
+        <v>-2.565021374379028</v>
       </c>
       <c r="E1985" t="n">
-        <v>1.339045167337961</v>
+        <v>1.490243950501438</v>
       </c>
       <c r="F1985" t="n">
-        <v>0.5002704948790845</v>
+        <v>0.8688475807819683</v>
       </c>
       <c r="G1985" t="n">
-        <v>2.789000401334629</v>
+        <v>3.037917473035979</v>
       </c>
     </row>
     <row r="1986">
@@ -47226,19 +47226,19 @@
         <v>3.86533868132102</v>
       </c>
       <c r="C1986" t="n">
-        <v>2.487278809001432</v>
+        <v>2.51504962916105</v>
       </c>
       <c r="D1986" t="n">
-        <v>-2.6659492782542</v>
+        <v>-2.357379370744552</v>
       </c>
       <c r="E1986" t="n">
-        <v>1.420542673386004</v>
+        <v>1.571741456549482</v>
       </c>
       <c r="F1986" t="n">
-        <v>0.7079124985135606</v>
+        <v>1.076489584416445</v>
       </c>
       <c r="G1986" t="n">
-        <v>2.912026308109568</v>
+        <v>3.160943379810917</v>
       </c>
     </row>
     <row r="1987">
@@ -47249,19 +47249,19 @@
         <v>3.864489842475137</v>
       </c>
       <c r="C1987" t="n">
-        <v>2.482227037239702</v>
+        <v>2.50999785739932</v>
       </c>
       <c r="D1987" t="n">
-        <v>-2.614917185531672</v>
+        <v>-2.306347278022024</v>
       </c>
       <c r="E1987" t="n">
-        <v>1.435903738713286</v>
+        <v>1.587102521876763</v>
       </c>
       <c r="F1987" t="n">
-        <v>0.7589445912360886</v>
+        <v>1.127521677138973</v>
       </c>
       <c r="G1987" t="n">
-        <v>2.937593791981355</v>
+        <v>3.186510863682704</v>
       </c>
     </row>
     <row r="1988">
@@ -47272,19 +47272,19 @@
         <v>3.842547360404851</v>
       </c>
       <c r="C1988" t="n">
-        <v>2.499414441332406</v>
+        <v>2.527185261492025</v>
       </c>
       <c r="D1988" t="n">
-        <v>-2.549693004404466</v>
+        <v>-2.241123096894818</v>
       </c>
       <c r="E1988" t="n">
-        <v>1.479180815256873</v>
+        <v>1.630379598420351</v>
       </c>
       <c r="F1988" t="n">
-        <v>0.8241687723632942</v>
+        <v>1.192745858266178</v>
       </c>
       <c r="G1988" t="n">
-        <v>2.993915704750383</v>
+        <v>3.242832776451732</v>
       </c>
     </row>
     <row r="1989">
@@ -47295,19 +47295,19 @@
         <v>3.840061186882556</v>
       </c>
       <c r="C1989" t="n">
-        <v>2.495375413631687</v>
+        <v>2.523146233791306</v>
       </c>
       <c r="D1989" t="n">
-        <v>-2.512265984333332</v>
+        <v>-2.203696076823685</v>
       </c>
       <c r="E1989" t="n">
-        <v>1.490112595584607</v>
+        <v>1.641311378748084</v>
       </c>
       <c r="F1989" t="n">
-        <v>0.8294203103924759</v>
+        <v>1.19799739629536</v>
       </c>
       <c r="G1989" t="n">
-        <v>2.993027599867172</v>
+        <v>3.241944671568522</v>
       </c>
     </row>
     <row r="1990">
@@ -47318,19 +47318,19 @@
         <v>3.845169808992659</v>
       </c>
       <c r="C1990" t="n">
-        <v>2.496632205962927</v>
+        <v>2.524403026122546</v>
       </c>
       <c r="D1990" t="n">
-        <v>-2.53237764036804</v>
+        <v>-2.223807732858393</v>
       </c>
       <c r="E1990" t="n">
-        <v>1.483324725501964</v>
+        <v>1.634523508665441</v>
       </c>
       <c r="F1990" t="n">
-        <v>0.8404476553898951</v>
+        <v>1.209024741292779</v>
       </c>
       <c r="G1990" t="n">
-        <v>3.000900799196864</v>
+        <v>3.249817870898214</v>
       </c>
     </row>
     <row r="1991">
@@ -47341,19 +47341,19 @@
         <v>3.828661445636286</v>
       </c>
       <c r="C1991" t="n">
-        <v>2.657189976984138</v>
+        <v>2.684960797143757</v>
       </c>
       <c r="D1991" t="n">
-        <v>-2.478632825940835</v>
+        <v>-2.170062918431188</v>
       </c>
       <c r="E1991" t="n">
-        <v>1.665380422294056</v>
+        <v>1.816579205457534</v>
       </c>
       <c r="F1991" t="n">
-        <v>0.850510964830357</v>
+        <v>1.219088050733241</v>
       </c>
       <c r="G1991" t="n">
-        <v>3.167496555882352</v>
+        <v>3.416413627583702</v>
       </c>
     </row>
     <row r="1992">
@@ -47364,19 +47364,19 @@
         <v>3.813222820957623</v>
       </c>
       <c r="C1992" t="n">
-        <v>2.777302886201955</v>
+        <v>2.805073706361574</v>
       </c>
       <c r="D1992" t="n">
-        <v>-2.403850564915823</v>
+        <v>-2.095280657406176</v>
       </c>
       <c r="E1992" t="n">
-        <v>1.815406235921879</v>
+        <v>1.966605019085356</v>
       </c>
       <c r="F1992" t="n">
-        <v>0.9252932258553697</v>
+        <v>1.293870311758254</v>
       </c>
       <c r="G1992" t="n">
-        <v>3.332478821715177</v>
+        <v>3.581395893416526</v>
       </c>
     </row>
     <row r="1993">
@@ -47387,19 +47387,19 @@
         <v>3.814230727998753</v>
       </c>
       <c r="C1993" t="n">
-        <v>2.769010862215814</v>
+        <v>2.796781682375433</v>
       </c>
       <c r="D1993" t="n">
-        <v>-2.377766480652015</v>
+        <v>-2.069196573142368</v>
       </c>
       <c r="E1993" t="n">
-        <v>1.817547845641261</v>
+        <v>1.968746628804738</v>
       </c>
       <c r="F1993" t="n">
-        <v>0.9252932258553697</v>
+        <v>1.293870311758254</v>
       </c>
       <c r="G1993" t="n">
-        <v>3.324186797729036</v>
+        <v>3.573103869430385</v>
       </c>
     </row>
     <row r="1994">
@@ -47410,19 +47410,19 @@
         <v>3.803397818896927</v>
       </c>
       <c r="C1994" t="n">
-        <v>2.767204057799594</v>
+        <v>2.794974877959212</v>
       </c>
       <c r="D1994" t="n">
-        <v>-2.299635299803068</v>
+        <v>-1.991065392293421</v>
       </c>
       <c r="E1994" t="n">
-        <v>1.846993513564619</v>
+        <v>1.998192296728097</v>
       </c>
       <c r="F1994" t="n">
-        <v>0.9994700367390541</v>
+        <v>1.368047122641939</v>
       </c>
       <c r="G1994" t="n">
-        <v>3.366886079843026</v>
+        <v>3.615803151544376</v>
       </c>
     </row>
     <row r="1995">
@@ -47433,19 +47433,19 @@
         <v>3.796264143959855</v>
       </c>
       <c r="C1995" t="n">
-        <v>2.784758463526385</v>
+        <v>2.812529283686004</v>
       </c>
       <c r="D1995" t="n">
-        <v>-2.290742838409785</v>
+        <v>-1.982172930900138</v>
       </c>
       <c r="E1995" t="n">
-        <v>1.868104903848724</v>
+        <v>2.019303687012201</v>
       </c>
       <c r="F1995" t="n">
-        <v>0.9994700367390541</v>
+        <v>1.368047122641939</v>
       </c>
       <c r="G1995" t="n">
-        <v>3.384440485569818</v>
+        <v>3.633357557271167</v>
       </c>
     </row>
     <row r="1996">
@@ -47456,19 +47456,19 @@
         <v>3.794424941945366</v>
       </c>
       <c r="C1996" t="n">
-        <v>2.776613510930969</v>
+        <v>2.804384331090588</v>
       </c>
       <c r="D1996" t="n">
-        <v>-2.459218955379663</v>
+        <v>-2.150649047870016</v>
       </c>
       <c r="E1996" t="n">
-        <v>1.792569504465356</v>
+        <v>1.943768287628834</v>
       </c>
       <c r="F1996" t="n">
-        <v>0.9715222010224733</v>
+        <v>1.340099286925358</v>
       </c>
       <c r="G1996" t="n">
-        <v>3.359526831544453</v>
+        <v>3.608443903245802</v>
       </c>
     </row>
     <row r="1997">
@@ -47479,19 +47479,19 @@
         <v>3.795574066782707</v>
       </c>
       <c r="C1997" t="n">
-        <v>2.757883208118831</v>
+        <v>2.785654028278449</v>
       </c>
       <c r="D1997" t="n">
-        <v>-1.76141942651808</v>
+        <v>-1.452849519008432</v>
       </c>
       <c r="E1997" t="n">
-        <v>2.052959013197852</v>
+        <v>2.204157796361329</v>
       </c>
       <c r="F1997" t="n">
-        <v>0.9011741416520627</v>
+        <v>1.269751227554947</v>
       </c>
       <c r="G1997" t="n">
-        <v>3.298587693110068</v>
+        <v>3.547504764811418</v>
       </c>
     </row>
     <row r="1998">
@@ -47502,19 +47502,19 @@
         <v>3.784671345632635</v>
       </c>
       <c r="C1998" t="n">
-        <v>2.748547230615735</v>
+        <v>2.776318050775354</v>
       </c>
       <c r="D1998" t="n">
-        <v>-1.738698322834927</v>
+        <v>-1.43012841532528</v>
       </c>
       <c r="E1998" t="n">
-        <v>2.052711477168017</v>
+        <v>2.203910260331495</v>
       </c>
       <c r="F1998" t="n">
-        <v>0.9011741416520627</v>
+        <v>1.269751227554947</v>
       </c>
       <c r="G1998" t="n">
-        <v>3.289251715606973</v>
+        <v>3.538168787308322</v>
       </c>
     </row>
     <row r="1999">
@@ -47525,19 +47525,19 @@
         <v>3.783205696777672</v>
       </c>
       <c r="C1999" t="n">
-        <v>2.907453356466904</v>
+        <v>2.935224176626523</v>
       </c>
       <c r="D1999" t="n">
-        <v>-1.736973279544883</v>
+        <v>-1.428403372035236</v>
       </c>
       <c r="E1999" t="n">
-        <v>2.212307620335204</v>
+        <v>2.363506403498681</v>
       </c>
       <c r="F1999" t="n">
-        <v>0.9028991849421064</v>
+        <v>1.271476270844991</v>
       </c>
       <c r="G1999" t="n">
-        <v>3.449192867432168</v>
+        <v>3.698109939133518</v>
       </c>
     </row>
     <row r="2000">
@@ -47548,19 +47548,19 @@
         <v>3.779933725644411</v>
       </c>
       <c r="C2000" t="n">
-        <v>2.944531178960551</v>
+        <v>2.97230199912017</v>
       </c>
       <c r="D2000" t="n">
-        <v>-1.891754286323139</v>
+        <v>-1.583184378813491</v>
       </c>
       <c r="E2000" t="n">
-        <v>2.187473040117548</v>
+        <v>2.338671823281026</v>
       </c>
       <c r="F2000" t="n">
-        <v>0.8695315108876303</v>
+        <v>1.238108596790515</v>
       </c>
       <c r="G2000" t="n">
-        <v>3.466250085493129</v>
+        <v>3.715167157194479</v>
       </c>
     </row>
     <row r="2001">
@@ -47571,19 +47571,19 @@
         <v>3.769443619799962</v>
       </c>
       <c r="C2001" t="n">
-        <v>2.941206534950096</v>
+        <v>2.968977355109715</v>
       </c>
       <c r="D2001" t="n">
-        <v>-1.884699596107965</v>
+        <v>-1.576129688598318</v>
       </c>
       <c r="E2001" t="n">
-        <v>2.186970272193163</v>
+        <v>2.33816905535664</v>
       </c>
       <c r="F2001" t="n">
-        <v>0.8765862011028041</v>
+        <v>1.245163287005689</v>
       </c>
       <c r="G2001" t="n">
-        <v>3.467158255611779</v>
+        <v>3.716075327313128</v>
       </c>
     </row>
     <row r="2002">
@@ -47594,19 +47594,19 @@
         <v>3.766673496331116</v>
       </c>
       <c r="C2002" t="n">
-        <v>2.951212688594838</v>
+        <v>2.978983508754456</v>
       </c>
       <c r="D2002" t="n">
-        <v>-1.857748371781477</v>
+        <v>-1.54917846427183</v>
       </c>
       <c r="E2002" t="n">
-        <v>2.2077569155685</v>
+        <v>2.358955698731977</v>
       </c>
       <c r="F2002" t="n">
-        <v>0.8914665471305232</v>
+        <v>1.260043633033408</v>
       </c>
       <c r="G2002" t="n">
-        <v>3.486092616873152</v>
+        <v>3.735009688574501</v>
       </c>
     </row>
     <row r="2003">
@@ -47617,19 +47617,19 @@
         <v>3.768052067784106</v>
       </c>
       <c r="C2003" t="n">
-        <v>3.135315820739797</v>
+        <v>3.163086640899416</v>
       </c>
       <c r="D2003" t="n">
-        <v>-1.993701379837793</v>
+        <v>-1.685131472328146</v>
       </c>
       <c r="E2003" t="n">
-        <v>2.337478844490933</v>
+        <v>2.488677627654411</v>
       </c>
       <c r="F2003" t="n">
-        <v>0.8914665471305232</v>
+        <v>1.260043633033408</v>
       </c>
       <c r="G2003" t="n">
-        <v>3.670195749018112</v>
+        <v>3.919112820719461</v>
       </c>
     </row>
     <row r="2004">
@@ -47640,19 +47640,19 @@
         <v>3.743925505714424</v>
       </c>
       <c r="C2004" t="n">
-        <v>3.12743251564279</v>
+        <v>3.155203335802409</v>
       </c>
       <c r="D2004" t="n">
-        <v>-2.016109497642665</v>
+        <v>-1.707539590133018</v>
       </c>
       <c r="E2004" t="n">
-        <v>2.320632292271977</v>
+        <v>2.471831075435455</v>
       </c>
       <c r="F2004" t="n">
-        <v>0.8914665471305232</v>
+        <v>1.260043633033408</v>
       </c>
       <c r="G2004" t="n">
-        <v>3.662312443921105</v>
+        <v>3.911229515622454</v>
       </c>
     </row>
     <row r="2005">
@@ -47663,19 +47663,19 @@
         <v>3.719118627155031</v>
       </c>
       <c r="C2005" t="n">
-        <v>3.129486515192428</v>
+        <v>3.157257335352047</v>
       </c>
       <c r="D2005" t="n">
-        <v>-2.164115265122065</v>
+        <v>-1.855545357612417</v>
       </c>
       <c r="E2005" t="n">
-        <v>2.263483984829855</v>
+        <v>2.414682767993332</v>
       </c>
       <c r="F2005" t="n">
-        <v>0.8047395382669817</v>
+        <v>1.173316624169866</v>
       </c>
       <c r="G2005" t="n">
-        <v>3.612330238152617</v>
+        <v>3.861247309853967</v>
       </c>
     </row>
     <row r="2006">
@@ -47686,19 +47686,19 @@
         <v>3.729452285161976</v>
       </c>
       <c r="C2006" t="n">
-        <v>3.185740232914275</v>
+        <v>3.213511053073894</v>
       </c>
       <c r="D2006" t="n">
-        <v>-2.173556191010594</v>
+        <v>-1.864986283500947</v>
       </c>
       <c r="E2006" t="n">
-        <v>2.31596133219629</v>
+        <v>2.467160115359768</v>
       </c>
       <c r="F2006" t="n">
-        <v>0.9271666558103732</v>
+        <v>1.173316624169866</v>
       </c>
       <c r="G2006" t="n">
-        <v>3.742040226400499</v>
+        <v>3.917501027575813</v>
       </c>
     </row>
     <row r="2007">
@@ -47709,19 +47709,19 @@
         <v>3.714941193321633</v>
       </c>
       <c r="C2007" t="n">
-        <v>3.188631327459576</v>
+        <v>3.216402147619195</v>
       </c>
       <c r="D2007" t="n">
-        <v>-2.225829798346236</v>
+        <v>-1.917259890836588</v>
       </c>
       <c r="E2007" t="n">
-        <v>2.297942983807334</v>
+        <v>2.449141766970812</v>
       </c>
       <c r="F2007" t="n">
-        <v>0.8748930484747319</v>
+        <v>1.121043016834225</v>
       </c>
       <c r="G2007" t="n">
-        <v>3.713567156544415</v>
+        <v>3.88902795771973</v>
       </c>
     </row>
     <row r="2008">
@@ -47732,19 +47732,19 @@
         <v>3.727898186347701</v>
       </c>
       <c r="C2008" t="n">
-        <v>3.186743140353351</v>
+        <v>3.21451396051297</v>
       </c>
       <c r="D2008" t="n">
-        <v>-2.302159775947142</v>
+        <v>-1.993589868437494</v>
       </c>
       <c r="E2008" t="n">
-        <v>2.265522805660747</v>
+        <v>2.416721588824225</v>
       </c>
       <c r="F2008" t="n">
-        <v>0.8748930484747319</v>
+        <v>1.121043016834225</v>
       </c>
       <c r="G2008" t="n">
-        <v>3.71167896943819</v>
+        <v>3.887139770613505</v>
       </c>
     </row>
     <row r="2009">
@@ -47755,19 +47755,19 @@
         <v>3.710654104887745</v>
       </c>
       <c r="C2009" t="n">
-        <v>3.181563369956213</v>
+        <v>3.209334190115832</v>
       </c>
       <c r="D2009" t="n">
-        <v>-2.413916728562443</v>
+        <v>-2.105346821052795</v>
       </c>
       <c r="E2009" t="n">
-        <v>2.215640254217489</v>
+        <v>2.366839037380966</v>
       </c>
       <c r="F2009" t="n">
-        <v>0.7631360958594309</v>
+        <v>1.009286064218924</v>
       </c>
       <c r="G2009" t="n">
-        <v>3.639445027471872</v>
+        <v>3.814905828647187</v>
       </c>
     </row>
     <row r="2010">
@@ -47778,19 +47778,19 @@
         <v>3.712897612343063</v>
       </c>
       <c r="C2010" t="n">
-        <v>3.179997380166366</v>
+        <v>3.207768200325984</v>
       </c>
       <c r="D2010" t="n">
-        <v>-2.412075709504192</v>
+        <v>-2.103505801994544</v>
       </c>
       <c r="E2010" t="n">
-        <v>2.214810672050942</v>
+        <v>2.36600945521442</v>
       </c>
       <c r="F2010" t="n">
-        <v>0.7644043225308993</v>
+        <v>1.010554290890392</v>
       </c>
       <c r="G2010" t="n">
-        <v>3.638639973684906</v>
+        <v>3.81410077486022</v>
       </c>
     </row>
     <row r="2011">
@@ -47801,19 +47801,19 @@
         <v>3.754911907647103</v>
       </c>
       <c r="C2011" t="n">
-        <v>3.193070787032284</v>
+        <v>3.220841607191903</v>
       </c>
       <c r="D2011" t="n">
-        <v>-2.544377001601745</v>
+        <v>-2.235807094092098</v>
       </c>
       <c r="E2011" t="n">
-        <v>2.174963562077839</v>
+        <v>2.326162345241317</v>
       </c>
       <c r="F2011" t="n">
-        <v>0.7644043225308993</v>
+        <v>1.010554290890392</v>
       </c>
       <c r="G2011" t="n">
-        <v>3.651713380550824</v>
+        <v>3.827174181726138</v>
       </c>
     </row>
     <row r="2012">
@@ -47824,19 +47824,19 @@
         <v>3.74989685176353</v>
       </c>
       <c r="C2012" t="n">
-        <v>3.193070787032284</v>
+        <v>3.220841607191903</v>
       </c>
       <c r="D2012" t="n">
-        <v>-2.545938644416605</v>
+        <v>-2.237368736906958</v>
       </c>
       <c r="E2012" t="n">
-        <v>2.174338904951895</v>
+        <v>2.325537688115373</v>
       </c>
       <c r="F2012" t="n">
-        <v>0.7644043225308993</v>
+        <v>1.010554290890392</v>
       </c>
       <c r="G2012" t="n">
-        <v>3.651713380550824</v>
+        <v>3.827174181726138</v>
       </c>
     </row>
     <row r="2013">
@@ -47847,19 +47847,19 @@
         <v>3.715834055392113</v>
       </c>
       <c r="C2013" t="n">
-        <v>3.191594828159286</v>
+        <v>3.219365648318905</v>
       </c>
       <c r="D2013" t="n">
-        <v>-2.573839431526078</v>
+        <v>-2.265269524016431</v>
       </c>
       <c r="E2013" t="n">
-        <v>2.161702631235108</v>
+        <v>2.312901414398586</v>
       </c>
       <c r="F2013" t="n">
-        <v>0.7298073983879645</v>
+        <v>0.9759573667474574</v>
       </c>
       <c r="G2013" t="n">
-        <v>3.629479267192065</v>
+        <v>3.80494006836738</v>
       </c>
     </row>
     <row r="2014">
@@ -47870,19 +47870,19 @@
         <v>3.684909939172524</v>
       </c>
       <c r="C2014" t="n">
-        <v>3.188359272136485</v>
+        <v>3.216130092296104</v>
       </c>
       <c r="D2014" t="n">
-        <v>-2.576872429038752</v>
+        <v>-2.268302521529105</v>
       </c>
       <c r="E2014" t="n">
-        <v>2.157253876207237</v>
+        <v>2.308452659370715</v>
       </c>
       <c r="F2014" t="n">
-        <v>0.7267744008752905</v>
+        <v>0.9729243692347835</v>
       </c>
       <c r="G2014" t="n">
-        <v>3.62442391266166</v>
+        <v>3.799884713836974</v>
       </c>
     </row>
     <row r="2015">
@@ -47893,19 +47893,19 @@
         <v>3.619362241971077</v>
       </c>
       <c r="C2015" t="n">
-        <v>3.255065231726989</v>
+        <v>3.282836051886608</v>
       </c>
       <c r="D2015" t="n">
-        <v>-2.596933750315259</v>
+        <v>-2.288363842805611</v>
       </c>
       <c r="E2015" t="n">
-        <v>2.215935307287138</v>
+        <v>2.367134090450616</v>
       </c>
       <c r="F2015" t="n">
-        <v>0.7067130795987835</v>
+        <v>0.9528630479582765</v>
       </c>
       <c r="G2015" t="n">
-        <v>3.679093079486259</v>
+        <v>3.854553880661574</v>
       </c>
     </row>
     <row r="2016">
@@ -47916,19 +47916,19 @@
         <v>3.640764248199804</v>
       </c>
       <c r="C2016" t="n">
-        <v>3.395376950728836</v>
+        <v>3.423147770888455</v>
       </c>
       <c r="D2016" t="n">
-        <v>-2.853654568310083</v>
+        <v>-2.545084660800435</v>
       </c>
       <c r="E2016" t="n">
-        <v>2.253558699091055</v>
+        <v>2.404757482254533</v>
       </c>
       <c r="F2016" t="n">
-        <v>0.5982985054549687</v>
+        <v>0.8444484738144616</v>
       </c>
       <c r="G2016" t="n">
-        <v>3.754356054001817</v>
+        <v>3.929816855177132</v>
       </c>
     </row>
     <row r="2017">
@@ -47939,19 +47939,19 @@
         <v>3.668303164622235</v>
       </c>
       <c r="C2017" t="n">
-        <v>3.464357219874476</v>
+        <v>3.492128040034094</v>
       </c>
       <c r="D2017" t="n">
-        <v>-3.007640986086223</v>
+        <v>-2.699071078576576</v>
       </c>
       <c r="E2017" t="n">
-        <v>2.260944401126239</v>
+        <v>2.412143184289717</v>
       </c>
       <c r="F2017" t="n">
-        <v>0.5982985054549687</v>
+        <v>0.8444484738144616</v>
       </c>
       <c r="G2017" t="n">
-        <v>3.823336323147457</v>
+        <v>3.998797124322771</v>
       </c>
     </row>
     <row r="2018">
@@ -47962,19 +47962,19 @@
         <v>3.619937176808527</v>
       </c>
       <c r="C2018" t="n">
-        <v>3.450408421994597</v>
+        <v>3.478179242154215</v>
       </c>
       <c r="D2018" t="n">
-        <v>-2.957119082258557</v>
+        <v>-2.64854917474891</v>
       </c>
       <c r="E2018" t="n">
-        <v>2.267204364777426</v>
+        <v>2.418403147940904</v>
       </c>
       <c r="F2018" t="n">
-        <v>0.5982985054549687</v>
+        <v>0.8444484738144616</v>
       </c>
       <c r="G2018" t="n">
-        <v>3.809387525267578</v>
+        <v>3.984848326442893</v>
       </c>
     </row>
     <row r="2019">
@@ -47985,19 +47985,19 @@
         <v>3.656346893994892</v>
       </c>
       <c r="C2019" t="n">
-        <v>3.462278911050011</v>
+        <v>3.490049731209629</v>
       </c>
       <c r="D2019" t="n">
-        <v>-3.209594236266282</v>
+        <v>-2.901024328756635</v>
       </c>
       <c r="E2019" t="n">
-        <v>2.17808479222975</v>
+        <v>2.329283575393228</v>
       </c>
       <c r="F2019" t="n">
-        <v>0.5982985054549687</v>
+        <v>0.8444484738144616</v>
       </c>
       <c r="G2019" t="n">
-        <v>3.821258014322992</v>
+        <v>3.996718815498307</v>
       </c>
     </row>
     <row r="2020">
@@ -48008,19 +48008,19 @@
         <v>3.674042696358296</v>
       </c>
       <c r="C2020" t="n">
-        <v>3.463489445568954</v>
+        <v>3.491260265728573</v>
       </c>
       <c r="D2020" t="n">
-        <v>-3.47906703818799</v>
+        <v>-3.170497130678343</v>
       </c>
       <c r="E2020" t="n">
-        <v>2.071506205980011</v>
+        <v>2.222704989143488</v>
       </c>
       <c r="F2020" t="n">
-        <v>0.5982985054549687</v>
+        <v>0.8444484738144616</v>
       </c>
       <c r="G2020" t="n">
-        <v>3.822468548841936</v>
+        <v>3.99792935001725</v>
       </c>
     </row>
     <row r="2021">
@@ -48031,19 +48031,19 @@
         <v>3.663523617637084</v>
       </c>
       <c r="C2021" t="n">
-        <v>3.467611187796276</v>
+        <v>3.495382007955894</v>
       </c>
       <c r="D2021" t="n">
-        <v>-3.636611109917431</v>
+        <v>-3.328041202407784</v>
       </c>
       <c r="E2021" t="n">
-        <v>2.012610319515556</v>
+        <v>2.163809102679033</v>
       </c>
       <c r="F2021" t="n">
-        <v>0.5313967003146942</v>
+        <v>0.7775466686741872</v>
       </c>
       <c r="G2021" t="n">
-        <v>3.786449207985092</v>
+        <v>3.961910009160407</v>
       </c>
     </row>
     <row r="2022">
@@ -48054,19 +48054,19 @@
         <v>3.652163313301341</v>
       </c>
       <c r="C2022" t="n">
-        <v>3.462689040532465</v>
+        <v>3.490459860692084</v>
       </c>
       <c r="D2022" t="n">
-        <v>-3.765461660619478</v>
+        <v>-3.456891753109831</v>
       </c>
       <c r="E2022" t="n">
-        <v>1.956147951970927</v>
+        <v>2.107346735134404</v>
       </c>
       <c r="F2022" t="n">
-        <v>0.4904032914639727</v>
+        <v>0.7365532598234656</v>
       </c>
       <c r="G2022" t="n">
-        <v>3.756931015410849</v>
+        <v>3.932391816586163</v>
       </c>
     </row>
     <row r="2023">
@@ -48077,19 +48077,19 @@
         <v>3.667976467215468</v>
       </c>
       <c r="C2023" t="n">
-        <v>3.624893097231509</v>
+        <v>3.652663917391128</v>
       </c>
       <c r="D2023" t="n">
-        <v>-3.882429353258369</v>
+        <v>-3.573859445748722</v>
       </c>
       <c r="E2023" t="n">
-        <v>2.071564931614414</v>
+        <v>2.222763714777892</v>
       </c>
       <c r="F2023" t="n">
-        <v>0.4904032914639727</v>
+        <v>0.7365532598234656</v>
       </c>
       <c r="G2023" t="n">
-        <v>3.919135072109893</v>
+        <v>4.094595873285208</v>
       </c>
     </row>
     <row r="2024">
@@ -48100,19 +48100,19 @@
         <v>3.69655362845669</v>
       </c>
       <c r="C2024" t="n">
-        <v>3.619739735195323</v>
+        <v>3.647510555354942</v>
       </c>
       <c r="D2024" t="n">
-        <v>-3.967147295479323</v>
+        <v>-3.658577387969675</v>
       </c>
       <c r="E2024" t="n">
-        <v>2.032524392689847</v>
+        <v>2.183723175853324</v>
       </c>
       <c r="F2024" t="n">
-        <v>0.4052872625359263</v>
+        <v>0.6514372308954193</v>
       </c>
       <c r="G2024" t="n">
-        <v>3.862912092716879</v>
+        <v>4.038372893892194</v>
       </c>
     </row>
     <row r="2025">
@@ -48123,19 +48123,19 @@
         <v>3.750058176253286</v>
       </c>
       <c r="C2025" t="n">
-        <v>3.629969152763814</v>
+        <v>3.657739972923433</v>
       </c>
       <c r="D2025" t="n">
-        <v>-4.049082113748206</v>
+        <v>-3.740512206238559</v>
       </c>
       <c r="E2025" t="n">
-        <v>2.009979882950785</v>
+        <v>2.161178666114262</v>
       </c>
       <c r="F2025" t="n">
-        <v>0.3953525169488461</v>
+        <v>0.6415024853083391</v>
       </c>
       <c r="G2025" t="n">
-        <v>3.867180662933122</v>
+        <v>4.042641464108437</v>
       </c>
     </row>
     <row r="2026">
@@ -48146,19 +48146,19 @@
         <v>3.78364702771783</v>
       </c>
       <c r="C2026" t="n">
-        <v>3.638894791219717</v>
+        <v>3.666665611379336</v>
       </c>
       <c r="D2026" t="n">
-        <v>-3.995343940347944</v>
+        <v>-3.686774032838297</v>
       </c>
       <c r="E2026" t="n">
-        <v>2.040400790766792</v>
+        <v>2.19159957393027</v>
       </c>
       <c r="F2026" t="n">
-        <v>0.4490906903491082</v>
+        <v>0.6952406587086012</v>
       </c>
       <c r="G2026" t="n">
-        <v>3.908349205429182</v>
+        <v>4.083810006604496</v>
       </c>
     </row>
     <row r="2027">
@@ -48169,19 +48169,19 @@
         <v>3.798310944616946</v>
       </c>
       <c r="C2027" t="n">
-        <v>3.631047678463892</v>
+        <v>3.658818498623511</v>
       </c>
       <c r="D2027" t="n">
-        <v>-3.885337656870722</v>
+        <v>-3.576767749361075</v>
       </c>
       <c r="E2027" t="n">
-        <v>2.076556191401856</v>
+        <v>2.227754974565334</v>
       </c>
       <c r="F2027" t="n">
-        <v>0.4722952622663834</v>
+        <v>0.7184452306258764</v>
       </c>
       <c r="G2027" t="n">
-        <v>3.914424835823723</v>
+        <v>4.089885636999037</v>
       </c>
     </row>
     <row r="2028">
@@ -48189,22 +48189,22 @@
         <v>45490</v>
       </c>
       <c r="B2028" t="n">
-        <v>3.470304620271417</v>
+        <v>3.78557808520366</v>
       </c>
       <c r="C2028" t="n">
-        <v>3.635297689185867</v>
+        <v>3.663068509345485</v>
       </c>
       <c r="D2028" t="n">
-        <v>-3.742278081129796</v>
+        <v>-3.433708173620149</v>
       </c>
       <c r="E2028" t="n">
-        <v>2.138030032420201</v>
+        <v>2.289228815583678</v>
       </c>
       <c r="F2028" t="n">
-        <v>0.4803086888563627</v>
+        <v>0.7264586572158557</v>
       </c>
       <c r="G2028" t="n">
-        <v>3.923482902499685</v>
+        <v>4.098943703674999</v>
       </c>
     </row>
     <row r="2029">
@@ -48212,22 +48212,22 @@
         <v>45491</v>
       </c>
       <c r="B2029" t="n">
-        <v>3.470169176307394</v>
+        <v>3.463420665858369</v>
       </c>
       <c r="C2029" t="n">
-        <v>3.642558572068403</v>
+        <v>3.713936175883822</v>
       </c>
       <c r="D2029" t="n">
-        <v>-3.590122696647164</v>
+        <v>-3.273279438624623</v>
       </c>
       <c r="E2029" t="n">
-        <v>2.20615306909579</v>
+        <v>2.404267976120225</v>
       </c>
       <c r="F2029" t="n">
-        <v>0.4803086888563627</v>
+        <v>0.886887392211382</v>
       </c>
       <c r="G2029" t="n">
-        <v>3.93074378538222</v>
+        <v>4.246068611210651</v>
       </c>
     </row>
   </sheetData>
